--- a/site/evidence-workbook.xlsx
+++ b/site/evidence-workbook.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Policy Paper Chart" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chart Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Projects" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Observations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Components" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Timeline" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Warnings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Policy Paper Chart" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Components" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warnings" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -712,6 +712,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -890,7 +891,7 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>Publishable only with corrections: the cost and millions-per-trunk-km cells are non-additive author aggregates, the date cell is contradicted by every archived timing, and the hubs, circuits, transformers and alt-routes cells are author derivations or judgments rather than sourced values.</t>
+          <t>Publishable only with corrections: the cost and millions-per-trunk-km cells are non-additive author aggregates, the date cell requires a defined milestone and the feeder length has an unresolved source discrepancy, and the hubs, circuits, transformers and alt-routes cells are author derivations or judgments rather than sourced values.</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
@@ -1168,7 +1169,7 @@
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>Topology, capacity, circuits, lines and transformer cells are supported by the archived 2026 ISP and, for capacity, circuits and lines, corroborated directly by Transgrid's now-archived PADR; the cost cell is contradicted because the chart's $3.510bn does not match either archived total ($2,621m AEMO-modelled or $3,519m PADR Option 6, of which $3.510bn is a transcription); trunk_km is supported with a boundary caveat (2023 preparatory 114 km vs the PADR's newer ~100 km), and the millions-per-trunk-km ratio still rests on the chart's unverified 3,510 figure, so the row should not be published as-is.</t>
+          <t>Cost supported with rounding and price-basis qualifications. Topology, capacity and transformer evidence retained; 114 km preparatory versus approximately 100 km PADR scope remains unreconciled. 30.70175438596491 = 3,500 AUD million / 114 km, using the original chart inputs. The $3.5bn rounds the $3,519m nominal Option 6 estimate; the 114 km is the older 2023 preparatory route, whereas the 2026 PADR describes approximately 100 km on a revised scope. This mixed-vintage ratio is not a reconciled source-defined construction cost per km (2023 preparatory p8; PADR pp38,43).</t>
         </is>
       </c>
       <c r="P8" s="5" t="inlineStr">
@@ -1367,7 +1368,7 @@
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>Not publishable as-is: the cost cell rests on a social-value figure rather than capital expenditure, and the closest capital-cost figure archived - TransGrid's own $3,628m (real 2022-23) February 2026 reopener forecast - is a proponent application on a different boundary and basis, not an approved amount. The trunk length now matches a sourced 160 km Stage 1 section exactly, but that is one section of a nine-hundred-kilometre project, and the capacity, syncon, transformer and feeder cells are contradicted by the archived scope.</t>
+          <t>Not publishable as-is: the cost cell rests on a social-value figure rather than capital expenditure, and the closest capital-cost figure archived - TransGrid's own $3,628m (real 2022-23) February 2026 reopener forecast - is a proponent application on a different boundary and basis, not an approved amount. The trunk length now matches a sourced 160 km Stage 1 section exactly, but that is one section of a nine-hundred-kilometre project, and the capacity, syncon and transformer cells conflict on stated source boundaries; line and feeder counts require explicit definitions.</t>
         </is>
       </c>
       <c r="P10" s="5" t="inlineStr">
@@ -1459,7 +1460,7 @@
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>The row describes a NSW half of a project whose archived cost, capacity and timing evidence exists only at whole-interconnector or conditional-option boundaries, so its headline cost is an author split, its transformer rating is contradicted, and its route, syncon and feeder cells are unsupported.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="P11" s="5" t="inlineStr">
@@ -1755,7 +1756,7 @@
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>The row should not be published as-is: the cost and capacity cells are contradicted by archived sources, the length and ratio cells are derivations under a definition Marinus does not meet, and five topology cells are gaps or author judgments.</t>
+          <t>The cost replacement is unresolved on a Link-only boundary; two-link nameplate capacity is 1.5 GW, contradicting 1.4 GW. Length and ratio remain author derivations; topology gaps remain.</t>
         </is>
       </c>
       <c r="P14" s="5" t="inlineStr">
@@ -1786,7 +1787,7 @@
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Project Marinus Stage 1 plus Stage 2, as reported in feedback-loop context</t>
+          <t>Project Marinus Stage 1 plus Stage 2 including NWTD, feedback-loop reported study-period cost; not Link-only</t>
         </is>
       </c>
       <c r="W14" s="5" t="n"/>
@@ -1848,6 +1849,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1923,17 +1925,17 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>contradicted</t>
+          <t>supported_with_boundary</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>2028-12</t>
+          <t>December 2028 committed-project milestone; AER staged infrastructure completion April 2028-April 2030; expansion March 2033</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>No archived source states 2029. AEMO's 2026 ISP gives December 2028 for the committed project; the AER records staged infrastructure completion between April 2028 and April 2030 with generation from December 2028 to September 2030; the Expansion, whose $855m sits in the same row's cost, is timed March 2033.</t>
+          <t>2029 is not the AEMO 2026 committed-project timing of December 2028 (CWO-22 p23), but falls within the AER infrastructure-completion window April 2028-April 2030 (CWO-18 p12). Expansion timing is March 2033 (CWO-22 p57). The chart milestone is unspecified; a timing conflict applies only if comparing the same committed-project milestone.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -1978,11 +1980,7 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>6.7871</t>
-        </is>
-      </c>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Sum of three separately bounded observations: CWO-AO-2025-MAIN-REMADE $5,526.1m (nominal NER-equivalent, Main only, consumer-funded) + CWO-AO-2026-ENABLING-FINAL-INC $406.0m (real 2025-26, Enabling) + CWO-AO-2026-EXPANSION-COST $855m (dollar year not stated, Class 5b, not yet authorised) = $6,787.1m. No source publishes this total, the inputs are not on a common basis, and the sum omits generator-funded H2P and CSS, construction finance and the $186.8m Barigan Creek acquisition. See NON_ADDITIVE_BOUNDARIES (blocker).</t>
@@ -2032,7 +2030,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 GW. Boundary/qualification: 6,000 MW is the declared intended network capacity after the December 2023 amendment, as reported by AEMO and the AER, not capacity available at the row's date: initial delivery is 4,500 MW, the AER states capacity is planned to increase to 6 GW by 2038, and the Expansion's +1,500 MW is timed March 2033. The row's single cell also sits alongside three other archived capacity measures (7.7 GW hosting, 7.7 GW aggregate access cap, 7.15/7.7 GW awarded access rights).</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2084,7 +2082,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>90 km. Boundary/qualification: The AER states core infrastructure comprises a 90 km transmission line corridor between Wollar and Elong Elong. The ASL statement of reasons for the Main authorisation corroborates this as the sum of two segments: an approximately 60 km line from Barigan Creek to Merotherie and an approximately 30 km line from Merotherie to Elong Elong (60+30=90). ACEREZ's own project page separately corroborates 90 km, stating the project consists of 90km of 500kV overhead transmission lines. The boundary is the Main core corridor only: it excludes the Enabling 330 kV lines and the Expansion's new Merotherie-A to Merotherie-B line, both of whose costs are inside this row's cost cell.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -2134,7 +2132,7 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="inlineStr">
         <is>
           <t>$6,787.1m / 90 km = 75.41. The numerator aggregates Main, Enabling and Expansion on three different bases while the denominator is the Main core corridor only, so the ratio is not a like-for-like unit cost. Inputs: CWO-AO-2025-MAIN-REMADE, CWO-AO-2026-ENABLING-FINAL-INC, CWO-AO-2026-EXPANSION-COST, CWO-AO-2025-TRUNK-90KM.</t>
@@ -2180,7 +2178,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 circuits. Boundary/qualification: No archived source states a circuit count. The AER states the transmission lines will be two double circuit 500 kV lines, the authorisation describes each corridor section as comprising two 500 kV double circuit lines, and the ASL statement of reasons for the Main authorisation describes both the Barigan Creek-Merotherie and Merotherie-Elong Elong segments as each comprising two 500 kV double circuit lines; 2 lines x 2 circuits = 4. Inputs: CWO-AO-2025-LINES-2, CWO-AO-2024-AUTH-DC-LINES, CWO-AO-2024-LINES-ASL-SOR.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2228,7 +2226,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 lines. Boundary/qualification: The AER states the transmission lines on the 90 km core corridor will be two double circuit 500 kV lines, initially operated at 330 kV between Merotherie and Elong Elong; the authorisation and the ASL statement of reasons both state the same composition for each of the Barigan Creek-Merotherie (approx. 60 km, operated at 500 kV) and Merotherie-Elong Elong (approx. 30 km, operated at 330 kV) sections.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -2278,7 +2276,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>No archived source counts or assesses alternative routes for this project. The value is an author definition; see the AUTHOR_DECISION_REQUIRED warning.</t>
@@ -2316,7 +2314,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>Up to 1,750 MVA authorised Main system strength; AER 7 × 250 MVA units versus PACR 7 × 240 MVA units, unresolved rating discrepancy; not confirmed installed total</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -2368,7 +2366,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 hubs. Boundary/qualification: Archived sources name two energy hubs for the committed project (Merotherie and Elong Elong) and treat Barigan Creek as a switching station. The chart's 3 counts Merotherie-A, Merotherie-B and Elong Elong by combining the committed project with the future Expansion; no source counts hubs that way.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -2420,7 +2418,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15000 MVA (chart arithmetic, not unit count). Boundary/qualification: No archived source states an installed transformer MVA total. The 2026 ISP states 4 x 1,500 MVA 500/330/33 kV transformers at the committed Merotherie substation, 3 x 1,500 MVA at the Expansion's Merotherie-B and 3 x 1,500 MVA at the expanded Elong Elong; (4+3+3) x 1,500 = 15,000 MVA. The figure therefore mixes committed and future scope. Inputs: CWO-AO-2026-TX-MEROTHERIE-A, CWO-AO-2026-TX-MEROTHERIE-B, CWO-AO-2026-TX-ELONG.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -2463,13 +2461,17 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>contradicted</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
+          <t>supported_with_boundary</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Around 150 km H2P corridor / 150 km generator-connection lines; unresolved 166 km conditional/vintage alternative</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Two archived sources state 150 km: the AER's remade determination states the hub to project 330 kV network will cover a corridor of around 150 km, and ACEREZ's own project page states the project consists of 150 km of 330kV transmission lines for generator connections. A third, the ASL statement of reasons for the Main authorisation, instead states the 330 kV H2P network from the Energy Hubs to 13 switching stations comprises a total of approximately 166 kilometres of transmission lines. All three describe the same H2P/generator-connection network boundary but state different lengths; the contradiction is retained unresolved. The H2P network is generator-funded and includes conditional separable portions, five of which were excluded in 2025.</t>
+          <t>The chart's 150 km has positive support: CWO-18 p11 states a corridor of around 150 km and CWO-26 derivative line18 states 150 km of 330 kV generator-connection lines. CWO-23 p10 instead describes approximately 166 km of H2P lines, with conditional separable portions (pp12,19). Different vintages, corridor versus line measurement and conditional scope remain unreconciled. Retain an unresolved source discrepancy, not a same-boundary numerical disproof; five portions were excluded in 2025.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -2482,7 +2484,11 @@
           <t>CWO-18 PDF p11; CWO-23 PDF p10; CWO-26 web</t>
         </is>
       </c>
-      <c r="J16" s="6" t="n"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CWO-AO-2025-H2P-150KM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2564,7 +2570,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4892 AUD million. Boundary/qualification: The only archived amount that rounds to $4.9 billion is AEMO's 2024 ISP expected cost of $4,892 million in June 2023 dollars, Class 3 (-5% to +12%), for the HumeLink candidate option. The 2026 ISP publishes no cost for HumeLink because it is now committed, so the chart's cell is two ISP vintages old. It is not the controlling regulatory amount: the AER determined $4,573.5 million across all stages (real 2022-23, excluding equity raising). Other dated amounts on other boundaries are Transgrid's $4,881m (June 2023 dollars, escalators and equity raising deducted), AEMO's feedback-loop total of $4.88 billion ($2022-23), and the NSW planning capital investment value of $4.8 billion. Whether the author intended the ISP estimate, the feedback-loop total, or a scope-complete total that also includes the separately actionable Wondalga switching station at $220 million cannot be determined from the workbook; see AUTHOR_DECISION_REQUIRED.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2616,7 +2622,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2200 MW. Boundary/qualification: AEMO's 2026 ISP states that after HumeLink is in service the transfer capability between SNSW and CNSW will increase by 2,200 MW in both directions, and the 2024 ISP reports 2,200 MW in both directions as additional network capacity. That is a direction-specific transfer-capability increase on one flow path, not a rating of the line or a single 'network capacity'. The workbook does not define the column. Different dated measures exist for the same project: 2,570 MW of additional firm capacity or generation accommodated (PADR and PACR), 2,230-2,570 MW of Tumut to Sydney transfer uplift (2020 ISP), and REZ hosting figures of +1,000 MW at Wagga Wagga (2020 ISP) and 400 MW in N5 / 2,200 MW in N6+N7 (2026 ISP).</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2668,7 +2674,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>365 km. Boundary/qualification: The NSW planning decision approves development of around 365 kilometres of new double circuit 500 kV transmission lines, and the 2026 ISP records -365 km when HumeLink moved from actionable to committed. Neither source labels the metric, so route-km versus circuit-km is unresolved and is not resolved here. Two other archived lengths exist on other bases: approximately 630 km of upgrades (2020 ISP, before the all-double-circuit refinement, where the PADR's three sections were 260 km, 110 km and 260 km) and around 360 km (AER 2022 and AER 2023). The chart defines trunk km as total distance rated at 500 kV; the Gugaa to Wagga Wagga line is built to 500 kV but initially operated at 330 kV and its length is not stated anywhere in the archive.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2720,7 +2726,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>13.424657534246577</t>
+          <t>13.424657534246577 AUD million per km (chart-derived). Boundary/qualification: The cell is the chart's own arithmetic: 4,900 divided by 365 = 13.4247. Its inputs are the chart's cost cell and trunk km cell, not two sourced observations on a common boundary, and no archived source publishes a cost per kilometre for HumeLink. Substituting the AER all-stage allowance (HUM-AO-2024-AER-ALLSTAGE, $4,573.5m) over the same 365 km gives 12.53; substituting the 2020 ISP's 630 km over the 2024 ISP cost (HUM-AO-2024-ISP-COST) gives 7.77. The ratio therefore carries the boundary problems of both inputs.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2768,7 +2774,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: Transgrid confirmed to the AER that in all-double-circuit Option 3C two circuits are constructed on one double circuit transmission tower, i.e. one line of towers, and that the preferred option is a complete double circuit configuration between all three substation locations. So 2 circuits is correct for a single line section. The project as a whole is three such sections: the 2026 ISP lists three new 500 kV transmission circuits between Maragle-Bannaby, Maragle-Gugaa and Gugaa-Bannaby, and the 2024 ISP adds that these circuits are built on double circuit transmission structures. Read against the workbook's definition ('New parallel 500kV circuits added') the chart's 2 counts one section, not the project. The archive uses 'lines' (2021 PACR) and 'circuits' (2026 ISP) for the same three elements and does not reconcile the terms.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2820,7 +2826,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 lines. Boundary/qualification: The archived scope is three new 500 kV transmission lines forming an electrical loop between Maragle, Wagga Wagga and Bannaby, each constructed double-circuit, which is three lines of towers under the workbook's definition ('Number of lines of towers'), not one. The chart's 1 is correct only for a single section. A further separate line is in scope: a new 500 kV double-circuit line between Gugaa and Wagga Wagga initially operated at 330 kV. The PACR also warns that its schematic lines represent circuits and are not intended to represent transmission line routes, so the count depends on which convention the author is using.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2870,7 +2876,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Alternative geographically separated corridors are an author definition that no archived source supplies; per the contract alt_routes is always a judgment. The archive contains competing, unresolved statements about route diversity rather than a count: the PADR treated the loop as offering greater route-diversity opportunity while deferring final diversity decisions; Wunelli alleged the developed 3C configuration had limited diversity potential; and the AER rejected the route-diversity grounds of the dispute while requiring a different option (1C-new) to be added. September 2021 route changes removed two proposed segments and added a Gilmore Valley connection. None of this establishes a corridor count of 0 or any other number.</t>
@@ -2914,7 +2920,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>No archived source states that HumeLink includes no synchronous condensers. The scope lists in the 2021 PACR, the 2024 ISP and the 2026 ISP name transformers, line shunt reactors and substation augmentations and do not mention synchronous condensers, but silence is not a stated absence and the contract forbids backfilling the chart value.</t>
@@ -2958,7 +2964,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>The workbook's notes define trunk km, circuits, lines, alt routes, syncons, transformers and feeder lines but never define 'Hubs', and no archived HumeLink source counts hubs or states that there are none. Nothing archived supports or contradicts the 0.</t>
@@ -2996,7 +3002,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7500 MVA (chart arithmetic, not unit count). Boundary/qualification: 7,500 MVA is the sum of the published unit ratings and counts: three 500/330 kV 1,500 MVA transformers at Maragle (HUM-AO-2026-ISP-TX-MARAGLE, count 3) plus two at the new Gugaa substation (HUM-AO-2026-ISP-TX-GUGAA, count 2), i.e. 5 x 1,500 MVA. No archived source publishes a cumulative MVA total; the addition is the chart's. The same five units are described in the 2021 PACR (as 500/330/33 kV at Maragle and the new Wagga Wagga substation) and in the 2020 ISP and 2024 ISP, so the scope has been stable since 2020.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3046,7 +3052,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
           <t>No archived source states that HumeLink includes no lower-voltage feeder lines, so the 0 cannot be marked supported. The archive in fact describes lower-voltage connections inside the approved scope whose route lengths are not published: a new 500 kV double-circuit line between Gugaa and Wagga Wagga initially operated at 330 kV (2026 ISP; a 330 kV double circuit connection to the existing Wagga Wagga substation in the 2021 PACR), and a demolition and rebuild of around 2 km of Line 51 as a double circuit 330 kV line (NSW planning decision). Whether these meet the workbook's feeder-line definition, and what length to record, is unresolved.</t>
@@ -3144,12 +3150,12 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1,364 AUD million; CNSW-SNW Option 1 including Waratah Super Battery and related upgrades (AEMO 2026 p39 footnote79); Class 5b ±50%, dollar year unstated; not the 110 km line alone</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>AEMO 2026 ISP Appendix A5 reports $1,364 million, Class 5b (±50%), for CNSW-SNW Option 1. The chart's $1.36bn is that amount expressed in billions. The dollar year is not stated in the table, and the 2024 ISP $1,099m and the May 2023 NSW Network Infrastructure Strategy Stage 1 figure of about $1 billion are separate non-comparable observations.</t>
+          <t>AEMO 2026 p39 reports $1,364m, Class 5b ±50%, for CNSW-SNW Option 1. Footnote79 includes Waratah Super Battery and related upgrades; do not reduce the cost boundary to the 110 km line alone. The original $1.36bn is consistent with rounding, but the dollar year is unstated. The 2024 $1,099m and 2023 approximately $1bn observations are separate non-comparable vintages.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -3196,7 +3202,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5000 MW. Boundary/qualification: AEMO 2026 states forward additional network capacity of 5,000 MW, described as accommodation of additional new generation from north of Bayswater and 2/3 generation from Central West New South Wales, plus REZ N10: 2,000 MW. The boundary is a network hosting/transfer uplift across the CNSW-SNW flow path, not a rating of the single Olney-Bayswater South line; the EnergyCo strategy frames the same project as lifting supportable combined REZ output from 3 GW to as much as 8 GW.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3248,7 +3254,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>110 km. Boundary/qualification: EnergyCo's 2026 transmission infrastructure page states 'The new overhead 500 kV transmission line will span 110 kilometres, connecting existing transmission lines at Bayswater and Olney, near Eraring,' and the EnergyCo project page states 'a new, 110-kilometre, overhead 500 kilovolt (kV) transmission line between Bayswater in the Upper Hunter and Olney in the Lower Hunter.' No AEMO ISP appendix states a route length.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -3300,7 +3306,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>12.363636363636365</t>
+          <t>12.363636363636365 AUD million per km (chart-derived). Boundary/qualification: The chart's ratio is cost_aud_billion times 1000 divided by trunk_km: 1.36 * 1000 / 110 = 12.363636363636365. Both inputs are now archived: cost_aud_billion is the $1,364m AEMO 2026 ISP figure (HTP-AO-2026-COST) expressed and rounded to $1.36bn, and trunk_km is the 110 km EnergyCo route length (HTP-AO-2026-ENERGYCO-TRUNK-KM). This reproduces the chart's existing cell exactly; no new value is computed.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3348,7 +3354,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: AEMO 2026 describes 'A new 500 kV double-circuit line between Olney substation and Bayswater South substation'; a double-circuit line carries two circuits. AEMO 2024 uses the same double-circuit wording for the near Eraring to near Bayswater line. EnergyCo's 2026 transmission infrastructure page corroborates this: 'It will be supported by double-circuit steel lattice towers,' adding a physical boundary (towers up to 85 m tall, generally spaced 300-600 m apart) without changing the two-circuit count.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3400,7 +3406,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lines. Boundary/qualification: AEMO 2026 describes a single new 500 kV double-circuit line between Olney and Bayswater South substations. EnergyCo's 2026 pages corroborate a single line and add a route boundary: the transmission infrastructure page states 'The new overhead 500 kV transmission line will span 110 kilometres, connecting existing transmission lines at Bayswater and Olney, near Eraring,' and the project page adds that it will 'create a 500 kV ring of transmission infrastructure' by connecting to the state's existing 500 kV lines.</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -3450,7 +3456,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Route diversity is an author definition. The author counts 1 because completing the northern Sydney Ring gives an alternative 500 kV path south from Bayswater, discounting sections that parallel the existing 330 kV corridor. Archived sources make network-flow and enabled-generation claims only; no captured source counts alternative routes. The NSW Network Infrastructure Strategy's third-corridor indication for HTP Stage 2 is a map feature and does not appear in the archived text derivative, so it is not cited.</t>
@@ -3486,7 +3492,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="inlineStr">
         <is>
           <t>No archived source states that the project includes or excludes synchronous condensers. AEMO's 2026 scope list does not mention syncons, but absence from a scope list is not a stated absence, and the Transgrid system strength PACR the author relies on was not captured.</t>
@@ -3522,7 +3528,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
           <t>No archived source states that the project provides zero connection hubs. The author's reasoning is that HTP is not a REZ and so hosts no renewable connection hubs; the archived sources list switching stations and substations without counting hubs either way.</t>
@@ -3560,7 +3566,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3000 MVA (chart arithmetic, not unit count). Boundary/qualification: AEMO 2026 and AEMO 2024 both state 'Two 500/330 kV 1,500 MVA transformers at Eraring substation'. The chart's 3000 is the two stated 1,500 MVA units expressed as a combined MVA figure; the sources state the unit rating and the count, not the combined figure.</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -3610,7 +3616,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="inlineStr">
         <is>
           <t>No archived source states that the project includes or excludes hub-to-project feeder lines. The author's zero rests on EIS Table 4.1, which was not captured (NSW planning portal returned HTTP 404 on both routes).</t>
@@ -3695,17 +3701,13 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>contradicted</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>7570 AUD million in $2023 (Stage 1 $5,035m plus Stage 2 $2,535m, as reported by AEMO)</t>
-        </is>
-      </c>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>No archived source states $5.5 billion for any Project Marinus boundary. For the chart's own boundary (Marinus Link 1 &amp; 2) AEMO's 2026 feedback-loop assessment reports a total project cost of $7,570 million in $2023. Separately stated observations range from $3,481m (2021 PACR, $2020) to $5,035m Stage 1 plus $2,535m Stage 2 ($2023). NWTD ($1,144m plus $525m) is excluded from these figures. Separately, the September 2025 joint ministerial release reports $3.8bn CEFC funding secured for Stage 1 at financial close, alongside unstated equity commitments from the Commonwealth, Tasmania and Victoria; this is a funding/debt figure for Stage 1 only, not a total project cost, and does not state $5.5bn for any boundary either.</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -3844,16 +3846,17 @@
           <t>millions_per_trunk_km</t>
         </is>
       </c>
-      <c r="D45" s="5">
-        <f>C11/E11 *1000</f>
-        <v/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>=C11/E11 *1000</t>
+        </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="inlineStr">
         <is>
           <t>A workbook formula dividing the cost cell by the trunk length cell. Both inputs are unsupported or derived: the cost cell is contradicted (see cost_aud_billion) and the length cell is the sum of ML-AO-2025-LENGTH-SUBSEA and ML-AO-2025-LENGTH-UNDERGROUND. No archived source publishes a cost per kilometre for Project Marinus.</t>
@@ -3993,7 +3996,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="n"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Geographic route diversity is an author definition that no archived source supplies. Sources establish that Marinus Link operates in parallel with the existing Basslink interconnector across Bass Strait, which is the fact the author's count would rest on; the count of 2 remains the author's.</t>
@@ -4037,7 +4040,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="inlineStr">
         <is>
           <t>No archived source states synchronous condenser capacity within the Project Marinus or NWTD scope. The zero is not contradicted, but it is not evidenced either.</t>
@@ -4073,7 +4076,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n"/>
       <c r="G50" s="5" t="inlineStr">
         <is>
           <t>No archived source counts hubs for Project Marinus. The scope names converter stations at Burnie and Hazelwood and switching stations at Heybridge and Staverton; whether any of these count as a hub under the chart's definition is the author's decision.</t>
@@ -4117,7 +4120,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="n"/>
       <c r="G51" s="6" t="inlineStr">
         <is>
           <t>No archived source states committed or actionable transformer capacity for Project Marinus. The delivery scope names HVDC converter stations, whose rating AEMO reports as link capacity rather than transformer MVA.</t>
@@ -4161,7 +4164,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="n"/>
       <c r="G52" s="6" t="inlineStr">
         <is>
           <t>The 2026 ISP describes 220 kV NWTD works (Sheffield-Heybridge-Burnie, Palmerston-Sheffield, Staverton-Hampshire, Sheffield-Staverton) that meet the chart's definition of lower-voltage lines connecting to the main trunk, but no archived source states their length. The zero is therefore unsupported rather than confirmed.</t>
@@ -4257,7 +4260,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="n"/>
       <c r="G54" s="6" t="inlineStr">
         <is>
           <t>The author sums CNSW-NNSW Option 1, CNSW-NNSW Option 2 and N2 Option 1 from the Draft 2026 ISP Appendix 5, pages 34-35. That draft is not archived. In the archived final 2026 ISP Appendix A5 the New England section (pp30-32) carries only CNSW-NNSW Option 1 with a blank reported-cost field, and pages 34-35 are the Gladstone Project. The three amounts are therefore not found and the chart value is not backfilled. The archived 2024 ISP Appendix A5 does state $1,834m, $1,493m and $370m for the equivalent superseded two-part options (NER-AO-2024-COST-FP1, NER-AO-2024-COST-FP2, NER-AO-2024-COST-N2OPT1); those are recorded as observations only and are not summed.</t>
@@ -4397,7 +4400,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="n"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
           <t>The cell is the chart's own arithmetic, $5,914m divided by 305 km. The cost input remains a gap against the archive: no archived source states a current NIP cost. The 305 km input is now supported with a boundary caveat (a recommended-but-not-yet-finalised corridor length from the Bulk Corridor Design Refinement Report, Table E-1/6-1), but a ratio with an unsupported cost input cannot itself be marked supported. Nothing archived states or contradicts this $/km ratio, and it is not recalculated from any observation.</t>
@@ -4435,7 +4438,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 circuits. Boundary/qualification: EnergyCo's 2025 Generation and Storage Consultation Paper states the New REZ Network Infrastructure's new transmission infrastructure comprises two new double-circuit 500 kV transmission lines to Bayswater Power Station (NER-AO-2025-CONSULT-LINES, NER-AO-2025-CONSULT-CIRCUITS). Two lines at two circuits per double-circuit line is 2 x 2 = 4 circuits, matching the chart's cell. AEMO's archived 2026 ISP delivery scope does not state this count itself; its scope list enumerates five distinct double-circuit lines (Central B - Bayswater South 500 kV DCST, Central A - Bayswater South 500 kV DCST, Central A - Central B 500 kV DCST, Central A - North 500 kV built / 330 kV operated DCST, and two 330 kV DCST lines between Central B and East), so this derivation applies to the two Bayswater-connecting lines the consultation paper describes, not the whole delivery scope. The Bulk Corridor Design Refinement report the author also cited is still not archived.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -4487,7 +4490,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 lines. Boundary/qualification: EnergyCo's 2025 Generation and Storage Consultation Paper states the New REZ Network Infrastructure's new transmission infrastructure comprises two new double-circuit 500 kV transmission lines connecting the New England REZ to the existing NSW transmission network near Bayswater Power Station, matching the chart's cell directly. The archived 2026 ISP Appendix A5 does not state this itself; its delivery scope enumerates five distinct double-circuit lines (three at 500 kV, one 500 kV built / 330 kV operated, and 330 kV lines between Central B and East), on a different counting boundary from the chart's trunk-line count. The Bulk Corridor Design Refinement report the author also cited is still not archived.</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -4537,7 +4540,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="n"/>
       <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Route redundancy is an author definition no source supplies. The author reasons that because the two parallel lines share a single 140 m corridor with a 70 m easement each, there is no effective route redundancy; that corridor width statement is from the unarchived Bulk Corridor Design Refinement report. No archived source counts alternative routes.</t>
@@ -4573,7 +4576,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="n"/>
       <c r="G61" s="6" t="inlineStr">
         <is>
           <t>No archived source states that synchronous condensers are absent from the NIP scope. The 2026 ISP delivery-scope list for CNSW-NNSW Option 1 contains no synchronous condensers, but silence in a scope list is not a stated absence, and the appendix states the final scope is subject to the competitive procurement outcome. The author's supporting material (Transgrid PACR on meeting system strength requirements in NSW, Section 2.3.5.4) is not archived.</t>
@@ -4611,7 +4614,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 hubs. Boundary/qualification: The archived 2026 ISP delivery scope names five hubs inside CNSW-NNSW Option 1: Central B Hub, North and East Hubs, Central South Hub and Central A Hub. The count matches the chart's 5, but the chart's names and voltages (Central South 500 kV, Central Hub A 500 kV, Central Hub B 500 kV, East 330 kV, North 330 kV) come from the EnergyCo interactive map, which is not archived; the ISP describes North and East as 330 kV hubs and Central South as 500 kV without a five-hub tally of its own. The Bulk Corridor Design Refinement Report corroborates the count and its history: its main text describes 'Four energy hubs' (p25), and footnote 2 on the same page states the total number of energy hubs increased to five following the splitting of the central hub into two substations (Central Hub A and Central Hub B) in October 2025, matching the 2026 ISP's five-hub scope.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -4663,7 +4666,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10500 MVA (chart arithmetic, not unit count). Boundary/qualification: The chart cell is a sum of two archived line items: four 500/330/33 kV 1,500 MVA transformers at Central B Hub (NER-AO-2026-TFMR-CENTRALB) plus three 500/330/33 kV 1,500 MVA transformers at Central A Hub (NER-AO-2026-TFMR-CENTRALA), that is (4 x 1,500) + (3 x 1,500) = 10,500 MVA. The four 340 MVA phase shifting transformers at Central B (NER-AO-2026-PST-CENTRALB) are a separate archived item and are not in the total. AEMO does not publish the 10,500 MVA total itself, and it states the final scope is subject to the procurement outcome.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -4713,7 +4716,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="n"/>
       <c r="G64" s="6" t="inlineStr">
         <is>
           <t>No archived source documents hub-to-project feeder lines for the NIP, and none states their absence either. The author's note records only that no feeder lines are yet documented, in contrast with Central-West Orana. The zero is therefore an absence of evidence, not a sourced zero.</t>
@@ -4803,7 +4806,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>3.628</t>
+          <t>3.628 AUD billion. Boundary/qualification: TransGrid's February 2026 application to reopen its 2023-2028 revenue determination states a forecast total capital expenditure to complete PEC of $3,628 million (real 2022-23), compared with the AER's inflation-adjusted $2,121 million PEC CPA allowance; the application's own cover letter rounds this to 'the forecast cost to deliver PEC had increased to $3.6 billion.' This is TransGrid's (NSW) forecast only, following the Contract Failure Transgrid's Board recognised on 25 October 2023 - it is a proponent application, not an AER-approved amount, and it is not stated to include ElectraNet's SA component. It is on a different price basis and boundary from the AER's 2021 $457.4m/$1,817.9m ($2017-18) determinations and the AER's $2.3bn ($2017-18) descriptive figure. The chart's $4.1 billion still matches only Transgrid's separate estimate of social value generated from June 2023 to June 2026 - a benefit measure, not capital expenditure; see CHART_DERIVATION.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4855,7 +4858,7 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.8 GW. Boundary/qualification: No archived source states 2.2 GW on any boundary. AEMO 2026 states 150 MW after Stage 1 and that the NSW-SA interconnector is expected to increase to 800 MW in both directions after Stage 2 (0.8 GW). AEMO 2024 states Stage 1 150 MW, Stage 2 800 MW NSW-SA and 100 MW VIC-SA. The joint ElectraNet/Transgrid project page corroborates this, describing the interconnector as built with 'approximately 800MW transfer capacity'. REZ network limits (S2 800, N5 800, SWNSW1 400) are a separate measure and are not interconnector capacity.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -4907,7 +4910,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>160 km. Boundary/qualification: No archived source defines a trunk length for Project EnergyConnect. Transgrid's June 2026 completion release now gives an exact match for the chart's 160 km - 'the first stage of the project, a 160km line from the South Australian border to Buronga and into Victoria' - but that is Stage 1 alone, not the interconnector trunk. Other archived candidates remain: the 165 km Dinawan to Wagga Wagga section (built 500 kV, operated at 330 kV); 135 km (SA border-Buronga) and 375 km (Buronga-Dinawan), both 330 kV; and a 540 km Buronga-Wagga Wagga Stage 2 line per the same release. Both Transgrid's own page and the joint ElectraNet/Transgrid project page state the whole project stretches 900 km, and both Transgrid's completion release and the joint project page separately state a 700 km NSW section (which does not reconcile arithmetically with the individually stated 330/500 kV section lengths, 675 km). The South Australian route length is not stated anywhere in the archive.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4957,10 +4960,10 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="n"/>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>25.625 = 4,100 / 160, dividing the chart's cost cell by its trunk cell. Both inputs fail: the $4.1bn is a social-value figure (PEC-AO-2026-TG-SOCIAL-VALUE), not capital cost, and 160 km is one 165 km section of a 900 km project (PEC-AO-2026-KM-DINAWAN-WAGGA, PEC-AO-2026-KM-WHOLE). No archived source supports a $/km for PEC on any boundary.</t>
+          <t>25.625 = 4,100 / 160 uses the chart inputs, but $4.1bn is social value, not capex (PEC-TG-PROJECT-PAGE line1705), and 160 km is the sourced Stage 1 SA-border-Buronga-and-Victoria length (PEC-TG-2026-COMPLETION lines161-166), not the whole 900 km project. A social-benefit numerator and a stage-only denominator do not establish project construction cost per km.</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -5003,7 +5006,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: AEMO describes every new PEC line section as double-circuit, so 2 is right per line but is not a project-wide count. It is also time-dependent: Bundey-Buronga was strung one circuit initially in Stage 1, and the second 330 kV circuit is closed in Stage 2.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -5050,13 +5053,13 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>contradicted</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr"/>
+          <t>supported_with_boundary</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="n"/>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>AEMO's delivery scope lists at least five distinct new or converted line sections at three voltages: Robertstown-Bundey 275 kV, Bundey-Buronga 330 kV, Buronga-Red Cliffs 220 kV, Buronga-Dinawan 330 kV and Dinawan-Wagga Wagga 500 kV, plus the Para-Robertstown 275 kV conversion into Tungkillo. No source states a project-wide line count of 1.</t>
+          <t>AEMO 2024 pp17-18 lists multiple physical sections/lines. The chart's one line may instead mean one interconnector corridor; no chart-compatible line count is established without defining lines versus sections/corridors.</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -5101,7 +5104,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="n"/>
       <c r="G72" s="5" t="inlineStr">
         <is>
           <t>No archived source counts alternative routes for Project EnergyConnect. The 2020 ISP records that non-network alternatives were investigated but not pursued in the RIT-T; that is not a route count. The 0 is an author definition.</t>
@@ -5147,7 +5150,7 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2 × 100 MVA per synchronous condenser at Dinawan; additional 1 × 100 MVA at Buronga; not a certified project-wide total</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -5197,7 +5200,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="n"/>
       <c r="G74" s="5" t="inlineStr">
         <is>
           <t>No archived source counts hubs for PEC. AEMO states a new 330 kV switching station at Dinawan and Transgrid a new 4.5ha substation near Bundure; whether a switching station counts as a hub is an author definition, so 0 is neither supported nor contradicted.</t>
@@ -5245,7 +5248,7 @@
           <t>contradicted</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="n"/>
       <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Transformers are an explicit, substantial part of the sourced scope: 3 x 400 MVA 330/275 kV at Bundey; 1 x 200 MVA 330/220 kV and 1 x 200 MVA 330 kV phase shifting transformer at Buronga; additional 4 x 200 MVA phase shifting transformers and 2 x 200 MVA 330/220 kV transformers at Buronga. Transgrid records 5 phase shifting transformers installed at Buronga. A chart value of 0 is contradicted; no source states a single project transformer total.</t>
@@ -5290,17 +5293,17 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>contradicted</t>
+          <t>supported_with_boundary</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Approximately 22 km 220 kV Buronga-Red Cliffs works; feeder classification unresolved</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>The project scope includes a new Buronga to Red Cliffs 220 kV double-circuit line, and Transgrid records the upgrade of about 22 km of existing 220 kV transmission between Buronga substation and Red Cliffs, replacing lattice structures with 79 monopoles. Lower-voltage works are not zero.</t>
+          <t>Approximately 22 km of 220 kV Buronga-Red Cliffs works is sourced (AEMO 2024 p18; Transgrid project page line1262). It is an interconnector spur: zero lower-voltage works is false, but whether this is a hub-to-project feeder depends on the chart definition. No unqualified REZ-feeder replacement is established.</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -5394,17 +5397,17 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>contradicted</t>
+          <t>supported_with_boundary</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>3.519</t>
+          <t>3.519 AUD billion nominal, combined Option 6 stages; P50 Class 5 (+100%/-50%); rounds to original 3.5</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Transgrid's own PADR, now archived, states Option 6's total capital cost as $3,519 million (nominal), staged $1,135 million (Stage 1) then $2,384 million (Stage 2), confirming AEMO's secondhand quotation. The chart's 3.510 is not a separate basis but a transcription of 3,519 (last two digits transposed). For the same combined boundary AEMO separately states a modelled $2025 cost of $2,621 million ($261m + $2,360m), which is not comparable on price basis.</t>
+          <t>The immutable chart contains $3.5bn, consistent with rounding the PADR Option 6 total of $3,519m nominal to one decimal billion. The source gives Stage 1 $1,135m and Stage 2 $2,384m, P50 Class 5 (+100%/-50%). AEMO's $2,621m modelled $2025 amount is a different price basis. No transcription error is established (PADR p38; AEMO 2026 p43).</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -5451,7 +5454,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.6 GW. Boundary/qualification: Transgrid's own PADR states that Option 6, once complete (both stages), adds 3.6 GW of transfer capacity to the network supplying Sydney, Newcastle and Wollongong from the south -- the same combined Option 6 boundary the chart represents. AEMO separately states 3,600 MW forward capacity for the 500 kV transmission option alone (and 0 MW for the power flow control option).</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5503,7 +5506,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>114 km. Boundary/qualification: Transgrid's June 2023 Southern Ring preparatory-activities document, now archived, states the new Bannaby-South Creek 500 kV double-circuit overhead line has an approximate length of 114 km, matching the chart exactly. However, Transgrid's later 2026 PADR instead describes the (differently scoped) Bannaby-South Western Sydney 500 kV line as extending to around 100 km, so the chart's figure reflects an earlier preparatory estimate, not the current PADR boundary.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -5553,10 +5556,10 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="n"/>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Chart derivation: 3,510 AUD million divided by 114 km. The 114 km is now archived (2023 Southern Ring document), but 3,510 does not match any archived cost figure -- the archived PADR Table 3.1 total for Option 6 is $3,519 million, not $3,510 million -- so the ratio as calculated still cannot be validated.</t>
+          <t>30.70175438596491 = 3,500 AUD million / 114 km, using the original chart inputs. The $3.5bn rounds the $3,519m nominal Option 6 estimate; the 114 km is the older 2023 preparatory route, whereas the 2026 PADR describes approximately 100 km on a revised scope. This mixed-vintage ratio is not a reconciled source-defined construction cost per km (2023 preparatory p8; PADR pp38,43).</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr"/>
@@ -5591,7 +5594,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: AEMO describes a double-circuit 330 kV transmission line built to a 500 kV design between Bannaby and the new South Creek switching station. Transgrid's own PADR (Option 6) confirms a new 500 kV double circuit transmission line between Bannaby and South Western Sydney.</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -5643,7 +5646,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lines. Boundary/qualification: A single new line is described between Bannaby and South Creek; the other line works are rebuild and reconductoring of existing lines. Transgrid's own PADR (Option 6) likewise describes a single new 500 kV double circuit line commissioned from Bannaby to South Western Sydney.</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -5693,7 +5696,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr"/>
+      <c r="F84" s="5" t="n"/>
       <c r="G84" s="5" t="inlineStr">
         <is>
           <t>No archived source counts alternative routes. The count rests on the author's reading of PADR Figure 2.5 and on the Sydney Ring providing a 500 kV path north of Bannaby; shared South Creek and Sydney West interfaces mean geographic diversity is not equivalent to independent route security.</t>
@@ -5729,7 +5732,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="n"/>
       <c r="G85" s="6" t="inlineStr">
         <is>
           <t>No archived source states the presence or absence of synchronous condensers for this project; the now-archived PADR does not mention synchronous condensers either. The archived reactive plant is four 120 MVAr line shunt reactors.</t>
@@ -5765,7 +5768,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="n"/>
       <c r="G86" s="6" t="inlineStr">
         <is>
           <t>No archived source counts hubs for Sydney Ring South. AEMO records REZ N11 + N12 capacity of 2,000 MW attributed to the option but does not count connection hubs.</t>
@@ -5803,7 +5806,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4500 MVA (chart arithmetic, not unit count). Boundary/qualification: AEMO states the South Creek 330/500 kV upgrade includes three 1,500 MVA 500/330 kV transformers, corresponding to the chart's 4,500 MVA installed rating. The superseded 2024 alternative Option 2 had two 1,500 MVA units.</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -5853,7 +5856,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="n"/>
       <c r="G88" s="6" t="inlineStr">
         <is>
           <t>No archived source states hub-to-project feeder lines or their length for this project; the archived scope contains no feeder lines, but the absence is not stated as a quantity.</t>
@@ -5941,10 +5944,10 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr"/>
+      <c r="F90" s="5" t="n"/>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>No archived source states a NSW-only whole-project cost. The chart's 3.7 is half of a whole-interconnector amount, matched by the identical 3.7 in the VNI West (VIC) row. The only current whole-VNI figure is $7,600m ($2025, Class 4, two Dinawan transformers) per VNN-AO-2026-VNIWEST-TOTAL, which halves to 3.8, not 3.7; historical whole-VNI figures are VNN-AO-2024-VNIWEST-3499, VNN-AO-2024-VNIWEST-3614 and, from the AER, $3,963.6m ($Real 2022-23, VNN-AO-2024-AER-VNIWEST-TOTAL). The exact input the author halved is not reconstructible from the archive. The only NSW-specific approved amount now archived is the AER's stage 1 early works determination: Transgrid proposed $1,096.3 million ($Real 2022-23) for the New South Wales portion of the project (VNN-AO-2024-AER-CPA-PROPOSED), and the AER substituted $948.8 million ($Real 2022-23, VNN-AO-2024-AER-CPA-APPROVED). Both are a partial, stage 1 early works boundary, not the whole NSW component cost the chart cell implies, so neither resolves the chart's 3.7.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5991,7 +5994,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1800 MW. Boundary/qualification: AEMO 2026 states a +1,800 MW expansion of REZ transfer capacity from Dinawan, but only as the separately modelled N5 Option 2 third-transformer increment above the base N5 figure of 600 MW; it is not the NSW component's base capacity. AEMO 2020 separately reported +1,800 MW southward VIC-NSW transfer for the Kerang route, a different (whole-interconnector, superseded) boundary.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -6043,7 +6046,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>203 km. Boundary/qualification: PACR Table 6 (p48) gives an approximate NSW line length of 203 km for preferred Option 5A (184 km was Option 5, superseded). This is an indicative corridor-stage length between Dinawan and the WRL connection, not a built 500 kV trunk length as the chart defines it; no NSW-specific length is stated elsewhere.</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -6093,10 +6096,10 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="n"/>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Workbook ratio of the chart's own cost and trunk cells (3.7 billion / 240 km). The cost cell is an author split with no NSW-only whole-project figure archived (see cost_aud_billion), and the trunk cell's only archived figure (184 km, a PACR cost-estimating assumption, not the chart's boundary) does not match the chart's 240 km, so the ratio cannot be validated against any archived source.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr"/>
@@ -6131,7 +6134,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: AEMO 2026 describes upgrading the existing Dinawan - Wagga Wagga - Gugaa double-circuit line from 330 kV to 500 kV operation with a bypass at Wagga Wagga. Two circuits are therefore uprated existing circuits (built at 500 kV under Project EnergyConnect and HumeLink), not new-build circuits.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -6183,7 +6186,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lines. Boundary/qualification: The NSW component's line scope is the single Dinawan - Wagga Wagga - Gugaa double-circuit corridor, plus a Gugaa cut-in and a rebuild of a section of line TL51 between Gugaa and Wagga on the existing easement, which the source does not count as lines.</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -6233,7 +6236,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="n"/>
       <c r="G96" s="5" t="inlineStr">
         <is>
           <t>Alternative-route counting is an author definition no source supplies. AEMO 2020 did present Shepparton and Kerang route alternatives for VNI West, and the current route was selected as option 5A in the May 2023 RIT-T, so a zero depends entirely on the author's definition of a live alternative.</t>
@@ -6277,7 +6280,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr"/>
+      <c r="F97" s="6" t="n"/>
       <c r="G97" s="6" t="inlineStr">
         <is>
           <t>No archived source states a synchronous condenser rating for the South West NSW REZ component. The 2026 scope list names 500 kV line shunt reactors and reactor reconfiguration but no synchronous condensers, which is not a stated zero.</t>
@@ -6313,7 +6316,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr"/>
+      <c r="F98" s="5" t="n"/>
       <c r="G98" s="5" t="inlineStr">
         <is>
           <t>No source calls any NSW element a hub. The Dinawan 500 kV switchyard is a switchyard with 500/330 kV transformers and line reactors; the source does not describe it as a REZ hosting hub, so counting it as one hub is an author definition.</t>
@@ -6359,7 +6362,7 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>3 × 1,500 MVA per Dinawan transformer in N5 scope; only 2 units included in reported VNI cost; third separately modelled; no silent total</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -6409,7 +6412,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr"/>
+      <c r="F100" s="6" t="n"/>
       <c r="G100" s="6" t="inlineStr">
         <is>
           <t>No archived source states a feeder-line length for the South West NSW REZ component, and the sources do not use a feeder-line category, so the zero is neither supported nor contradicted.</t>
@@ -6497,14 +6500,10 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
+      <c r="F102" s="5" t="n"/>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>No source states $3.7bn for VNI West. The chart value equals half of the 2026 ISP reported $7,600m ($2025, Class 4 -30%/+50%) for 'South West NSW REZ + Interconnector' (VNV-AO-2026-REPORTED-TOTAL), split evenly across the VIC and NSW chart rows. AEMO publishes no Victoria/NSW allocation; the 2024 observations ($3,499m in 2020-21 dollars inclusive of $315m WRL, VNV-AO-2024-ISP-OPT1-COST; $3,614m modelling conversion, VNV-AO-2024-ISP-MODELLING) are also whole-interconnector and not comparable. The PACR (now archived) does state a Victoria/NSW split for its own May 2023 Option 5A estimate ($1,755m Victoria / $1,744m New South Wales, FY2020-21 dollars, VNV-AO-2023-PACR-COST) and the PADR similarly splits its superseded Option 1 estimate ($1,605m Victoria / $1,651m New South Wales, VNV-AO-2022-PADR-COST). These are captured as observations but are not used to construct a Victoria-only chart headline: they are a different vintage, price basis and RIT-T scope than the 2026 ISP's $7,600m reported total, and AEMO's current reporting still bundles 'South West NSW REZ + Interconnector' as one figure with no allocation of its own.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -6551,7 +6550,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.89 GW. Boundary/qualification: No source states a single 1.8 GW capacity for VNI West. The 2026 ISP states directional additional network capacity for the VIC-NSW component: forward 1,890 MW and reverse 1,670 MW, plus REZ V1 1,580 MW and WV2 200 MW. The only 1,800 MW in the sources is the separate third-Dinawan-transformer REZ expansion (VNV-AO-2026-CAP-THIRD-TF), a different boundary.</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -6603,7 +6602,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>206 km. Boundary/qualification: The 2023 PACR (Table 6, p48) states an approximate indicative line length of 206 km for the Victorian portion of the preferred Option 5A route (between EnergyConnect at Dinawan and the WRL connection point), with 203 km for the New South Wales portion; a route has not yet been determined and the figure is taken as the centre of the area of interest. This is a state-portion boundary, not the chart's implied whole-project trunk length, and belongs to a different (2023, FY2020-21 dollars) vintage than the 2026 ISP figures used elsewhere on this row. The PADR's earlier, superseded Option 1 route (via Bendigo) was approximately 400 km whole-route with no state split stated.</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6653,10 +6652,10 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="n"/>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>The trunk_km gap is now closed with a Victorian-portion length (206 km, PACR Table 6), but the numerator remains unusable: the chart's cost cell is a derived half of a whole-interconnector figure and no archived source states a Victoria-only cost for the current (2026 ISP) reported total that this pack treats as authoritative (see the cost_aud_billion finding and the AUTHOR_DECISION_REQUIRED warning on Victoria/NSW cost allocation). The ratio cannot be computed without constructing a Victoria-only cost, which this pack does not do.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr"/>
@@ -6691,7 +6690,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: The 2026 ISP describes a new 500 kV double-circuit overhead line from near Bulgana to Tragowel (near Kerang) to Dinawan; the 2024 ISP describes the same double-circuit configuration. The 2023 s16Y Ministerial Order (Schedule 1, the earliest statutory specification of the preferred option) already specified the same new 500 kV double-circuit overhead line from a new terminal station near Kerang to Dinawan and to Bulgana Terminal Station.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6743,7 +6742,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lines. Boundary/qualification: The 2026 ISP describes one new 500 kV double-circuit line on the Bulgana - Tragowel - Dinawan corridor. The 2023 s16Y Ministerial Order (Schedule 1) specifies the same single new line as the VNI West preferred option; no route length is stated in either.</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -6793,7 +6792,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr"/>
+      <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="inlineStr">
         <is>
           <t>Alternative-route counting is an author definition; no archived source counts 'alternative routes' the way the chart cell implies. The PADR and PACR are now archived and do describe multiple credible options: the PADR assessed Option 1 (VNI West, preferred, via Bendigo) against Option 2 (a Victorian Transmission Link brought forward ahead of VNI West); the Additional Consultation Report and PACR assessed Option 5, Option 5A (preferred) and two sensitivities (Option 5A westerly sensitivity; Option 5 without series compensation), with Options 1, 3 and 3A considered and not progressed. None of this constitutes a stated 'alt_routes' count for the chart's purposes.</t>
@@ -6837,7 +6836,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr"/>
+      <c r="F109" s="6" t="n"/>
       <c r="G109" s="6" t="inlineStr">
         <is>
           <t>No archived source states synchronous condenser MVA for VNI West. The itemised 2026 scope lists series compensation, 500 kV line shunt reactors and up to +/- 400 MVAr dynamic reactive compensation at Tragowel instead (VNV-AO-2026-REACTIVE); absence from a scope list is not a stated value.</t>
@@ -6881,7 +6880,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr"/>
+      <c r="F110" s="5" t="n"/>
       <c r="G110" s="5" t="inlineStr">
         <is>
           <t>Sources do not count hubs. The 2026 scope names a new Tragowel Terminal Station (Victoria), a terminal station near Bulgana and the Dinawan 500 kV switchyard (NSW); counting one hub for the Victorian row is an author allocation.</t>
@@ -6927,7 +6926,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2 × 1,000 MVA per Tragowel transformer; excludes Dinawan units; chart 2,000 MVA is author arithmetic, not a source-stated total</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -6977,7 +6976,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr"/>
+      <c r="F112" s="6" t="n"/>
       <c r="G112" s="6" t="inlineStr">
         <is>
           <t>No archived source states feeder or connection line lengths. The 2026 scope mentions 220 kV connections from the new Tragowel Terminal Station to the existing 220 kV lines near Kerang without any length.</t>
@@ -7065,14 +7064,10 @@
           <t>supported_with_boundary</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
+      <c r="F114" s="5" t="n"/>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>No archived source states a WRL cost of $1.6 billion, or any standalone WRL estimate. The only archived WRL-specific amount is $315 million in 2020-21 (FY2020-21) dollars, stated by AEMO 2024 as included within the VNI West quoted project cost of $3,499 million - a different boundary, price basis and date. The now-archived joint VNI West PACR (VNV-TRANSGRID-2023-PACR, the primary source AEMO's 2024 summary draws on) independently states the same $315 million WRL incremental cost, itemised separately as 'Included cost' within both the Option 5 ($3,406m) and Option 5A ($3,499m) all-states totals, and describes it as the direct cost of modifying WRL so it can connect VNI West at Bulgana. supported_value is in AUD million, not the chart's AUD billion; no conversion is asserted. Both AEMO project tables leave WRL's reported/expected cost blank. See SOURCE_UNAVAILABLE warnings for the 2019 PACR, VicGrid/NEVA and the AusNet cost update, and the AUTHOR_DECISION_REQUIRED note on the chart's $1.6 billion figure's likely origin.</t>
+          <t>No archived source states a WRL cost of $1.6 billion, or any standalone WRL estimate. The only archived WRL-specific amount is $315 million in 2020-21 (FY2020-21) dollars, stated by AEMO 2024 as included within the VNI West quoted project cost of $3,499 million - a different boundary, price basis and date. The now-archived joint VNI West PACR (VNV-TRANSGRID-2023-PACR, the primary source AEMO's 2024 summary draws on) independently states the same $315 million WRL incremental cost, itemised separately as 'Included cost' within both the Option 5 ($3,406m) and Option 5A ($3,499m) all-states totals, and describes it as the direct cost of modifying WRL so it can connect VNI West at Bulgana. No standalone replacement is established; $315m is the included WRL modification increment, not standalone WRL capex. Both AEMO project tables leave WRL's reported/expected cost blank. See SOURCE_UNAVAILABLE warnings for the 2019 PACR, VicGrid/NEVA and the AusNet cost update, and the AUTHOR_DECISION_REQUIRED note on the chart's $1.6 billion figure's likely origin.</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -7119,12 +7114,12 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>More than 3,000 MW proponent carrying capability, undefined basis; not exactly 3 GW guaranteed transfer</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>AusNet states WRL is 'Capable of carrying more than 3,000MW of energy' - a proponent capability lower bound on an undefined basis, matching the chart's 3 GW in magnitude only. AEMO's project-specific figures are different quantities: 1,460 MW renewable capacity harnessed, 695 MW additional MEL-WNV network capacity and V2 310 MW. supported_value is in MW. The 2023 s16Y Ministerial Order (VNV-VIC-GAZETTE-2023-S267) states only qualitative benefits for WRL ('alleviating network constraints and increasing hosting capacity in Victoria's west') and states no WRL capacity figure of any kind.</t>
+          <t>AusNet states WRL is 'Capable of carrying more than 3,000MW of energy' - a proponent capability lower bound on an undefined basis, matching the chart's 3 GW in magnitude only. AEMO's project-specific figures are different quantities: 1,460 MW renewable capacity harnessed, 695 MW additional MEL-WNV network capacity and V2 310 MW. The lower bound and capability definition must be retained. The 2023 s16Y Ministerial Order (VNV-VIC-GAZETTE-2023-S267) states only qualitative benefits for WRL ('alleviating network constraints and increasing hosting capacity in Victoria's west') and states no WRL capacity figure of any kind.</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -7171,7 +7166,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>190 km. Boundary/qualification: AusNet describes WRL as a proposed new 190 kilometre overhead line from Bulgana to Sydenham, the same trunk the chart measures. Neither AEMO ISP appendix states a route length.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -7221,7 +7216,7 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr"/>
+      <c r="F117" s="5" t="n"/>
       <c r="G117" s="5" t="inlineStr">
         <is>
           <t>Chart calculation: $1.6 billion divided by 190 km. The length input is supported (WRL-AO-2026-TRUNK-190KM) but the cost input is not: no archived source states $1.6 billion for WRL, so this ratio inherits an unsupported numerator. See CHART_DERIVATION warning.</t>
@@ -7267,7 +7262,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 circuits. Boundary/qualification: AEMO 2026 describes a planned 500 kV double-circuit overhead line from Bulgana to Sydenham, and the delivery scope specifies switched shunt line reactors at the end of each circuit. The 2023 s16Y Ministerial Order's Schedule 2 (VNV-VIC-GAZETTE-2023-S267), the legal instrument specifying the WRL Uprate, independently corroborates this: a new 500 kV double-circuit SYTS-BGTS line with switched shunt line reactors at the end of each circuit.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -7319,7 +7314,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 lines. Boundary/qualification: AEMO 2026 delivery scope states a single new transmission line: 'A new 500 kV double-circuit transmission line from Sydenham Terminal Station to Bulgana Terminal Station'. The 2023 s16Y Ministerial Order's Schedule 2 (VNV-VIC-GAZETTE-2023-S267) independently specifies the same single new line, SYTS to BGTS, as the WRL Uprate augmentation.</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -7369,7 +7364,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr"/>
+      <c r="F120" s="5" t="n"/>
       <c r="G120" s="5" t="inlineStr">
         <is>
           <t>Author definition. No archived source counts alternative routes for WRL. The 2019 RIT-T option set and the WRL EES route alternatives are unarchived, so a zero cannot be evidenced either way.</t>
@@ -7405,7 +7400,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr"/>
+      <c r="F121" s="6" t="n"/>
       <c r="G121" s="6" t="inlineStr">
         <is>
           <t>No archived source states a synchronous condenser rating for WRL, and none states that WRL includes no synchronous condensers. The AEMO 2026 delivery scope enumerates reactive plant as shunt line reactors (approximately 70 MVAr per circuit) and a 100 MVAr 500 kV switched bus reactor at Sydenham only; absence from an enumerated list is not a sourced zero. See AUTHOR_DECISION_REQUIRED.</t>
@@ -7449,7 +7444,7 @@
           <t>judgment</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr"/>
+      <c r="F122" s="5" t="n"/>
       <c r="G122" s="5" t="inlineStr">
         <is>
           <t>Author definition. No archived source counts hubs. The 2026 delivery scope names works at Bulgana Terminal Station (new 500 kV switchyard), Sydenham Terminal Station (extension, bays, bus reactor) and Elaine Terminal Station (cut-ins and realignment), plus minor augmentations at unnamed existing terminals, so a hub count of 1 reflects an author boundary choice. Bulgana is a shared WRL / VNI West terminal; see SHARED_ATTRIBUTION. The 2023 s16Y Ministerial Order's Schedule 2 (VNV-VIC-GAZETTE-2023-S267) names a fourth WRL terminal not enumerated in AEMO's 2024/2026 delivery scope summaries: Ballarat Terminal Station (BATS), where new 220 kV circuit breakers establish double switching on the existing bays. A hub count of 1 therefore also excludes a fourth, order-specified terminal.</t>
@@ -7493,7 +7488,7 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr"/>
+      <c r="F123" s="5" t="n"/>
       <c r="G123" s="5" t="inlineStr">
         <is>
           <t>Chart calculation: the sum of two 1,000 MVA units. AEMO 2026 states a new 500 kV switchyard at Bulgana Terminal Station with two new 500/220 kV 1,000 MVA transformers (WRL-AO-2026-TRANSFORMERS-1000; 2024 equivalent WRL-AO-2024-TRANSFORMERS-1000). The per-unit rating is preserved rather than summed in observations. These transformers sit at the shared Bulgana terminal; see SHARED_ATTRIBUTION. The 2023 s16Y Ministerial Order's Schedule 2 (VNV-VIC-GAZETTE-2023-S267), the legal instrument specifying the WRL Uprate, independently states the same two 500/220 kV 1,000 MVA transformers at the new Bulgana switchyard (WRL-AO-2023-TRANSFORMERS-1000).</t>
@@ -7541,7 +7536,7 @@
           <t>gap</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr"/>
+      <c r="F124" s="6" t="n"/>
       <c r="G124" s="6" t="inlineStr">
         <is>
           <t>No archived source states feeder line lengths for WRL. The 2026 delivery scope describes cut-ins and realignments of existing 220 kV lines at Elaine and Bulgana without stating any length.</t>
@@ -7612,6 +7607,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7765,7 +7761,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>Publishable only with corrections: the cost and millions-per-trunk-km cells are non-additive author aggregates, the date cell is contradicted by every archived timing, and the hubs, circuits, transformers and alt-routes cells are author derivations or judgments rather than sourced values.</t>
+          <t>Publishable only with corrections: the cost and millions-per-trunk-km cells are non-additive author aggregates, the date cell requires a defined milestone and the feeder length has an unresolved source discrepancy, and the hubs, circuits, transformers and alt-routes cells are author derivations or judgments rather than sourced values.</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -7952,7 +7948,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>One provisional Project Marinus; Stage 1 and Stage 2 are separate components/versions pending lifecycle review.</t>
+          <t>Project Marinus comprises Marinus Link (HVDC interconnector) and TasNetworks NWTD (HVAC network works); Stage 1 and Stage 2 and Option 2/2A are distinct scope/version boundaries.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -7994,12 +7990,12 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Published amounts are discrete observations with different scope, price, maturity and sunk-cost treatment. They do not establish a simple cost-overrun series or one reconciled current total.</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex.</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>The row should not be published as-is: the cost and capacity cells are contradicted by archived sources, the length and ratio cells are derivations under a definition Marinus does not meet, and five topology cells are gaps or author judgments.</t>
+          <t>The cost replacement is unresolved on a Link-only boundary; two-link nameplate capacity is 1.5 GW, contradicting 1.4 GW. Length and ratio remain author derivations; topology gaps remain.</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -8158,12 +8154,12 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>There is no archived reconciled whole-project cost for Project EnergyConnect. The AER approved two separate owner allowances, $457.4m ($2017-18) for ElectraNet and $1,817.9m ($2017-18) for TransGrid, and described the project as a proposed $2.3 billion ($2017-18) contingent project. TransGrid's February 2026 reopener application, citing Contract Failure, now states a forecast cost of $3,628 million (real 2022-23) to complete TransGrid's own NSW component - a proponent forecast, not an AER-approved amount, and not stated to include ElectraNet's SA works. The chart's $4.1 billion still matches only Transgrid's separate social-value claim, a benefit measure, and the chart's 160 km now has an exact but different match: Transgrid's June 2026 completion release states Stage 1 (SA border to Buronga and into Victoria) is 160 km, distinct from the 165 km Dinawan-Wagga Wagga section and from the 900 km whole-route figure both Transgrid's page and the joint ElectraNet/Transgrid project page state. Cost, capacity, trunk km, syncons, transformers and feeder km all fail on the chart's boundaries.</t>
+          <t>There is no archived reconciled whole-project cost for Project EnergyConnect. The AER approved two separate owner allowances, $457.4m ($2017-18) for ElectraNet and $1,817.9m ($2017-18) for TransGrid, and described the project as a proposed $2.3 billion ($2017-18) contingent project. TransGrid's February 2026 reopener application, citing Contract Failure, now states a forecast cost of $3,628 million (real 2022-23) to complete TransGrid's own NSW component - a proponent forecast, not an AER-approved amount, and not stated to include ElectraNet's SA works. The chart's $4.1 billion still matches only Transgrid's separate social-value claim, a benefit measure, and the chart's 160 km now has an exact but different match: Transgrid's June 2026 completion release states Stage 1 (SA border to Buronga and into Victoria) is 160 km, distinct from the 165 km Dinawan-Wagga Wagga section and from the 900 km whole-route figure both Transgrid's page and the joint ElectraNet/Transgrid project page state. Cost, capacity, trunk km, syncons and transformers require the stated boundary corrections; line and feeder interpretations depend on explicit chart definitions.</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Not publishable as-is: the cost cell rests on a social-value figure rather than capital expenditure, and the closest capital-cost figure archived - TransGrid's own $3,628m (real 2022-23) February 2026 reopener forecast - is a proponent application on a different boundary and basis, not an approved amount. The trunk length now matches a sourced 160 km Stage 1 section exactly, but that is one section of a nine-hundred-kilometre project, and the capacity, syncon, transformer and feeder cells are contradicted by the archived scope.</t>
+          <t>Not publishable as-is: the cost cell rests on a social-value figure rather than capital expenditure, and the closest capital-cost figure archived - TransGrid's own $3,628m (real 2022-23) February 2026 reopener forecast - is a proponent application on a different boundary and basis, not an approved amount. The trunk length now matches a sourced 160 km Stage 1 section exactly, but that is one section of a nine-hundred-kilometre project, and the capacity, syncon and transformer cells conflict on stated source boundaries; line and feeder counts require explicit definitions.</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -8240,12 +8236,12 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>The archived record supports the topology, capacity and transformer figures. Transgrid's own PADR is now archived and directly states Option 6's total capital cost as $3,519 million (nominal), staged $1,135 million then $2,384 million; this confirms AEMO's secondhand quotation and shows the chart's $3.510 billion is a transcription of $3,519 million, not a separate basis. The chart's 114 km matches Transgrid's archived 2023 preparatory estimate for the Bannaby-South Creek line, but the archived 2026 PADR instead describes the (now differently scoped) line as extending to around 100 km.</t>
+          <t>The immutable chart contains $3.5bn, consistent with rounding the PADR Option 6 total of $3,519m nominal to one decimal billion. The source gives Stage 1 $1,135m and Stage 2 $2,384m, P50 Class 5 (+100%/-50%). AEMO's $2,621m modelled $2025 amount is a different price basis. No transcription error is established (PADR p38; AEMO 2026 p43). 30.70175438596491 = 3,500 AUD million / 114 km, using the original chart inputs. The $3.5bn rounds the $3,519m nominal Option 6 estimate; the 114 km is the older 2023 preparatory route, whereas the 2026 PADR describes approximately 100 km on a revised scope. This mixed-vintage ratio is not a reconciled source-defined construction cost per km (2023 preparatory p8; PADR pp38,43).</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>Topology, capacity, circuits, lines and transformer cells are supported by the archived 2026 ISP and, for capacity, circuits and lines, corroborated directly by Transgrid's now-archived PADR; the cost cell is contradicted because the chart's $3.510bn does not match either archived total ($2,621m AEMO-modelled or $3,519m PADR Option 6, of which $3.510bn is a transcription); trunk_km is supported with a boundary caveat (2023 preparatory 114 km vs the PADR's newer ~100 km), and the millions-per-trunk-km ratio still rests on the chart's unverified 3,510 figure, so the row should not be published as-is.</t>
+          <t>Cost supported with rounding and price-basis qualifications. Topology, capacity and transformer evidence retained; 114 km preparatory versus approximately 100 km PADR scope remains unreconciled. 30.70175438596491 = 3,500 AUD million / 114 km, using the original chart inputs. The $3.5bn rounds the $3,519m nominal Option 6 estimate; the 114 km is the older 2023 preparatory route, whereas the 2026 PADR describes approximately 100 km on a revised scope. This mixed-vintage ratio is not a reconciled source-defined construction cost per km (2023 preparatory p8; PADR pp38,43).</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -8322,12 +8318,12 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Every archived monetary figure is a whole-VNI West boundary ($7,600m 2026; $3,499m 2024 inclusive of WRL; $3,614m modelled). No archived source allocates a NSW share, so the chart's 3.7 is an author split of a whole-interconnector amount, not a sourced NSW cost.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>The row describes a NSW half of a project whose archived cost, capacity and timing evidence exists only at whole-interconnector or conditional-option boundaries, so its headline cost is an author split, its transformer rating is contradicted, and its route, syncon and feeder cells are unsupported.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -8552,6 +8548,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -8725,7 +8722,7 @@
           <t>Cost $450 million to $850 million</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="inlineStr">
         <is>
           <t>The 2020 ISP project table states no dollar year for this estimate. PRICE_BASIS_UNKNOWN warning applies.</t>
@@ -8808,7 +8805,7 @@
           <t>Cost $450 million to $850 million</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated in the project table.</t>
@@ -8891,7 +8888,7 @@
           <t>[$650 million]</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="inlineStr">
         <is>
           <t>Table 2 shows 'Cost range [ISP modelled cost]'. Price basis not stated.</t>
@@ -8982,7 +8979,7 @@
           <t>Construction cost preliminary estimate $3.2 billion $0.8 billion $1.3 billion</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="inlineStr">
         <is>
           <t>Same line states Secure Now $0.8 billion and Plan for the Future $1.3 billion.</t>
@@ -9073,7 +9070,7 @@
           <t>4,500 3,186 0.71 September</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="inlineStr">
         <is>
           <t>Table 1 row reads additional capacity 4,500 MW, total cost $3,186m, $0.71/MW. The same row records system strength remediation as 'Included as part of network build', which conflicts with the strategy's stated exclusion.</t>
@@ -9164,7 +9161,7 @@
           <t>Construction cost preliminary estimate $3.2 billion $0.8 billion $1.3 billion</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -9251,7 +9248,7 @@
           <t>Construction cost preliminary estimate $3.2 billion $0.8 billion $1.3 billion</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -9338,7 +9335,7 @@
           <t>3,000 324 0.11 March</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="inlineStr">
         <is>
           <t>Source note: Hunter Transmission Project required above 3 GW total network capacity; its cost is not included. Strategy text says Option 2B is limited to 1.5 GW until downstream augmentation.</t>
@@ -9425,7 +9422,7 @@
           <t>REZ is expected be around $5.45 billion (nominal value, adjusted for inflation) for recommendation</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="n"/>
       <c r="S13" s="4" t="inlineStr">
         <is>
           <t>Already includes the Enabling works; do not add the 2026 Enabling determination to this figure.</t>
@@ -9599,7 +9596,7 @@
           <t>following our adjustment decision, as calculated by EnergyCo. This is a reduction of $173.2m</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="inlineStr">
         <is>
           <t>The initial determination's own NER-equivalent total is not published in either archived AER report; $5,699.3m appears only as an arithmetic complement and is not recorded here as a sourced observation.</t>
@@ -9682,7 +9679,7 @@
           <t>Project with total capital expenditure (capex) of $437.9 million ($2025–26) and proposed total</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -9761,7 +9758,7 @@
           <t>Project with total capital expenditure (capex) of $437.9 million ($2025–26) and proposed total</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="inlineStr">
         <is>
           <t>Excerpt line continues 'revenue of $165.1 million ($ nominal) over the 2026-31 period.' Recorded to prevent revenue/capex conflation.</t>
@@ -9844,7 +9841,7 @@
           <t>Our final decision is to provide an alternative capex estimate of $402.8 million ($2025–26).</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="inlineStr">
         <is>
           <t>PDF page 50 is printed page 46.</t>
@@ -9927,7 +9924,7 @@
           <t>Total capex - 284.4 108.1 13.5 - - 406.0</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="inlineStr">
         <is>
           <t>Table 9.2, PDF page 50 (printed page 46), matching the author's citation.</t>
@@ -10010,7 +10007,7 @@
           <t>• excluding $8.2 million of pre-period costs for early development activities incurred prior to</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -10085,7 +10082,7 @@
           <t>$186.8 million) and then energise and commission the asset.</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="inlineStr">
         <is>
           <t>Adjustable through the 'BCSS Purchase Price Adjustment' mechanism; costs to enter a future revenue determination. Dollar basis not stated. PRICE_BASIS_UNKNOWN warning applies.</t>
@@ -10172,7 +10169,7 @@
           <t>1,500 855</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="n"/>
       <c r="S22" s="4" t="inlineStr">
         <is>
           <t>Table row reads additional network capacity 1,500 MW and reported cost 855 ($ million), followed by 'Class 5b (±50%)'. The project entry does not state a dollar year. PRICE_BASIS_UNKNOWN warning applies.</t>
@@ -10255,7 +10252,7 @@
           <t>H2P FeeQ $1,524,456.88 per Calendar Quarter</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="inlineStr">
         <is>
           <t>Project-specific H2P capex inputs are redacted. Payment term stated as 124 quarters at PDF page 6.</t>
@@ -10338,7 +10335,7 @@
           <t>CSS FeeQ $3,090.84/MW</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="n"/>
       <c r="S24" s="4" t="inlineStr">
         <is>
           <t>Formula: Access FeeQ=(((C&amp;E FeeQ+ Non C&amp;E FeeQ + CSS FeeQ ) x Maximum Capacity) + H2P FeeQ ) x Fixed Indexation (CWO-13, PDF p7).</t>
@@ -10417,7 +10414,7 @@
           <t>Additional REZ hosting capacity Central West NSW: +3,000 MW</t>
         </is>
       </c>
-      <c r="R25" s="4" t="inlineStr"/>
+      <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
@@ -10492,7 +10489,7 @@
           <t>energy zone is 3 gigawatts.</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
@@ -10650,7 +10647,7 @@
           <t>• Deliver Now. 4.5 GW capacity by 2027/2028,</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
@@ -10725,7 +10722,7 @@
           <t>• Secure Now. An additional 2.3 GW</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="n"/>
       <c r="S29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
@@ -10800,7 +10797,7 @@
           <t>• Central-West Orana REZ: add 3.5 GW of network</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -10875,7 +10872,7 @@
           <t>transfer capacity of the access rights network has been made  at 4.5 GW</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="inlineStr">
         <is>
           <t>The determination document itself (CWO-16) has no usable text derivative; the value is cited from the headroom decision that recites it, and matches CWO-10 PDF p2 and CWO-18 PDF p11.</t>
@@ -10954,7 +10951,7 @@
           <t>Wollar to Elong Elong via Merotherie. It is designed to initially deliver 4.5 GW of network</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="inlineStr">
         <is>
           <t>Footnote 36 states network capacity is planned to be increased to 6 GW by 2038.</t>
@@ -11033,7 +11030,7 @@
           <t>capacity 36 and support up to 7.7 GW of generation.</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr"/>
+      <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -11108,7 +11105,7 @@
           <t>• Previous aggregate maximum capacity cap: 5.84 GW</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="n"/>
       <c r="S34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -11183,7 +11180,7 @@
           <t>• New aggregate maximum capacity cap: 7.7 GW</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr"/>
+      <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -11258,7 +11255,7 @@
           <t>begun in June 202534 towards energisation in 2028. EnergyCo have awarded 7.15 GW of generation and storage projects</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr"/>
+      <c r="R36" s="4" t="n"/>
       <c r="S36" s="4" t="inlineStr">
         <is>
           <t>Same sentence gives 7.7 GW as the current aggregate maximum capacity.</t>
@@ -11337,7 +11334,7 @@
           <t>EnergyCo has awarded 7.7 GW of generation and storage projects under its access rights scheme112.</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr"/>
+      <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
@@ -11412,7 +11409,7 @@
           <t>1,500 855</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr"/>
+      <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
@@ -11487,7 +11484,7 @@
           <t>approximately 900 MW, which will increase by 4,500 MW once Central-West Orana REZ is established.</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr"/>
+      <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
@@ -11645,7 +11642,11 @@
           <t>cover a corridor of around 150 km.</t>
         </is>
       </c>
-      <c r="R41" s="4" t="inlineStr"/>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
           <t>The author cited the ACEREZ website (not archived) for the feeder length; the AER states it directly.</t>
@@ -11803,7 +11804,7 @@
           <t>comprising two 500 kV double circuit lines,</t>
         </is>
       </c>
-      <c r="R43" s="4" t="inlineStr"/>
+      <c r="R43" s="4" t="n"/>
       <c r="S43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
@@ -11957,7 +11958,7 @@
           <t>Seven 250 MVA synchronous condenser</t>
         </is>
       </c>
-      <c r="R45" s="4" t="inlineStr"/>
+      <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="inlineStr">
         <is>
           <t>EnergyCo's 2024 recommendation states 'a system strength solution for an installed 1,750 MVA' (CWO-09, PDF p10).</t>
@@ -12036,7 +12037,7 @@
           <t>System strength infrastructure, which includes a system strength solution for an installed 1,750</t>
         </is>
       </c>
-      <c r="R46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
@@ -12194,7 +12195,7 @@
           <t>• New Merotherie 500/330 kV substation with 4 x 500/330/33 kV 1,500 MVA</t>
         </is>
       </c>
-      <c r="R48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
@@ -12269,7 +12270,7 @@
           <t>• Construct Merotherie-B 500/330 kV substation with 3 x 500/330/33 kV 1,500</t>
         </is>
       </c>
-      <c r="R49" s="4" t="inlineStr"/>
+      <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
@@ -12344,7 +12345,7 @@
           <t>• Expand Elong Elong as 500/330 kV substation with 3 x 500/330/33 kV 1,500 MVA</t>
         </is>
       </c>
-      <c r="R50" s="4" t="inlineStr"/>
+      <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
@@ -12419,7 +12420,7 @@
           <t>• two 500 kV double circuits between Wollar and</t>
         </is>
       </c>
-      <c r="R51" s="4" t="inlineStr"/>
+      <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
@@ -12494,7 +12495,7 @@
           <t>(a) A 500 kV transmission network from Wollar</t>
         </is>
       </c>
-      <c r="R52" s="4" t="inlineStr"/>
+      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
@@ -12571,7 +12572,7 @@
           <t>Timing Central-West Orana REZ Transmission Link is an actionable project and is timed for 2024-25.</t>
         </is>
       </c>
-      <c r="R53" s="4" t="inlineStr"/>
+      <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
@@ -12648,7 +12649,7 @@
           <t>Construction of the Central-West Orana RNIP is expected to begin in early 2025 and be completed</t>
         </is>
       </c>
-      <c r="R54" s="4" t="inlineStr"/>
+      <c r="R54" s="4" t="n"/>
       <c r="S54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
@@ -12725,7 +12726,7 @@
           <t>paid to ACEREZ.37 Infrastructure completion will be staged between April 2028 and</t>
         </is>
       </c>
-      <c r="R55" s="4" t="inlineStr"/>
+      <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
@@ -12887,7 +12888,7 @@
           <t>March 2033</t>
         </is>
       </c>
-      <c r="R57" s="4" t="inlineStr"/>
+      <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
@@ -12967,7 +12968,7 @@
 double circuit lines at an operating voltage of 500kV</t>
         </is>
       </c>
-      <c r="R58" s="4" t="inlineStr"/>
+      <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="inlineStr">
         <is>
           <t>ASL statement of reasons section 3.2, describing the Main project scope underlying the 2024 Notice of Authorisation (CWO-10).</t>
@@ -13051,7 +13052,7 @@
 double circuit lines at an operating voltage of 330 kV</t>
         </is>
       </c>
-      <c r="R59" s="4" t="inlineStr"/>
+      <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
@@ -13127,7 +13128,7 @@
 double circuit lines at an operating voltage of 500kV</t>
         </is>
       </c>
-      <c r="R60" s="4" t="inlineStr"/>
+      <c r="R60" s="4" t="n"/>
       <c r="S60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
@@ -13188,7 +13189,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Contradicts the AER's 'around 150 km' H2P corridor figure (CWO-AO-2025-H2P-150KM) for what appears to be the same hub-to-project network boundary; see CONTRADICTION warning</t>
+          <t>The chart's 150 km has positive support: CWO-18 p11 states a corridor of around 150 km and CWO-26 derivative line18 states 150 km of 330 kV generator-connection lines. CWO-23 p10 instead describes approximately 166 km of H2P lines, with conditional separable portions (pp12,19). Different vintages, corridor versus line measurement and conditional scope remain unreconciled. Retain an unresolved source discrepancy, not a same-boundary numerical disproof; five portions were excluded in 2025.</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -13207,7 +13208,7 @@
 of transmission lines (H2P Assets)</t>
         </is>
       </c>
-      <c r="R61" s="4" t="inlineStr"/>
+      <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
@@ -13283,7 +13284,7 @@
 for the remediation of the first 5.84 GW of IBR within the Central West Orana REZ</t>
         </is>
       </c>
-      <c r="R62" s="4" t="inlineStr"/>
+      <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="inlineStr">
         <is>
           <t>See CONTRADICTION warning on synchronous condenser unit rating.</t>
@@ -13363,7 +13364,7 @@
 Central West Orana REZ Stage 1 (5.84 GW of IBR) via ACEREZ</t>
         </is>
       </c>
-      <c r="R63" s="4" t="inlineStr"/>
+      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="inlineStr">
         <is>
           <t>Section 2.3.5.1 'Central West Orana REZ Stage 1' at PDF p31 gives the full detail underlying this summary bullet; see CWO-AO-2025-SYNCON-CWO24-240MVA.</t>
@@ -13442,7 +13443,7 @@
           <t>The project consists of 90km of 500kV overhead transmission lines and 150 km of 330kV transmission lines for generator connections,</t>
         </is>
       </c>
-      <c r="R64" s="4" t="inlineStr"/>
+      <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="inlineStr">
         <is>
           <t>Unpaged web capture accessed 2026-09-04; the source page carries no publication date, so the observation date is recorded as the retrieval year.</t>
@@ -13503,7 +13504,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>States the same 150 km figure as the AER's 'around 150 km' H2P corridor (CWO-AO-2025-H2P-150KM), but contradicts the ASL statement of reasons' 166 km H2P total (CWO-AO-2024-H2P-166KM) for what appears to be the same generator-connection network boundary; see CONTRADICTION warning</t>
+          <t>The chart's 150 km has positive support: CWO-18 p11 states a corridor of around 150 km and CWO-26 derivative line18 states 150 km of 330 kV generator-connection lines. CWO-23 p10 instead describes approximately 166 km of H2P lines, with conditional separable portions (pp12,19). Different vintages, corridor versus line measurement and conditional scope remain unreconciled. Retain an unresolved source discrepancy, not a same-boundary numerical disproof; five portions were excluded in 2025.</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -13521,7 +13522,7 @@
           <t>150 km of 330kV transmission lines for generator connections, stretching from Elong Elong in the west through to Barigan Creek in the east, via an energy hub at Merotherie.</t>
         </is>
       </c>
-      <c r="R65" s="4" t="inlineStr"/>
+      <c r="R65" s="4" t="n"/>
       <c r="S65" s="4" t="inlineStr">
         <is>
           <t>Unpaged web capture accessed 2026-09-04.</t>
@@ -13602,7 +13603,7 @@
           <t>This Order commences on the date that it is published in the Gazette.</t>
         </is>
       </c>
-      <c r="R66" s="4" t="inlineStr"/>
+      <c r="R66" s="4" t="n"/>
       <c r="S66" s="4" t="inlineStr">
         <is>
           <t>The instrument's signature block ('Dated this ... 2022, Matthew Kean MP') has an illegible day/month in the archived text derivative; the order's own commencement clause ties into the Gazette's cover date instead. Resolves the prior SOURCE_UNAVAILABLE warning for this instrument.</t>
@@ -13683,7 +13684,7 @@
 initial CWO REZ Declaration, is 5.84GW.</t>
         </is>
       </c>
-      <c r="R67" s="4" t="inlineStr"/>
+      <c r="R67" s="4" t="n"/>
       <c r="S67" s="4" t="inlineStr">
         <is>
           <t>Clause 8(1) and clause 9(1) of the Order, PDF page 22 of the archived Gazette. Resolves the prior SOURCE_UNAVAILABLE warning for this instrument.</t>
@@ -13771,7 +13772,7 @@
 electricity network</t>
         </is>
       </c>
-      <c r="R68" s="4" t="inlineStr"/>
+      <c r="R68" s="4" t="n"/>
       <c r="S68" s="4" t="inlineStr">
         <is>
           <t>The consolidated approval's signature page reads 'Minister for Planning and Public Spaces / Sydney     2024' with no legible day or month in the archived text derivative; the December 2024 date is taken from the manifest's captured publication_date for this document. The approval already carries one modification (SSI-48323210-Mod-1, determined 14 October 2024, minor administrative changes).</t>
@@ -13854,7 +13855,7 @@
           <t>• Install a Wagga–Bannaby–Snowy2.0–Wagga single circuit 500 kV loop.</t>
         </is>
       </c>
-      <c r="R69" s="4" t="inlineStr"/>
+      <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="inlineStr">
         <is>
           <t>The 2018 documents do not state that all of SnowyLink later became HumeLink.</t>
@@ -13937,7 +13938,7 @@
           <t>The estimated capital cost of this option is approximately $1,350 million.</t>
         </is>
       </c>
-      <c r="R70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="inlineStr">
         <is>
           <t>Also stated at PDF pp. 4, 22 and 53. Price year not stated; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -14020,7 +14021,7 @@
           <t>additional 2,570 MW generation could be accommodated</t>
         </is>
       </c>
-      <c r="R71" s="4" t="inlineStr"/>
+      <c r="R71" s="4" t="n"/>
       <c r="S71" s="4" t="inlineStr">
         <is>
           <t>The PADR summary tables call the same number 'Additional firm capacity 2,570 MW' (PDF pp. 4, 22).</t>
@@ -14103,7 +14104,7 @@
           <t>Cost $1,470 million to $2,730 million</t>
         </is>
       </c>
-      <c r="R72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="inlineStr">
         <is>
           <t>Price year not stated; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -14186,7 +14187,7 @@
           <t>Cost $1,470 million to $2,730 million</t>
         </is>
       </c>
-      <c r="R73" s="4" t="inlineStr"/>
+      <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="inlineStr">
         <is>
           <t>Price year not stated; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -14269,7 +14270,7 @@
           <t>[$2,100 million]</t>
         </is>
       </c>
-      <c r="R74" s="4" t="inlineStr"/>
+      <c r="R74" s="4" t="n"/>
       <c r="S74" s="4" t="inlineStr">
         <is>
           <t>Published in the actionable-project table as '[ISP modelled cost]'. Price year not stated.</t>
@@ -14352,7 +14353,7 @@
           <t>Tumut to Sydney Transfer (at time of peak demand) 2,230 MW to 2,570 MW</t>
         </is>
       </c>
-      <c r="R75" s="4" t="inlineStr"/>
+      <c r="R75" s="4" t="n"/>
       <c r="S75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
@@ -14431,7 +14432,7 @@
           <t>Tumut to Sydney Transfer (at time of peak demand) 2,230 MW to 2,570 MW</t>
         </is>
       </c>
-      <c r="R76" s="4" t="inlineStr"/>
+      <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
@@ -14510,7 +14511,7 @@
           <t>Wagga Wagga: +1,000 MW</t>
         </is>
       </c>
-      <c r="R77" s="4" t="inlineStr"/>
+      <c r="R77" s="4" t="n"/>
       <c r="S77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
@@ -14589,7 +14590,7 @@
           <t>span a distance of approximately 630 km</t>
         </is>
       </c>
-      <c r="R78" s="4" t="inlineStr"/>
+      <c r="R78" s="4" t="n"/>
       <c r="S78" s="4" t="inlineStr">
         <is>
           <t>The PADR's Option 3C section lists section lengths of 260 km, 110 km and 260 km (PDF p. 27); no source performs that addition.</t>
@@ -14674,7 +14675,7 @@
           <t>Timing HumeLink is an actionable project and is timed for 2025-26 across all scenarios.</t>
         </is>
       </c>
-      <c r="R79" s="4" t="inlineStr"/>
+      <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
@@ -14761,7 +14762,7 @@
           <t>approximately $3,317 million ($2020/21)</t>
         </is>
       </c>
-      <c r="R80" s="4" t="inlineStr"/>
+      <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="inlineStr">
         <is>
           <t>Estimate class and P-value are confirmed in the December 2021 PACR addendum, PDF p. 5.</t>
@@ -14852,7 +14853,7 @@
           <t>Lines and substations: $2,380m</t>
         </is>
       </c>
-      <c r="R81" s="4" t="inlineStr"/>
+      <c r="R81" s="4" t="n"/>
       <c r="S81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
@@ -14939,7 +14940,7 @@
           <t>Biodiversity offset cost: $935m</t>
         </is>
       </c>
-      <c r="R82" s="4" t="inlineStr"/>
+      <c r="R82" s="4" t="n"/>
       <c r="S82" s="4" t="inlineStr">
         <is>
           <t>Transgrid's 1 September 2021 response to the AER states the estimated biodiversity costs for the preferred option 3C as $953m (RFI PDF p. 2); the two figures are not reconciled in the archive.</t>
@@ -15030,7 +15031,7 @@
           <t>estimated capital cost of $4,253 million</t>
         </is>
       </c>
-      <c r="R83" s="4" t="inlineStr"/>
+      <c r="R83" s="4" t="n"/>
       <c r="S83" s="4" t="inlineStr">
         <is>
           <t>Identified in the PACR as the 2020 ISP candidate option.</t>
@@ -15121,7 +15122,7 @@
           <t>capital cost of $3,509 million;</t>
         </is>
       </c>
-      <c r="R84" s="4" t="inlineStr"/>
+      <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
@@ -15204,7 +15205,7 @@
           <t>approximately $491 million in net benefits</t>
         </is>
       </c>
-      <c r="R85" s="4" t="inlineStr"/>
+      <c r="R85" s="4" t="n"/>
       <c r="S85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
@@ -15370,7 +15371,7 @@
           <t>Three new 500/330/33 kV 1,500 MVA transformers at Maragle substation and two new 500/330/33 kV 1,500 MVA transformers at new Wagga</t>
         </is>
       </c>
-      <c r="R87" s="4" t="inlineStr"/>
+      <c r="R87" s="4" t="n"/>
       <c r="S87" s="4" t="inlineStr">
         <is>
           <t>Count = 3. No archived source multiplies or sums these ratings.</t>
@@ -15453,7 +15454,7 @@
           <t>Three new 500/330/33 kV 1,500 MVA transformers at Maragle substation and two new 500/330/33 kV 1,500 MVA transformers at new Wagga</t>
         </is>
       </c>
-      <c r="R88" s="4" t="inlineStr"/>
+      <c r="R88" s="4" t="n"/>
       <c r="S88" s="4" t="inlineStr">
         <is>
           <t>Count = 2. No archived source multiplies or sums these ratings.</t>
@@ -15536,7 +15537,7 @@
           <t>additional 2,570 MW generation could be accommodated</t>
         </is>
       </c>
-      <c r="R89" s="4" t="inlineStr"/>
+      <c r="R89" s="4" t="n"/>
       <c r="S89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
@@ -15710,7 +15711,7 @@
           <t>The estimated capital cost of this option is approximately $2,695 million</t>
         </is>
       </c>
-      <c r="R91" s="4" t="inlineStr"/>
+      <c r="R91" s="4" t="n"/>
       <c r="S91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
@@ -15797,7 +15798,7 @@
           <t>which includes $858 million of</t>
         </is>
       </c>
-      <c r="R92" s="4" t="inlineStr"/>
+      <c r="R92" s="4" t="n"/>
       <c r="S92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
@@ -15876,7 +15877,7 @@
           <t>an additional 2,510 MW generation could be accommodated</t>
         </is>
       </c>
-      <c r="R93" s="4" t="inlineStr"/>
+      <c r="R93" s="4" t="n"/>
       <c r="S93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
@@ -15959,7 +15960,7 @@
           <t>estimate for the project is $3,317 million, which includes $330 million for early works.</t>
         </is>
       </c>
-      <c r="R94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="n"/>
       <c r="S94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
@@ -16042,7 +16043,7 @@
           <t>estimate for the project is $3,317 million, which includes $330 million for early works.</t>
         </is>
       </c>
-      <c r="R95" s="4" t="inlineStr"/>
+      <c r="R95" s="4" t="n"/>
       <c r="S95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
@@ -16125,7 +16126,7 @@
           <t>These costs are equivalent to $3.28 billion and $327.6 million in real 2017-18 dollars.</t>
         </is>
       </c>
-      <c r="R96" s="4" t="inlineStr"/>
+      <c r="R96" s="4" t="n"/>
       <c r="S96" s="4" t="inlineStr">
         <is>
           <t>Published as $3.28 billion.</t>
@@ -16212,7 +16213,7 @@
           <t>These costs are equivalent to $3.28 billion and $327.6 million in real 2017-18 dollars.</t>
         </is>
       </c>
-      <c r="R97" s="4" t="inlineStr"/>
+      <c r="R97" s="4" t="n"/>
       <c r="S97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
@@ -16295,7 +16296,7 @@
           <t>Transgrid’s application proposed $321.9 million ($2017-18) in forecast capex to undertake</t>
         </is>
       </c>
-      <c r="R98" s="4" t="inlineStr"/>
+      <c r="R98" s="4" t="n"/>
       <c r="S98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
@@ -16378,7 +16379,7 @@
           <t>$321.9 million ($2017-18) is a prudent</t>
         </is>
       </c>
-      <c r="R99" s="4" t="inlineStr"/>
+      <c r="R99" s="4" t="n"/>
       <c r="S99" s="4" t="inlineStr">
         <is>
           <t>The AER accepted Transgrid's proposed forecast capex and noted it is within AEMO's feedback-loop confirmation of $327.6 million.</t>
@@ -16465,7 +16466,7 @@
           <t>Table 6 shows Transgrid is to recover $71.4 million ($ nominal) in indicative additional</t>
         </is>
       </c>
-      <c r="R100" s="4" t="inlineStr"/>
+      <c r="R100" s="4" t="n"/>
       <c r="S100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
@@ -16544,7 +16545,7 @@
           <t>involves around 360 kilometres of new 500 kilovolts (kV) transmission lines, which will</t>
         </is>
       </c>
-      <c r="R101" s="4" t="inlineStr"/>
+      <c r="R101" s="4" t="n"/>
       <c r="S101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
@@ -16623,7 +16624,7 @@
           <t>Cost estimates of $330 million (stage 1) and $2,985 million</t>
         </is>
       </c>
-      <c r="R102" s="4" t="inlineStr"/>
+      <c r="R102" s="4" t="n"/>
       <c r="S102" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated in the row; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -16706,7 +16707,7 @@
           <t>Cost estimates of $330 million (stage 1) and $2,985 million</t>
         </is>
       </c>
-      <c r="R103" s="4" t="inlineStr"/>
+      <c r="R103" s="4" t="n"/>
       <c r="S103" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated in the row; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -16789,7 +16790,7 @@
           <t>HumeLink would contribute roughly $1.3 billion of the $24.5 billion in net market benefits delivered by the ODP</t>
         </is>
       </c>
-      <c r="R104" s="4" t="inlineStr"/>
+      <c r="R104" s="4" t="n"/>
       <c r="S104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
@@ -16870,7 +16871,7 @@
           <t>HumeLink  July 2026  A 500 kV transmission upgrade connecting Project EnergyConnect</t>
         </is>
       </c>
-      <c r="R105" s="4" t="inlineStr"/>
+      <c r="R105" s="4" t="n"/>
       <c r="S105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
@@ -16953,7 +16954,7 @@
           <t>long-lead equipment forecast capex of $209.6</t>
         </is>
       </c>
-      <c r="R106" s="4" t="inlineStr"/>
+      <c r="R106" s="4" t="n"/>
       <c r="S106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
@@ -17036,7 +17037,7 @@
           <t>HumeLink are $531.5 million.</t>
         </is>
       </c>
-      <c r="R107" s="4" t="inlineStr"/>
+      <c r="R107" s="4" t="n"/>
       <c r="S107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
@@ -17119,7 +17120,7 @@
           <t>Transgrid’s application proposed $226.7 million ($2022-23) in forecast capex to undertake</t>
         </is>
       </c>
-      <c r="R108" s="4" t="inlineStr"/>
+      <c r="R108" s="4" t="n"/>
       <c r="S108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
@@ -17202,7 +17203,7 @@
           <t>AER final decision HumeLink stage 1 (part 2) $227.9 million</t>
         </is>
       </c>
-      <c r="R109" s="4" t="inlineStr"/>
+      <c r="R109" s="4" t="n"/>
       <c r="S109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
@@ -17285,7 +17286,7 @@
           <t>HumeLink is a $3.9 billion ($2022-23) transmission update linking Greater Sydney load area</t>
         </is>
       </c>
-      <c r="R110" s="4" t="inlineStr"/>
+      <c r="R110" s="4" t="n"/>
       <c r="S110" s="4" t="inlineStr">
         <is>
           <t>Published as $3.9 billion.</t>
@@ -17368,7 +17369,7 @@
           <t>360 km of new 500 kilovolts (kV) transmission lines, which will expand transmission in</t>
         </is>
       </c>
-      <c r="R111" s="4" t="inlineStr"/>
+      <c r="R111" s="4" t="n"/>
       <c r="S111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
@@ -17451,7 +17452,7 @@
           <t>the total cost of the project, $4.88 billion ($2022-23),</t>
         </is>
       </c>
-      <c r="R112" s="4" t="inlineStr"/>
+      <c r="R112" s="4" t="n"/>
       <c r="S112" s="4" t="inlineStr">
         <is>
           <t>Published as $4.88 billion.</t>
@@ -17538,7 +17539,7 @@
           <t>– $4.28 billion for project delivery, and</t>
         </is>
       </c>
-      <c r="R113" s="4" t="inlineStr"/>
+      <c r="R113" s="4" t="n"/>
       <c r="S113" s="4" t="inlineStr">
         <is>
           <t>Published as $4.28 billion.</t>
@@ -17625,7 +17626,7 @@
           <t>– $0.6 billion for early works activities already</t>
         </is>
       </c>
-      <c r="R114" s="4" t="inlineStr"/>
+      <c r="R114" s="4" t="n"/>
       <c r="S114" s="4" t="inlineStr">
         <is>
           <t>Published as $0.6 billion.</t>
@@ -17708,7 +17709,7 @@
           <t>• 17 August 2022: The AER approved $375.6 million in</t>
         </is>
       </c>
-      <c r="R115" s="4" t="inlineStr"/>
+      <c r="R115" s="4" t="n"/>
       <c r="S115" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated; recorded under PRICE_BASIS_UNKNOWN. Do not treat the difference from $321.9m as cost growth.</t>
@@ -17791,7 +17792,7 @@
           <t>the total cost of early works ($632.9 million) did not</t>
         </is>
       </c>
-      <c r="R116" s="4" t="inlineStr"/>
+      <c r="R116" s="4" t="n"/>
       <c r="S116" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -17876,7 +17877,7 @@
           <t>– Northern Circuit (Gugaa to Bannaby): July 2026</t>
         </is>
       </c>
-      <c r="R117" s="4" t="inlineStr"/>
+      <c r="R117" s="4" t="n"/>
       <c r="S117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
@@ -17957,7 +17958,7 @@
           <t>– Southern Circuit (Gugaa to Maragle to Bannaby):</t>
         </is>
       </c>
-      <c r="R118" s="4" t="inlineStr"/>
+      <c r="R118" s="4" t="n"/>
       <c r="S118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
@@ -18044,7 +18045,7 @@
           <t>Our total Humelink Stage 2 forecast capex is $4,279.14 million (Table 0.1), excluding equity raising costs.</t>
         </is>
       </c>
-      <c r="R119" s="4" t="inlineStr"/>
+      <c r="R119" s="4" t="n"/>
       <c r="S119" s="4" t="inlineStr">
         <is>
           <t>Submitted 22 December 2023; the archived public file carries a 1 March 2024 publication date. Store submission and publication dates separately.</t>
@@ -18131,7 +18132,7 @@
           <t>Equity raising costs  33.14</t>
         </is>
       </c>
-      <c r="R120" s="4" t="inlineStr"/>
+      <c r="R120" s="4" t="n"/>
       <c r="S120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
@@ -18218,7 +18219,7 @@
           <t>• direct capex of $3,867.55 million (90.38 per cent of Stage 2 capex)</t>
         </is>
       </c>
-      <c r="R121" s="4" t="inlineStr"/>
+      <c r="R121" s="4" t="n"/>
       <c r="S121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
@@ -18305,7 +18306,7 @@
           <t>• labour and indirect capex of $411.59 million (9.62 per cent of Stage 2 capex).</t>
         </is>
       </c>
-      <c r="R122" s="4" t="inlineStr"/>
+      <c r="R122" s="4" t="n"/>
       <c r="S122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
@@ -18392,7 +18393,7 @@
           <t>PACR addendum Real 2021 dollars $1,809 million $845 million $3,266 million</t>
         </is>
       </c>
-      <c r="R123" s="4" t="inlineStr"/>
+      <c r="R123" s="4" t="n"/>
       <c r="S123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
@@ -18479,7 +18480,7 @@
           <t>Transgrid’s capital cost estimate for Option 3C has increased by 28 per cent from $3,820 million to $4,881</t>
         </is>
       </c>
-      <c r="R124" s="4" t="inlineStr"/>
+      <c r="R124" s="4" t="n"/>
       <c r="S124" s="4" t="inlineStr">
         <is>
           <t>Conversion factor and derivation stated at PDF p. 11, footnote 18.</t>
@@ -18570,7 +18571,7 @@
           <t>Transgrid’s capital cost estimate for Option 3C has increased by 28 per cent from $3,820 million to $4,881</t>
         </is>
       </c>
-      <c r="R125" s="4" t="inlineStr"/>
+      <c r="R125" s="4" t="n"/>
       <c r="S125" s="4" t="inlineStr">
         <is>
           <t>Also stated at PDF p. 13 with the escalator and equity-raising deductions.</t>
@@ -18657,7 +18658,7 @@
           <t>Transgrid’s capital cost estimate for Option 3C has increased by 28 per cent from $3,820 million to $4,881</t>
         </is>
       </c>
-      <c r="R126" s="4" t="inlineStr"/>
+      <c r="R126" s="4" t="n"/>
       <c r="S126" s="4" t="inlineStr">
         <is>
           <t>Transgrid attributes the movement to early-works refinement, global construction activity, supply-chain disruption, fuel costs and commodity prices (PDF p. 11); this is attribution, not an audited decomposition.</t>
@@ -18744,7 +18745,7 @@
           <t>a cost increase of $1.06 billion in June 2023 dollar terms</t>
         </is>
       </c>
-      <c r="R127" s="4" t="inlineStr"/>
+      <c r="R127" s="4" t="n"/>
       <c r="S127" s="4" t="inlineStr">
         <is>
           <t>Published as $1.06 billion; the p. 16 table implies $1,061 million.</t>
@@ -18831,7 +18832,7 @@
           <t>benefit of $4.186 billion.</t>
         </is>
       </c>
-      <c r="R128" s="4" t="inlineStr"/>
+      <c r="R128" s="4" t="n"/>
       <c r="S128" s="4" t="inlineStr">
         <is>
           <t>Published as $4.186 billion.</t>
@@ -19013,7 +19014,7 @@
 directions.</t>
         </is>
       </c>
-      <c r="R130" s="4" t="inlineStr"/>
+      <c r="R130" s="4" t="n"/>
       <c r="S130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
@@ -19096,7 +19097,7 @@
           <t>Transgrid’s proposed forecast capex of $4,279.1 million for its stage 2</t>
         </is>
       </c>
-      <c r="R131" s="4" t="inlineStr"/>
+      <c r="R131" s="4" t="n"/>
       <c r="S131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
@@ -19179,7 +19180,7 @@
           <t>some costs were included in error, which lowered its initial capex forecast to $4,173.4 million.</t>
         </is>
       </c>
-      <c r="R132" s="4" t="inlineStr"/>
+      <c r="R132" s="4" t="n"/>
       <c r="S132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
@@ -19262,7 +19263,7 @@
           <t>Our determination substitutes forecast capex of $3,964.8 million, which is $314.4 million (or</t>
         </is>
       </c>
-      <c r="R133" s="4" t="inlineStr"/>
+      <c r="R133" s="4" t="n"/>
       <c r="S133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
@@ -19345,7 +19346,7 @@
           <t>Our determination substitutes forecast capex of $3,964.8 million, which is $314.4 million (or</t>
         </is>
       </c>
-      <c r="R134" s="4" t="inlineStr"/>
+      <c r="R134" s="4" t="n"/>
       <c r="S134" s="4" t="inlineStr">
         <is>
           <t>The AER separately records that $208.6 million of the reduction is against Transgrid's revised $4,173.4m forecast.</t>
@@ -19432,7 +19433,7 @@
           <t>Total 306.0 4,267.4 4,573.5</t>
         </is>
       </c>
-      <c r="R135" s="4" t="inlineStr"/>
+      <c r="R135" s="4" t="n"/>
       <c r="S135" s="4" t="inlineStr">
         <is>
           <t>Published as $4,573.5 million, i.e. $4.5735 billion.</t>
@@ -19519,7 +19520,7 @@
           <t>Stage 1 (Part 1) early works 306.0 74.8 380.8</t>
         </is>
       </c>
-      <c r="R136" s="4" t="inlineStr"/>
+      <c r="R136" s="4" t="n"/>
       <c r="S136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
@@ -19602,7 +19603,7 @@
           <t>Stage 1 (Part 2) early works - 227.8 227.8</t>
         </is>
       </c>
-      <c r="R137" s="4" t="inlineStr"/>
+      <c r="R137" s="4" t="n"/>
       <c r="S137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
@@ -19685,7 +19686,7 @@
           <t>Tendered works (design and construction) 2,604.1 2,590.6 −13.5 −0.5%</t>
         </is>
       </c>
-      <c r="R138" s="4" t="inlineStr"/>
+      <c r="R138" s="4" t="n"/>
       <c r="S138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
@@ -19768,7 +19769,7 @@
           <t>Other construction costs (risk costs) 599.1 382.1 −217.0 −36.2%</t>
         </is>
       </c>
-      <c r="R139" s="4" t="inlineStr"/>
+      <c r="R139" s="4" t="n"/>
       <c r="S139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
@@ -19851,7 +19852,7 @@
           <t>Long lead equipment 29.6 29.6 0.0 0.0%</t>
         </is>
       </c>
-      <c r="R140" s="4" t="inlineStr"/>
+      <c r="R140" s="4" t="n"/>
       <c r="S140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
@@ -19934,7 +19935,7 @@
           <t>Land easement acquisition 197.3 197.3 0.0 0.0%</t>
         </is>
       </c>
-      <c r="R141" s="4" t="inlineStr"/>
+      <c r="R141" s="4" t="n"/>
       <c r="S141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
@@ -20017,7 +20018,7 @@
           <t>Biodiversity offset costs 437.5 353.6 −83.9 −19.2%</t>
         </is>
       </c>
-      <c r="R142" s="4" t="inlineStr"/>
+      <c r="R142" s="4" t="n"/>
       <c r="S142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
@@ -20100,7 +20101,7 @@
           <t>Labour and indirect costs (incl. escalation) 411.6 411.6 0.0 0.0%</t>
         </is>
       </c>
-      <c r="R143" s="4" t="inlineStr"/>
+      <c r="R143" s="4" t="n"/>
       <c r="S143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
@@ -20183,7 +20184,7 @@
           <t>alternative cost assumptions (present value)C 1,010 1,320 1,523</t>
         </is>
       </c>
-      <c r="R144" s="4" t="inlineStr"/>
+      <c r="R144" s="4" t="n"/>
       <c r="S144" s="4" t="inlineStr">
         <is>
           <t>The row also reports $1,010m for Option 1C-new and $1,320m for Option 2C.</t>
@@ -20353,7 +20354,7 @@
           <t>development of around 365 kilometres (km) of new double circuit 500 kV transmission lines and associated</t>
         </is>
       </c>
-      <c r="R146" s="4" t="inlineStr"/>
+      <c r="R146" s="4" t="n"/>
       <c r="S146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
@@ -20432,7 +20433,7 @@
           <t>investment of $4.8 billion and the creation of up to 1,600 full-time equivalent jobs during</t>
         </is>
       </c>
-      <c r="R147" s="4" t="inlineStr"/>
+      <c r="R147" s="4" t="n"/>
       <c r="S147" s="4" t="inlineStr">
         <is>
           <t>The assessment report states the same $4.8 billion capital investment value at PDF p. 4. Price basis not stated; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -20691,7 +20692,7 @@
           <t>– HumeLink progressed from actionable to committed: -365 km.</t>
         </is>
       </c>
-      <c r="R150" s="4" t="inlineStr"/>
+      <c r="R150" s="4" t="n"/>
       <c r="S150" s="4" t="inlineStr">
         <is>
           <t>The negative sign reflects removal from the actionable total, not a negative length.</t>
@@ -20774,7 +20775,7 @@
           <t>• Three new 500 kV transmission circuits between:</t>
         </is>
       </c>
-      <c r="R151" s="4" t="inlineStr"/>
+      <c r="R151" s="4" t="n"/>
       <c r="S151" s="4" t="inlineStr">
         <is>
           <t>A separate new 500 kV double-circuit line between Gugaa and Wagga Wagga, initially operated at 330 kV, is listed in the same scope.</t>
@@ -20944,7 +20945,7 @@
           <t>• Two 500/330 kV 1,500 MVA transformers at new Gugaa substation.</t>
         </is>
       </c>
-      <c r="R153" s="4" t="inlineStr"/>
+      <c r="R153" s="4" t="n"/>
       <c r="S153" s="4" t="inlineStr">
         <is>
           <t>Count = 2.</t>
@@ -21032,7 +21033,7 @@
 Class 5b (±50%)</t>
         </is>
       </c>
-      <c r="R154" s="4" t="inlineStr"/>
+      <c r="R154" s="4" t="n"/>
       <c r="S154" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -21115,7 +21116,7 @@
           <t>providing an additional 450 MW of transfer capacity to the SNSW to CNSW flow path</t>
         </is>
       </c>
-      <c r="R155" s="4" t="inlineStr"/>
+      <c r="R155" s="4" t="n"/>
       <c r="S155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
@@ -21196,7 +21197,7 @@
           <t>April 203192</t>
         </is>
       </c>
-      <c r="R156" s="4" t="inlineStr"/>
+      <c r="R156" s="4" t="n"/>
       <c r="S156" s="4" t="inlineStr">
         <is>
           <t>The trailing '92' in the excerpt is a footnote marker; AEMO modelled an earliest in-service date of December 2030 as advised by Transgrid.</t>
@@ -21277,7 +21278,7 @@
           <t>When completed in late 2027, the project will significantly increase power grid capacity by better connecting and distributing electricity in Australia’s eastern states.</t>
         </is>
       </c>
-      <c r="R157" s="4" t="inlineStr"/>
+      <c r="R157" s="4" t="n"/>
       <c r="S157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
@@ -21346,7 +21347,7 @@
           <t>Preparations are in place to erect the first transmission tower on the 140 kilometre HumeLink West section of HumeLink.</t>
         </is>
       </c>
-      <c r="R158" s="4" t="inlineStr"/>
+      <c r="R158" s="4" t="n"/>
       <c r="S158" s="4" t="inlineStr">
         <is>
           <t>Same page states earthworks underway for around 70 access points and the first third of about 300 km of access tracks, and that bulk civil earthworks are underway or nearing completion at the Maragle, Gugaa and Wagga Wagga substation sites.</t>
@@ -21425,7 +21426,7 @@
           <t>The nation-critical HumeLink project is on track to generate up to 1,600 jobs and drive $6.3 billion of direct and indirect investment into the surrounding regional economy.</t>
         </is>
       </c>
-      <c r="R159" s="4" t="inlineStr"/>
+      <c r="R159" s="4" t="n"/>
       <c r="S159" s="4" t="inlineStr">
         <is>
           <t>The 1,600 jobs figure matches the 'up to 1,600 full-time equivalent jobs' figure separately stated in the NSW planning decision (HUM-NSW-2024-DECISION), which pairs it with the unrelated $4.8 billion planning capital investment value; see NON_COMPARABLE_SERIES.</t>
@@ -21605,7 +21606,7 @@
 (±50%) </t>
         </is>
       </c>
-      <c r="R161" s="4" t="inlineStr"/>
+      <c r="R161" s="4" t="n"/>
       <c r="S161" s="4" t="inlineStr">
         <is>
           <t>The table gives no price basis; recorded under PRICE_BASIS_UNKNOWN.</t>
@@ -21697,7 +21698,7 @@
 $1 billion.</t>
         </is>
       </c>
-      <c r="R162" s="4" t="inlineStr"/>
+      <c r="R162" s="4" t="n"/>
       <c r="S162" s="4" t="inlineStr">
         <is>
           <t>Source wording is 'approximately $1 billion'; the page 46 figure panel gives '$1 billion' for Deliver Now Stage 1 alongside $1.8 billion for a later Stage 2.</t>
@@ -21783,7 +21784,7 @@
 connection and system strength costs).</t>
         </is>
       </c>
-      <c r="R163" s="4" t="inlineStr"/>
+      <c r="R163" s="4" t="n"/>
       <c r="S163" s="4" t="inlineStr">
         <is>
           <t>The same footnote states the total cost for a REZ typically adds 70% to 110% of development and construction costs for those excluded items.</t>
@@ -21955,7 +21956,7 @@
           <t xml:space="preserve">REZ: N10: 2,000 </t>
         </is>
       </c>
-      <c r="R165" s="4" t="inlineStr"/>
+      <c r="R165" s="4" t="n"/>
       <c r="S165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
@@ -22034,7 +22035,7 @@
           <t>This option increases the transfer capacity by up to 5,000 MW, and</t>
         </is>
       </c>
-      <c r="R166" s="4" t="inlineStr"/>
+      <c r="R166" s="4" t="n"/>
       <c r="S166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
@@ -22117,7 +22118,7 @@
 2/3 generation from Central West NSW) </t>
         </is>
       </c>
-      <c r="R167" s="4" t="inlineStr"/>
+      <c r="R167" s="4" t="n"/>
       <c r="S167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
@@ -22197,7 +22198,7 @@
 the downstream network.</t>
         </is>
       </c>
-      <c r="R168" s="4" t="inlineStr"/>
+      <c r="R168" s="4" t="n"/>
       <c r="S168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
@@ -22278,7 +22279,7 @@
 capacity</t>
         </is>
       </c>
-      <c r="R169" s="4" t="inlineStr"/>
+      <c r="R169" s="4" t="n"/>
       <c r="S169" s="4" t="inlineStr">
         <is>
           <t>The same passage states that without HTP Stage 1 the network would only support 3 GW of combined output from the three REZs.</t>
@@ -22519,7 +22520,7 @@
           <t xml:space="preserve">• A new 500 kV double-circuit line between near Eraring substation and near </t>
         </is>
       </c>
-      <c r="R172" s="4" t="inlineStr"/>
+      <c r="R172" s="4" t="n"/>
       <c r="S172" s="4" t="inlineStr">
         <is>
           <t>Substations were later named Olney and Bayswater South.</t>
@@ -22681,7 +22682,7 @@
           <t xml:space="preserve">• Two 500/330 kV 1,500 MVA transformers at Eraring substation.  </t>
         </is>
       </c>
-      <c r="R174" s="4" t="inlineStr"/>
+      <c r="R174" s="4" t="n"/>
       <c r="S174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
@@ -22756,7 +22757,7 @@
           <t>Sydney Ring Northern 500 kV loop or the Hunter Transmission Project (HTP)</t>
         </is>
       </c>
-      <c r="R175" s="4" t="inlineStr"/>
+      <c r="R175" s="4" t="n"/>
       <c r="S175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
@@ -22928,7 +22929,7 @@
 December 2028 </t>
         </is>
       </c>
-      <c r="R177" s="4" t="inlineStr"/>
+      <c r="R177" s="4" t="n"/>
       <c r="S177" s="4" t="inlineStr">
         <is>
           <t>The same cell lists ISP optimal timing of Progressive Change 2030-31, Step Change 2028-29, Green Energy Export 2028-29.</t>
@@ -23005,7 +23006,7 @@
           <t>The project is now in the New South Wales Government’s independent assessment phase. If the Hunter Transmission project is approved, construction is expected to start in late 2026.</t>
         </is>
       </c>
-      <c r="R178" s="4" t="inlineStr"/>
+      <c r="R178" s="4" t="n"/>
       <c r="S178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
@@ -23075,7 +23076,7 @@
 Pre-requisite: None </t>
         </is>
       </c>
-      <c r="R179" s="4" t="inlineStr"/>
+      <c r="R179" s="4" t="n"/>
       <c r="S179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
@@ -23145,7 +23146,7 @@
 3 GW. </t>
         </is>
       </c>
-      <c r="R180" s="4" t="inlineStr"/>
+      <c r="R180" s="4" t="n"/>
       <c r="S180" s="4" t="inlineStr">
         <is>
           <t>AEMO 2024 p24 carries the equivalent note in the HTP option description.</t>
@@ -23219,7 +23220,7 @@
 should be considered to transfer this additional generation to SNW.</t>
         </is>
       </c>
-      <c r="R181" s="4" t="inlineStr"/>
+      <c r="R181" s="4" t="n"/>
       <c r="S181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
@@ -23288,7 +23289,7 @@
           <t>Pre-requisite: CNSW-SNW Option 1 (HTP)</t>
         </is>
       </c>
-      <c r="R182" s="4" t="inlineStr"/>
+      <c r="R182" s="4" t="n"/>
       <c r="S182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
@@ -23357,7 +23358,7 @@
           <t>This project is named the Hunter Transmission Project and includes the WSB and related upgrades.</t>
         </is>
       </c>
-      <c r="R183" s="4" t="inlineStr"/>
+      <c r="R183" s="4" t="n"/>
       <c r="S183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
@@ -23427,7 +23428,7 @@
 named the Hunter Transmission Project and may include the Waratah Super Battery and related upgrades.</t>
         </is>
       </c>
-      <c r="R184" s="4" t="inlineStr"/>
+      <c r="R184" s="4" t="n"/>
       <c r="S184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
@@ -23581,7 +23582,7 @@
           <t>The Hunter Transmission Project involves building a new, 110-kilometre, overhead 500 kilovolt (kV) transmission line between Bayswater in the Upper Hunter and Olney in the Lower Hunter.</t>
         </is>
       </c>
-      <c r="R186" s="4" t="inlineStr"/>
+      <c r="R186" s="4" t="n"/>
       <c r="S186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
@@ -23656,7 +23657,7 @@
           <t>It will be supported by double-circuit steel lattice towers.</t>
         </is>
       </c>
-      <c r="R187" s="4" t="inlineStr"/>
+      <c r="R187" s="4" t="n"/>
       <c r="S187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
@@ -23731,7 +23732,7 @@
           <t>The Hunter Transmission Project (HTP) involves building a new, 110-kilometre, 500 kilovolt (kV) overhead transmission line between Bayswater in the Upper Hunter and Olney in the Lower Hunter.</t>
         </is>
       </c>
-      <c r="R188" s="4" t="inlineStr"/>
+      <c r="R188" s="4" t="n"/>
       <c r="S188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
@@ -23806,7 +23807,7 @@
           <t>500 kilovolt (kV) overhead transmission line</t>
         </is>
       </c>
-      <c r="R189" s="4" t="inlineStr"/>
+      <c r="R189" s="4" t="n"/>
       <c r="S189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
@@ -23875,7 +23876,7 @@
           <t>The towers will be up to 85 metres tall and generally spaced 300 to 600 metres apart, depending on the terrain and other constraints along the corridor.</t>
         </is>
       </c>
-      <c r="R190" s="4" t="inlineStr"/>
+      <c r="R190" s="4" t="n"/>
       <c r="S190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
@@ -23950,7 +23951,7 @@
           <t>We’ll build 2 new switching stations – 1 near the existing Bayswater substation and another at a former timber plantation site in Olney State Forest.</t>
         </is>
       </c>
-      <c r="R191" s="4" t="inlineStr"/>
+      <c r="R191" s="4" t="n"/>
       <c r="S191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
@@ -24019,7 +24020,7 @@
           <t>The NSW Department of Planning, Housing and Infrastructure has granted planning approval for the Hunter Transmission Project, with the Minister for Planning and Public Spaces issuing the Conditions of Approval following a detailed and independent assessment process.</t>
         </is>
       </c>
-      <c r="R192" s="4" t="inlineStr"/>
+      <c r="R192" s="4" t="n"/>
       <c r="S192" s="4" t="inlineStr">
         <is>
           <t>The same page states this update is headed 'Planning approval granted for the Hunter Transmission Project | July 2026'.</t>
@@ -24096,7 +24097,7 @@
           <t>Construction is expected to start in mid-2027.</t>
         </is>
       </c>
-      <c r="R193" s="4" t="inlineStr"/>
+      <c r="R193" s="4" t="n"/>
       <c r="S193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
@@ -24175,7 +24176,7 @@
           <t>Our final decision is that Ausgrid can recover $189.6 million ($ nominal) for the 2026–31 period.</t>
         </is>
       </c>
-      <c r="R194" s="4" t="inlineStr"/>
+      <c r="R194" s="4" t="n"/>
       <c r="S194" s="4" t="inlineStr">
         <is>
           <t>The same $189.6 million figure recurs at pp22 and 83 of the same decision.</t>
@@ -24254,7 +24255,7 @@
           <t>It will provide an additional 1 GW of network transfer capacity and will consist of three portions:</t>
         </is>
       </c>
-      <c r="R195" s="4" t="inlineStr"/>
+      <c r="R195" s="4" t="n"/>
       <c r="S195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
@@ -24323,7 +24324,7 @@
           <t>Portion 2: Muswellbrook network rearrangement, Singleton to Kurri 132kV link, and installation of a communications link across the Hawkesbury River (providing a cumulative total of 630 MW additional network capacity), scheduled for completion in June 2028.</t>
         </is>
       </c>
-      <c r="R196" s="4" t="inlineStr"/>
+      <c r="R196" s="4" t="n"/>
       <c r="S196" s="4" t="inlineStr">
         <is>
           <t>Portion 1 (Upper Hunter secondary systems modernisation, 350MW, late 2025) and Portion 3 (new Antiene 132kV switching station and Antiene to Singleton 132kV link, cumulative 1 GW, July 2028) are described in the same passage (p9) but not separately recorded here.</t>
@@ -24396,7 +24397,7 @@
           <t>The Hunter-Central Coast renewable energy zone is hereby declared and comprises:</t>
         </is>
       </c>
-      <c r="R197" s="4" t="inlineStr"/>
+      <c r="R197" s="4" t="n"/>
       <c r="S197" s="4" t="inlineStr">
         <is>
           <t>The gazette masthead (p1) reads 'NSW Government Gazette No 569 of 9 December 2022' and 'Friday, 9 December 2022'; AER's 2025 final decision (p9) also states the Minister declared the HCC REZ on 9 December 2022. The manifest's document title records '16 December 2022', which does not match the date printed in the captured document.</t>
@@ -24475,7 +24476,7 @@
           <t>The intended network capacity for network infrastructure in the Hunter-Central Coast renewable energy zone is one gigawatt.</t>
         </is>
       </c>
-      <c r="R198" s="4" t="inlineStr"/>
+      <c r="R198" s="4" t="n"/>
       <c r="S198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
@@ -24558,7 +24559,7 @@
           <t>The Jacobs report provides an expected project cost for the delivery of Project Marinus of $3,481 million ($2020).</t>
         </is>
       </c>
-      <c r="R199" s="4" t="inlineStr"/>
+      <c r="R199" s="4" t="n"/>
       <c r="S199" s="4" t="inlineStr">
         <is>
           <t>Contingency-inclusive probabilistic estimate.</t>
@@ -24645,7 +24646,7 @@
           <t>Cost sensitivity P10 Estimate Expected Cost P90 Estimate Total project cost estimate 3,138 3,481 3,827</t>
         </is>
       </c>
-      <c r="R200" s="4" t="inlineStr"/>
+      <c r="R200" s="4" t="n"/>
       <c r="S200" s="4" t="inlineStr">
         <is>
           <t>Source narrative rounds overall range to $3.1bn-$3.8bn. Pinpoint corrected from p77 to the Table 19 page during migration.</t>
@@ -24732,7 +24733,7 @@
           <t>Cost sensitivity P10 Estimate Expected Cost P90 Estimate Total project cost estimate 3,138 3,481 3,827</t>
         </is>
       </c>
-      <c r="R201" s="4" t="inlineStr"/>
+      <c r="R201" s="4" t="n"/>
       <c r="S201" s="4" t="inlineStr">
         <is>
           <t>Source narrative rounds overall range to $3.1bn-$3.8bn. Pinpoint corrected from p77 to the Table 19 page during migration.</t>
@@ -24819,7 +24820,7 @@
           <t>3,840 (Total for Stage 1)</t>
         </is>
       </c>
-      <c r="R202" s="4" t="inlineStr"/>
+      <c r="R202" s="4" t="n"/>
       <c r="S202" s="4" t="inlineStr">
         <is>
           <t>Source-defined stage observation; do not automatically add Stage 2. Dollar year is not stated in the project table.</t>
@@ -24906,7 +24907,7 @@
           <t>2,890 (HVDC) Class 4 (±30%)</t>
         </is>
       </c>
-      <c r="R203" s="4" t="inlineStr"/>
+      <c r="R203" s="4" t="n"/>
       <c r="S203" s="4" t="inlineStr">
         <is>
           <t>Marinus Link supplied scope/cost.</t>
@@ -24993,7 +24994,7 @@
           <t>950 (HVAC) Class 4 (+30%,-15%)</t>
         </is>
       </c>
-      <c r="R204" s="4" t="inlineStr"/>
+      <c r="R204" s="4" t="n"/>
       <c r="S204" s="4" t="inlineStr">
         <is>
           <t>TasNetworks supplied scope/cost.</t>
@@ -25080,7 +25081,7 @@
           <t>2,735 (Total for Stage 2)</t>
         </is>
       </c>
-      <c r="R205" s="4" t="inlineStr"/>
+      <c r="R205" s="4" t="n"/>
       <c r="S205" s="4" t="inlineStr">
         <is>
           <t>Separate stage; additional $235m if completed more than two years after Stage 1.</t>
@@ -25167,7 +25168,7 @@
           <t>2,210 (HVDC) Class 4 (±30%)</t>
         </is>
       </c>
-      <c r="R206" s="4" t="inlineStr"/>
+      <c r="R206" s="4" t="n"/>
       <c r="S206" s="4" t="inlineStr">
         <is>
           <t>Marinus Link supplied scope/cost.</t>
@@ -25254,7 +25255,7 @@
           <t>525 (HVAC) Class 4 (+30%,-15%)</t>
         </is>
       </c>
-      <c r="R207" s="4" t="inlineStr"/>
+      <c r="R207" s="4" t="n"/>
       <c r="S207" s="4" t="inlineStr">
         <is>
           <t>TasNetworks supplied scope/cost.</t>
@@ -25337,7 +25338,7 @@
           <t>Note: This part is estimated to cost an additional $235 million if completed more than 2 years after Stage 1.</t>
         </is>
       </c>
-      <c r="R208" s="4" t="inlineStr"/>
+      <c r="R208" s="4" t="n"/>
       <c r="S208" s="4" t="inlineStr">
         <is>
           <t>Source-stated conditional amount.</t>
@@ -25401,12 +25402,12 @@
       </c>
       <c r="M209" s="4" t="inlineStr">
         <is>
-          <t>Stage 1 including facilitation for Stage 2; Project Marinus, excluding separately stated NWTD</t>
+          <t>Stage 1 including facilitation for Stage 2; Project Marinus, including NWTD; study-period valuation, not lifetime construction outturn</t>
         </is>
       </c>
       <c r="N209" s="4" t="inlineStr">
         <is>
-          <t>Not like-for-like with AEMO 2024</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex.</t>
         </is>
       </c>
       <c r="O209" s="4" t="inlineStr">
@@ -25424,7 +25425,7 @@
           <t>The costs for Project Marinus are $5,035 million for the first stage (which includes facilitation for stage 2), and $2,535 million for completion of the second stage.</t>
         </is>
       </c>
-      <c r="R209" s="4" t="inlineStr"/>
+      <c r="R209" s="4" t="n"/>
       <c r="S209" s="4" t="inlineStr">
         <is>
           <t>Approximately $534m sunk costs excluded from net-benefit calculation. Pinpoint corrected from pp15-16 during migration.</t>
@@ -25488,12 +25489,12 @@
       </c>
       <c r="M210" s="4" t="inlineStr">
         <is>
-          <t>Completion of Stage 2; Project Marinus, excluding separately stated NWTD</t>
+          <t>Completion of Stage 2; Project Marinus, including NWTD; study-period valuation, not lifetime construction outturn</t>
         </is>
       </c>
       <c r="N210" s="4" t="inlineStr">
         <is>
-          <t>Not like-for-like with AEMO 2024</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex.</t>
         </is>
       </c>
       <c r="O210" s="4" t="inlineStr">
@@ -25511,7 +25512,7 @@
           <t>$2,535 million for completion of the second stage.</t>
         </is>
       </c>
-      <c r="R210" s="4" t="inlineStr"/>
+      <c r="R210" s="4" t="n"/>
       <c r="S210" s="4" t="inlineStr">
         <is>
           <t>Stage 2 timing remains under review. Pinpoint corrected from pp15-16 during migration.</t>
@@ -25580,7 +25581,7 @@
       </c>
       <c r="N211" s="4" t="inlineStr">
         <is>
-          <t>Separate delivery/funding boundary</t>
+          <t>NWTD component included in Project Marinus stage costs; not an additional project total</t>
         </is>
       </c>
       <c r="O211" s="4" t="inlineStr">
@@ -25598,7 +25599,7 @@
           <t>The NWTD component is $1,144 million for the first stage, and $525 million for the second stage.</t>
         </is>
       </c>
-      <c r="R211" s="4" t="inlineStr"/>
+      <c r="R211" s="4" t="n"/>
       <c r="S211" s="4" t="inlineStr">
         <is>
           <t>Do not silently add to Project Marinus amount. Pinpoint corrected from p16 during migration.</t>
@@ -25667,7 +25668,7 @@
       </c>
       <c r="N212" s="4" t="inlineStr">
         <is>
-          <t>Separate delivery/funding boundary</t>
+          <t>NWTD component included in Project Marinus stage costs; not an additional project total</t>
         </is>
       </c>
       <c r="O212" s="4" t="inlineStr">
@@ -25685,7 +25686,7 @@
           <t>$525 million for the second stage.</t>
         </is>
       </c>
-      <c r="R212" s="4" t="inlineStr"/>
+      <c r="R212" s="4" t="n"/>
       <c r="S212" s="4" t="inlineStr">
         <is>
           <t>Do not silently add to Project Marinus amount. Pinpoint corrected from p16 during migration.</t>
@@ -25749,12 +25750,12 @@
       </c>
       <c r="M213" s="4" t="inlineStr">
         <is>
-          <t>Project Marinus Stage 1 plus Stage 2, as reported in feedback-loop context</t>
+          <t>Project Marinus Stage 1 plus Stage 2 including NWTD, feedback-loop reported study-period cost; not Link-only</t>
         </is>
       </c>
       <c r="N213" s="4" t="inlineStr">
         <is>
-          <t>Source-defined total; not construction outturn</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex.</t>
         </is>
       </c>
       <c r="O213" s="4" t="inlineStr">
@@ -25867,7 +25868,7 @@
           <t>The reported cost of $2,485 million (in $2025) represents the total cost of TAS-SEV Option 2A, escalated from the $2023 cost of $2,351 million</t>
         </is>
       </c>
-      <c r="R214" s="4" t="inlineStr"/>
+      <c r="R214" s="4" t="n"/>
       <c r="S214" s="4" t="inlineStr">
         <is>
           <t>Escalated from $2,351m in 2023 dollars; $184m Burnie-Hampshire removed; $51m incurred/approved works noted separately.</t>
@@ -25946,7 +25947,7 @@
           <t>the preferred option is a 1500 MW HVDC interconnector, comprising two 750 MW HVDC links, plus associated AC network upgrades.</t>
         </is>
       </c>
-      <c r="R215" s="4" t="inlineStr"/>
+      <c r="R215" s="4" t="n"/>
       <c r="S215" s="4" t="inlineStr">
         <is>
           <t>Earliest archived statement of the 1,500 MW configuration.</t>
@@ -26116,7 +26117,7 @@
           <t>approximately 90 kilometres of underground HVDC cable in Victoria</t>
         </is>
       </c>
-      <c r="R217" s="4" t="inlineStr"/>
+      <c r="R217" s="4" t="n"/>
       <c r="S217" s="4" t="inlineStr">
         <is>
           <t>One of the two length components the chart's 345 km sums.</t>
@@ -26278,7 +26279,7 @@
           <t>A 750 MW monopole HVDC link between Burnie area in Tasmania and Hazelwood area in Victoria.</t>
         </is>
       </c>
-      <c r="R219" s="4" t="inlineStr"/>
+      <c r="R219" s="4" t="n"/>
       <c r="S219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
@@ -26353,7 +26354,7 @@
           <t>Project Marinus Stage 2 comprises the second 750 MW development.</t>
         </is>
       </c>
-      <c r="R220" s="4" t="inlineStr"/>
+      <c r="R220" s="4" t="n"/>
       <c r="S220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
@@ -26511,7 +26512,7 @@
           <t>A new 500 kV connection from converter station in Hazelwood area.</t>
         </is>
       </c>
-      <c r="R222" s="4" t="inlineStr"/>
+      <c r="R222" s="4" t="n"/>
       <c r="S222" s="4" t="inlineStr">
         <is>
           <t>Relevant to the chart's definition of trunk km as distance rated at 500 kV.</t>
@@ -26590,7 +26591,7 @@
           <t>A new 220 kV switching station at Heybridge adjacent to the converter station.</t>
         </is>
       </c>
-      <c r="R223" s="4" t="inlineStr"/>
+      <c r="R223" s="4" t="n"/>
       <c r="S223" s="4" t="inlineStr">
         <is>
           <t>The NWTD lines are the candidate feeder lines for the chart's feeder column.</t>
@@ -26675,7 +26676,7 @@
           <t>Anticipated project December 2030</t>
         </is>
       </c>
-      <c r="R224" s="4" t="inlineStr"/>
+      <c r="R224" s="4" t="n"/>
       <c r="S224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
@@ -26841,7 +26842,7 @@
           <t>Financial close has been reached for Stage 1 of Marinus Link, marking the final decision for one of the most important energy projects in our nation’s history.</t>
         </is>
       </c>
-      <c r="R226" s="4" t="inlineStr"/>
+      <c r="R226" s="4" t="n"/>
       <c r="S226" s="4" t="inlineStr">
         <is>
           <t>Dated by the release's own dateline, 3 September 2025.</t>
@@ -26920,7 +26921,7 @@
           <t>Securing the $3.8bn funding from the Commonwealth's Clean Energy Finance Corporation, along with equity commitments from the Commonwealth, Tasmania and Victoria in August</t>
         </is>
       </c>
-      <c r="R227" s="4" t="inlineStr"/>
+      <c r="R227" s="4" t="n"/>
       <c r="S227" s="4" t="inlineStr">
         <is>
           <t>Dollar year not stated; equity commitment amounts not stated.</t>
@@ -26999,7 +27000,7 @@
           <t>Stage 1 will comprise of 750 megawatts of capacity – enough to power roughly 750,000 homes.</t>
         </is>
       </c>
-      <c r="R228" s="4" t="inlineStr"/>
+      <c r="R228" s="4" t="n"/>
       <c r="S228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
@@ -27078,7 +27079,7 @@
           <t>The $994 million ($nominal) contract covers the construction of converter stations in Heybridge and Hazelwood, the installation of equipment, and the land cable civil works, spanning 90km across Gippsland.</t>
         </is>
       </c>
-      <c r="R229" s="4" t="inlineStr"/>
+      <c r="R229" s="4" t="n"/>
       <c r="S229" s="4" t="inlineStr">
         <is>
           <t>MLPL's final Stage 1 major works contract; follows the September 2025 announcement of TVGL as preferred bidder for the 'Balance of Works' package.</t>
@@ -27157,7 +27158,7 @@
           <t>the land cable civil works, spanning 90km across Gippsland</t>
         </is>
       </c>
-      <c r="R230" s="4" t="inlineStr"/>
+      <c r="R230" s="4" t="n"/>
       <c r="S230" s="4" t="inlineStr">
         <is>
           <t>Contract land cable civil works boundary; do not merge with the RIT-T length observation without checking scope.</t>
@@ -27236,7 +27237,7 @@
           <t>The New England REZ was declared on 17 December 2021 under the Electricity Infrastructure Investment Act 2020 (NSW) with an intended 8,000 MW50 of</t>
         </is>
       </c>
-      <c r="R231" s="4" t="inlineStr"/>
+      <c r="R231" s="4" t="n"/>
       <c r="S231" s="4" t="inlineStr">
         <is>
           <t>The Gazette 2021 No 643 declaration is now archived directly as NER-NSWGOV-2021-GAZETTE-643; see NER-AO-2021-GAZETTE-8GW for the primary-source statement. This observation records AEMO's own account of it. The trailing 50 is a footnote marker in the source.</t>
@@ -27315,7 +27316,7 @@
           <t>Forward: 6,000</t>
         </is>
       </c>
-      <c r="R232" s="4" t="inlineStr"/>
+      <c r="R232" s="4" t="n"/>
       <c r="S232" s="4" t="inlineStr">
         <is>
           <t>Stated in the delivery-scope table for CNSW-NNSW Option 1.</t>
@@ -27394,7 +27395,7 @@
           <t>Reverse: 6,00057</t>
         </is>
       </c>
-      <c r="R233" s="4" t="inlineStr"/>
+      <c r="R233" s="4" t="n"/>
       <c r="S233" s="4" t="inlineStr">
         <is>
           <t>AEMO footnote 57 states it assumes a symmetrical uplift in both directions and that reverse capacity depends on the location of future generation. The trailing 57 is a footnote marker.</t>
@@ -27471,7 +27472,7 @@
           <t>Reported cost ($</t>
         </is>
       </c>
-      <c r="R234" s="4" t="inlineStr"/>
+      <c r="R234" s="4" t="n"/>
       <c r="S234" s="4" t="inlineStr">
         <is>
           <t>The delivery-scope table carries a 'Reported cost ($ million)' column but the New England row contains no amount. Footnote 56 states the final scope and cost is subject to the competitive procurement process outcome. Recorded as a null observation; never backfilled from the chart.</t>
@@ -27637,7 +27638,7 @@
           <t>EnergyCo has advised that this project (previously modelled in two parts) will now be completed in one part (CNSW-NNSW Option 1) by January 203455.</t>
         </is>
       </c>
-      <c r="R236" s="4" t="inlineStr"/>
+      <c r="R236" s="4" t="n"/>
       <c r="S236" s="4" t="inlineStr">
         <is>
           <t>The trailing 55 is a footnote marker.</t>
@@ -27716,7 +27717,7 @@
           <t>Since the 2024 ISP, the New England REZ NIP scope has been revised, including extending to Northern Hub with an additional 170 km.</t>
         </is>
       </c>
-      <c r="R237" s="4" t="inlineStr"/>
+      <c r="R237" s="4" t="n"/>
       <c r="S237" s="4" t="inlineStr">
         <is>
           <t>Appendix footnote 11. The related +1,166 km figure on the same page covers the New England REZ NIP and Project Marinus Stage 1 together and is not attributable to this project.</t>
@@ -27878,7 +27879,7 @@
           <t>New Central A Hub 500/330 kV substation with 3 x 500/330/33 kV 1,500 MVA</t>
         </is>
       </c>
-      <c r="R239" s="4" t="inlineStr"/>
+      <c r="R239" s="4" t="n"/>
       <c r="S239" s="4" t="inlineStr">
         <is>
           <t>Three units at 1,500 MVA.</t>
@@ -27957,7 +27958,7 @@
           <t>New 4 x 340 MVA phase shifting transformers at Central B.</t>
         </is>
       </c>
-      <c r="R240" s="4" t="inlineStr"/>
+      <c r="R240" s="4" t="n"/>
       <c r="S240" s="4" t="inlineStr">
         <is>
           <t>Recorded so the chart's transformer total is auditable against everything the source lists.</t>
@@ -28121,7 +28122,7 @@
           <t>June 2024, the New England REZ Network Infrastructure Project was declared a Critical State Significant Infrastructure project by the New South Wales</t>
         </is>
       </c>
-      <c r="R242" s="4" t="inlineStr"/>
+      <c r="R242" s="4" t="n"/>
       <c r="S242" s="4" t="inlineStr">
         <is>
           <t>See SOURCE_UNAVAILABLE for ENE-CSSI.</t>
@@ -28204,7 +28205,7 @@
           <t>1,834 (±50%)</t>
         </is>
       </c>
-      <c r="R243" s="4" t="inlineStr"/>
+      <c r="R243" s="4" t="n"/>
       <c r="S243" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated in the table; see PRICE_BASIS_UNKNOWN. Not summed with the other 2024 options.</t>
@@ -28291,7 +28292,7 @@
           <t>REZ N2: 1,000 370 Class 5b (±50%)</t>
         </is>
       </c>
-      <c r="R244" s="4" t="inlineStr"/>
+      <c r="R244" s="4" t="n"/>
       <c r="S244" s="4" t="inlineStr">
         <is>
           <t>The excerpt runs the option's 1,000 MW REZ N2 capacity into the cost cell because the table columns are adjacent in the derivative. Price basis not stated.</t>
@@ -28378,7 +28379,7 @@
           <t>1,493 Class 5b (± 50%)</t>
         </is>
       </c>
-      <c r="R245" s="4" t="inlineStr"/>
+      <c r="R245" s="4" t="n"/>
       <c r="S245" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated. Timing advised by proponent was June 2033.</t>
@@ -28457,7 +28458,7 @@
           <t>3,000 (both directions of CNSW to NNSW)</t>
         </is>
       </c>
-      <c r="R246" s="4" t="inlineStr"/>
+      <c r="R246" s="4" t="n"/>
       <c r="S246" s="4" t="inlineStr">
         <is>
           <t>The same row separately states REZ N2: 2,000.</t>
@@ -28536,7 +28537,7 @@
           <t>REZ N2: 2,000</t>
         </is>
       </c>
-      <c r="R247" s="4" t="inlineStr"/>
+      <c r="R247" s="4" t="n"/>
       <c r="S247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
@@ -28611,7 +28612,7 @@
           <t>REZ N2: 1,000</t>
         </is>
       </c>
-      <c r="R248" s="4" t="inlineStr"/>
+      <c r="R248" s="4" t="n"/>
       <c r="S248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
@@ -28686,7 +28687,7 @@
           <t>REZ N2: 3,000</t>
         </is>
       </c>
-      <c r="R249" s="4" t="inlineStr"/>
+      <c r="R249" s="4" t="n"/>
       <c r="S249" s="4" t="inlineStr">
         <is>
           <t>The table states the flow path figure for this option assumes downstream limitations are addressed by Hunter Transmission Project/CNSW-SNW Option 1.</t>
@@ -28767,7 +28768,7 @@
           <t>2031. EnergyCo has also advised that the timing for Flow Path Option 2 is June 2033.</t>
         </is>
       </c>
-      <c r="R250" s="4" t="inlineStr"/>
+      <c r="R250" s="4" t="n"/>
       <c r="S250" s="4" t="inlineStr">
         <is>
           <t>The table modelled commissioning by July 2030 while EnergyCo's earliest practical date was June 2031.</t>
@@ -28850,7 +28851,7 @@
           <t>The project is estimated to cost $1.9 billion ±50%.</t>
         </is>
       </c>
-      <c r="R251" s="4" t="inlineStr"/>
+      <c r="R251" s="4" t="n"/>
       <c r="S251" s="4" t="inlineStr">
         <is>
           <t>Price basis not stated; see PRICE_BASIS_UNKNOWN.</t>
@@ -28929,7 +28930,7 @@
           <t>It was formally declared on 17 December 2021, with an intended network capacity of 8 GW.10</t>
         </is>
       </c>
-      <c r="R252" s="4" t="inlineStr"/>
+      <c r="R252" s="4" t="n"/>
       <c r="S252" s="4" t="inlineStr">
         <is>
           <t>The same page states a further 2 GW of network capacity may be delivered by future augmentations. The trailing 10 is a footnote marker.</t>
@@ -29008,7 +29009,7 @@
           <t>New England REZ: add 6 GW of network capacity, with new lines to connect four new substation hubs to the existing network between Bayswater and the Tamworth–Armidale line.</t>
         </is>
       </c>
-      <c r="R253" s="4" t="inlineStr"/>
+      <c r="R253" s="4" t="n"/>
       <c r="S253" s="4" t="inlineStr">
         <is>
           <t>The same passage proposes the 6 GW over two stages of 2.4 GW and 3.6 GW.</t>
@@ -29087,7 +29088,7 @@
           <t>for the New England REZ would limit its network capacity to 6 GW, down from the intended 8 GW,</t>
         </is>
       </c>
-      <c r="R254" s="4" t="inlineStr"/>
+      <c r="R254" s="4" t="n"/>
       <c r="S254" s="4" t="inlineStr">
         <is>
           <t>The source adds that additional capacity would be considered for future expansions.</t>
@@ -29166,7 +29167,7 @@
           <t>Secure Now. An additional 0.8 GW capacity by 2029 to support long-duration storage in the region, delivered by an upgrade to an existing line between Armidale and Carrai.</t>
         </is>
       </c>
-      <c r="R255" s="4" t="inlineStr"/>
+      <c r="R255" s="4" t="n"/>
       <c r="S255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
@@ -29241,7 +29242,7 @@
           <t>Plan for the Future. An additional 1.5 GW capacity if needed to support strong state-wide electrification, delivered by a new 330 kV line running north from the Central hub.</t>
         </is>
       </c>
-      <c r="R256" s="4" t="inlineStr"/>
+      <c r="R256" s="4" t="n"/>
       <c r="S256" s="4" t="inlineStr"/>
     </row>
     <row r="257">
@@ -29316,7 +29317,7 @@
           <t>Construction cost preliminary estimates c $7.8 billion $1.5 billion $3.0 billion</t>
         </is>
       </c>
-      <c r="R257" s="4" t="inlineStr"/>
+      <c r="R257" s="4" t="n"/>
       <c r="S257" s="4" t="inlineStr">
         <is>
           <t>Recorded to show the only archived EnergyCo cost figure is not a NIP cost. Price basis not stated. The three amounts are Deliver Now, Secure Now and Plan for the Future respectively.</t>
@@ -29397,7 +29398,7 @@
           <t>New England REZ 2029</t>
         </is>
       </c>
-      <c r="R258" s="4" t="inlineStr"/>
+      <c r="R258" s="4" t="n"/>
       <c r="S258" s="4" t="inlineStr">
         <is>
           <t>From the proposed timing table for initial energisations.</t>
@@ -29478,7 +29479,7 @@
           <t>Pre-requisite: New England REZ Network Infrastructure Project</t>
         </is>
       </c>
-      <c r="R259" s="4" t="inlineStr"/>
+      <c r="R259" s="4" t="n"/>
       <c r="S259" s="4" t="inlineStr">
         <is>
           <t>QNI Connect is deferred to a future project in the 2026 ISP and its proponents are no longer progressing a PADR.</t>
@@ -29557,7 +29558,7 @@
           <t>the 6 GW network transfer capacity target to be unlocked by Stage s 1 and 2</t>
         </is>
       </c>
-      <c r="R260" s="4" t="inlineStr"/>
+      <c r="R260" s="4" t="n"/>
       <c r="S260" s="4" t="inlineStr">
         <is>
           <t>Page 9 states an initial network capacity of 6 GW delivered over two stages. Table 1 on page 11 states Stage 1 = 2.4 GW (2032) and Stage 2 cumulative = 6.0 GW (2034). The derivative's text extraction splits 'Stages' as 'Stage s'.</t>
@@ -29636,7 +29637,7 @@
           <t>the potential to increase the network capacity to 8 GW in the future</t>
         </is>
       </c>
-      <c r="R261" s="4" t="inlineStr"/>
+      <c r="R261" s="4" t="n"/>
       <c r="S261" s="4" t="inlineStr">
         <is>
           <t>Table 1 (page 11) separately states Stage 3 = 8.0 GW, timing TBC, an additional transfer capacity of at least 2 GW subject to energy demand and separate approvals.</t>
@@ -29883,7 +29884,7 @@
           <t>The final easement will be around 140m wide, generally 70m for each 500kV line.</t>
         </is>
       </c>
-      <c r="R264" s="4" t="inlineStr"/>
+      <c r="R264" s="4" t="n"/>
       <c r="S264" s="4" t="inlineStr">
         <is>
           <t>Also stated at p38 ('additional 140m-wide easement...generally 70m wide for each 500kV line') and p39 ('the 140m-wide transmission easement required for twin 500kV lines'). This report names the separately published Bulk Corridor Design Refinement Report (November 2025) but does not reproduce its route-length table; no '305' figure or Table E1 appears anywhere in this derivative.</t>
@@ -30130,7 +30131,7 @@
 Length 346 km 305 km</t>
         </is>
       </c>
-      <c r="R267" s="4" t="inlineStr"/>
+      <c r="R267" s="4" t="n"/>
       <c r="S267" s="4" t="inlineStr">
         <is>
           <t>The report recommends proceeding with the new study corridor (305 km) over the Refined PSC (346 km); see NER-AO-2025-BULKCORRIDOR-RECOMMEND.</t>
@@ -30209,7 +30210,7 @@
           <t>The project is currently about 350 kilometres in length, with the transmission corridor extending from the Bayswater Power Station in the Hunter region of NSW</t>
         </is>
       </c>
-      <c r="R268" s="4" t="inlineStr"/>
+      <c r="R268" s="4" t="n"/>
       <c r="S268" s="4" t="inlineStr">
         <is>
           <t>Restated near-identically at p24: 'The project is about 350 kilometres in length, with the transmission corridor extending from the Bayswater Power Station...'.</t>
@@ -30291,7 +30292,7 @@
 engagement, detailed environmental assessment and Reference Design development.</t>
         </is>
       </c>
-      <c r="R269" s="4" t="inlineStr"/>
+      <c r="R269" s="4" t="n"/>
       <c r="S269" s="4" t="inlineStr">
         <is>
           <t>Executive summary (p7) states the report 'recommends proceeding with the new study corridor'; an independent review panel found the new study corridor preferable on constructability grounds (p19).</t>
@@ -30371,7 +30372,7 @@
 central hub B) in October 2025.</t>
         </is>
       </c>
-      <c r="R270" s="4" t="inlineStr"/>
+      <c r="R270" s="4" t="n"/>
       <c r="S270" s="4" t="inlineStr">
         <is>
           <t>The main body text on the same page describes 'Four energy hubs' before this footnote (footnote 2) updates the count to five as of October 2025.</t>
@@ -30452,7 +30453,7 @@
 network</t>
         </is>
       </c>
-      <c r="R271" s="4" t="inlineStr"/>
+      <c r="R271" s="4" t="n"/>
       <c r="S271" s="4" t="inlineStr">
         <is>
           <t>The same sentence continues: 'and new single 500 kV and 330 kV transmission lines to connect to energy hubs and one switching station within the New England REZ' (p24-25); those single lines are a separate, unenumerated boundary not counted here.</t>
@@ -30531,7 +30532,7 @@
           <t>Cost The capital cost estimate is $1,393 million to $2,587 million.</t>
         </is>
       </c>
-      <c r="R272" s="4" t="inlineStr"/>
+      <c r="R272" s="4" t="n"/>
       <c r="S272" s="4" t="inlineStr">
         <is>
           <t>Dollar year not stated in the project entry; see PRICE_BASIS_UNKNOWN.</t>
@@ -30610,7 +30611,7 @@
           <t>Cost The capital cost estimate is $1,393 million to $2,587 million.</t>
         </is>
       </c>
-      <c r="R273" s="4" t="inlineStr"/>
+      <c r="R273" s="4" t="n"/>
       <c r="S273" s="4" t="inlineStr">
         <is>
           <t>Dollar year not stated in the project entry; see PRICE_BASIS_UNKNOWN.</t>
@@ -30693,7 +30694,7 @@
           <t>Table 4 details our current total capex forecast of $2,290.9 million (Real 2017-18) for our component of the</t>
         </is>
       </c>
-      <c r="R274" s="4" t="inlineStr"/>
+      <c r="R274" s="4" t="n"/>
       <c r="S274" s="4" t="inlineStr">
         <is>
           <t>Comprises $1,826.8m tendered works, $122.1m project risks, $342.0m other costs.</t>
@@ -30776,7 +30777,7 @@
           <t>application is $470.7 million ($2017-18). Competitive market pricing makes up most of these costs.</t>
         </is>
       </c>
-      <c r="R275" s="4" t="inlineStr"/>
+      <c r="R275" s="4" t="n"/>
       <c r="S275" s="4" t="inlineStr">
         <is>
           <t>Source footnote: excludes prior period expenditure of approximately $3.3 million already in the RAB.</t>
@@ -30859,7 +30860,7 @@
           <t>contingent project. TransGrid reduced this to $1,866.3 million in its April 2021</t>
         </is>
       </c>
-      <c r="R276" s="4" t="inlineStr"/>
+      <c r="R276" s="4" t="n"/>
       <c r="S276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
@@ -30938,7 +30939,7 @@
           <t>project of $468.6 million ($2017-18). This component of the project is proposed to</t>
         </is>
       </c>
-      <c r="R277" s="4" t="inlineStr"/>
+      <c r="R277" s="4" t="n"/>
       <c r="S277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
@@ -31017,7 +31018,7 @@
           <t>Forecast capital expenditure ($2017-18) $457.4 million</t>
         </is>
       </c>
-      <c r="R278" s="4" t="inlineStr"/>
+      <c r="R278" s="4" t="n"/>
       <c r="S278" s="4" t="inlineStr">
         <is>
           <t>AER states this is 2.3-2.4 per cent less than ElectraNet's proposal (pp5, 14).</t>
@@ -31100,7 +31101,7 @@
           <t>Forecast capital expenditure ($2017-18) $1,817.9 million</t>
         </is>
       </c>
-      <c r="R279" s="4" t="inlineStr"/>
+      <c r="R279" s="4" t="n"/>
       <c r="S279" s="4" t="inlineStr">
         <is>
           <t>AER states this is 2.6 per cent less than TransGrid's April 2021 proposal (p5).</t>
@@ -31183,7 +31184,7 @@
           <t>Forecast operating expenditure ($2017-18) $0.5 million</t>
         </is>
       </c>
-      <c r="R280" s="4" t="inlineStr"/>
+      <c r="R280" s="4" t="n"/>
       <c r="S280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
@@ -31262,7 +31263,7 @@
           <t>Forecast operating expenditure ($2017-18) $2.5 million</t>
         </is>
       </c>
-      <c r="R281" s="4" t="inlineStr"/>
+      <c r="R281" s="4" t="n"/>
       <c r="S281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
@@ -31341,7 +31342,7 @@
           <t>Project EnergyConnect is a proposed $2.3 billion ($2017-18) contingent project to</t>
         </is>
       </c>
-      <c r="R282" s="4" t="inlineStr"/>
+      <c r="R282" s="4" t="n"/>
       <c r="S282" s="4" t="inlineStr">
         <is>
           <t>The same sentence appears in the ElectraNet determination at physical page 7.</t>
@@ -31420,7 +31421,7 @@
           <t>EnergyConnect generated an estimated $4.1 billion in social value from June 2023 to June 2026</t>
         </is>
       </c>
-      <c r="R283" s="4" t="inlineStr"/>
+      <c r="R283" s="4" t="n"/>
       <c r="S283" s="4" t="inlineStr">
         <is>
           <t>This is the only $4.1 billion figure for PEC anywhere in the archive; see CHART_DERIVATION and AUTHOR_DECISION_REQUIRED warnings.</t>
@@ -31499,7 +31500,7 @@
           <t>SA to NSW (at time of peak demand, both directions) +800 MW</t>
         </is>
       </c>
-      <c r="R284" s="4" t="inlineStr"/>
+      <c r="R284" s="4" t="n"/>
       <c r="S284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
@@ -31574,7 +31575,7 @@
           <t>SA to VIC (at time of peak demand, both directions)A +100 MW</t>
         </is>
       </c>
-      <c r="R285" s="4" t="inlineStr"/>
+      <c r="R285" s="4" t="n"/>
       <c r="S285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
@@ -31649,7 +31650,7 @@
           <t>150 MW</t>
         </is>
       </c>
-      <c r="R286" s="4" t="inlineStr"/>
+      <c r="R286" s="4" t="n"/>
       <c r="S286" s="4" t="inlineStr">
         <is>
           <t>Table cell under 'Stage 1:' in the Additional network capacity (MW) column, physical p17.</t>
@@ -31728,7 +31729,7 @@
           <t>800 MW</t>
         </is>
       </c>
-      <c r="R287" s="4" t="inlineStr"/>
+      <c r="R287" s="4" t="n"/>
       <c r="S287" s="4" t="inlineStr">
         <is>
           <t>Table cell under 'Stage 2:' followed by 'In both directions of NSW-SA', physical p17.</t>
@@ -31807,7 +31808,7 @@
           <t>In both directions of</t>
         </is>
       </c>
-      <c r="R288" s="4" t="inlineStr"/>
+      <c r="R288" s="4" t="n"/>
       <c r="S288" s="4" t="inlineStr">
         <is>
           <t>Table cell '100 MW' / 'In both directions of' / 'VIC-SA', physical p17; the numeral and its qualifier are on separate derivative lines.</t>
@@ -31886,7 +31887,7 @@
           <t>Project EnergyConnect Stage 1 is completed. The maximum transfer capability from SNSW to CSA is 150 MW in both directions.</t>
         </is>
       </c>
-      <c r="R289" s="4" t="inlineStr"/>
+      <c r="R289" s="4" t="n"/>
       <c r="S289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
@@ -31961,7 +31962,7 @@
           <t>650 MW</t>
         </is>
       </c>
-      <c r="R290" s="4" t="inlineStr"/>
+      <c r="R290" s="4" t="n"/>
       <c r="S290" s="4" t="inlineStr">
         <is>
           <t>Table cell under 'Stage 2:' with 'In both directions of' / 'NSW-SA', physical p16.</t>
@@ -32040,7 +32041,7 @@
           <t>100 MW</t>
         </is>
       </c>
-      <c r="R291" s="4" t="inlineStr"/>
+      <c r="R291" s="4" t="n"/>
       <c r="S291" s="4" t="inlineStr">
         <is>
           <t>Table cell followed by 'In both directions of' / 'VIC-SA', physical p16.</t>
@@ -32202,7 +32203,7 @@
           <t>S2: 800 MW</t>
         </is>
       </c>
-      <c r="R293" s="4" t="inlineStr"/>
+      <c r="R293" s="4" t="n"/>
       <c r="S293" s="4" t="inlineStr"/>
     </row>
     <row r="294">
@@ -32277,7 +32278,7 @@
           <t>Stretching 900km across New South Wales, Victoria and South Australia, it has connected the three state grids for the very first time.</t>
         </is>
       </c>
-      <c r="R294" s="4" t="inlineStr"/>
+      <c r="R294" s="4" t="n"/>
       <c r="S294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
@@ -32352,7 +32353,7 @@
           <t>a further 165km of 500kV transmission line Dinawan to Wagga Wagga, comprising 334 towers</t>
         </is>
       </c>
-      <c r="R295" s="4" t="inlineStr"/>
+      <c r="R295" s="4" t="n"/>
       <c r="S295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
@@ -32427,7 +32428,7 @@
           <t>375km of new 330kV transmission line between Buronga and the new Dinawan substation at Bundure, comprising 800 towers</t>
         </is>
       </c>
-      <c r="R296" s="4" t="inlineStr"/>
+      <c r="R296" s="4" t="n"/>
       <c r="S296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
@@ -32502,7 +32503,7 @@
           <t>135km of new 330kV transmission line between the SA border and Buronga, comprising 291 towers.</t>
         </is>
       </c>
-      <c r="R297" s="4" t="inlineStr"/>
+      <c r="R297" s="4" t="n"/>
       <c r="S297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
@@ -32660,7 +32661,7 @@
           <t>Project EnergyConnect is a new 330 kV interconnector between New South Wales and South Australia. Project EnergyConnect is under</t>
         </is>
       </c>
-      <c r="R299" s="4" t="inlineStr"/>
+      <c r="R299" s="4" t="n"/>
       <c r="S299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
@@ -32735,7 +32736,7 @@
           <t>A new Robertstown to Bundey 275 kV double-circuit line.</t>
         </is>
       </c>
-      <c r="R300" s="4" t="inlineStr"/>
+      <c r="R300" s="4" t="n"/>
       <c r="S300" s="4" t="inlineStr"/>
     </row>
     <row r="301">
@@ -32810,7 +32811,7 @@
           <t>A new 500 kV double-circuit line from Dinawan to Wagga Wagga</t>
         </is>
       </c>
-      <c r="R301" s="4" t="inlineStr"/>
+      <c r="R301" s="4" t="n"/>
       <c r="S301" s="4" t="inlineStr">
         <is>
           <t>Next derivative line: 'operating at 330 kV'.</t>
@@ -33132,7 +33133,7 @@
           <t>An additional 1 x 100 MVA 330 kV connected synchronous condenser at</t>
         </is>
       </c>
-      <c r="R305" s="4" t="inlineStr"/>
+      <c r="R305" s="4" t="n"/>
       <c r="S305" s="4" t="inlineStr">
         <is>
           <t>Next derivative line: 'Buronga.'</t>
@@ -33290,7 +33291,7 @@
           <t>installation of 5 phase shifting transformers and 2 synchronous condensers.</t>
         </is>
       </c>
-      <c r="R307" s="4" t="inlineStr"/>
+      <c r="R307" s="4" t="n"/>
       <c r="S307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
@@ -33365,7 +33366,7 @@
           <t>Construction of new 4.5ha substation near Bundure including installation of 2 synchronous condensers.</t>
         </is>
       </c>
-      <c r="R308" s="4" t="inlineStr"/>
+      <c r="R308" s="4" t="n"/>
       <c r="S308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
@@ -33523,7 +33524,7 @@
           <t>A new 330/220 kV substation, 1 x 200 MVA 330/220 kV transformer and</t>
         </is>
       </c>
-      <c r="R310" s="4" t="inlineStr"/>
+      <c r="R310" s="4" t="n"/>
       <c r="S310" s="4" t="inlineStr">
         <is>
           <t>Next derivative line: '1 x 200 MVA 330 kV phase shifting transformer at Buronga.'</t>
@@ -33602,7 +33603,7 @@
           <t>Additional 4 x 200 megavolt amperes (MVA) 330 kV phase shifting transformers</t>
         </is>
       </c>
-      <c r="R311" s="4" t="inlineStr"/>
+      <c r="R311" s="4" t="n"/>
       <c r="S311" s="4" t="inlineStr">
         <is>
           <t>Next derivative line: 'at Buronga.'</t>
@@ -33681,7 +33682,7 @@
           <t>Additional 2 x 200 MVA 330/220 kV transformers at Buronga.</t>
         </is>
       </c>
-      <c r="R312" s="4" t="inlineStr"/>
+      <c r="R312" s="4" t="n"/>
       <c r="S312" s="4" t="inlineStr"/>
     </row>
     <row r="313">
@@ -33756,7 +33757,7 @@
           <t>15ha extension of Buronga Substation to accommodate the new 330kV and 220kV circuits and installation of 5 phase shifting transformers</t>
         </is>
       </c>
-      <c r="R313" s="4" t="inlineStr"/>
+      <c r="R313" s="4" t="n"/>
       <c r="S313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
@@ -33833,7 +33834,7 @@
           <t>implementation of this project is tracking ahead of schedule with commissioning targeted in stages between late</t>
         </is>
       </c>
-      <c r="R314" s="4" t="inlineStr"/>
+      <c r="R314" s="4" t="n"/>
       <c r="S314" s="4" t="inlineStr">
         <is>
           <t>Sentence continues '2022 and late 2023.' on the next derivative line.</t>
@@ -33914,7 +33915,7 @@
           <t>Project EnergyConnect July 2026‡ A new 330 kilovolt (kV) double-circuit interconnector between South</t>
         </is>
       </c>
-      <c r="R315" s="4" t="inlineStr"/>
+      <c r="R315" s="4" t="n"/>
       <c r="S315" s="4" t="inlineStr">
         <is>
           <t>A footnote marker follows 'July 2026' in the derivative; the excerpt drops it.</t>
@@ -33995,7 +33996,7 @@
           <t>Stage 1: December 2024</t>
         </is>
       </c>
-      <c r="R316" s="4" t="inlineStr"/>
+      <c r="R316" s="4" t="n"/>
       <c r="S316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
@@ -34072,7 +34073,7 @@
           <t>Stage 2: July 2027</t>
         </is>
       </c>
-      <c r="R317" s="4" t="inlineStr"/>
+      <c r="R317" s="4" t="n"/>
       <c r="S317" s="4" t="inlineStr">
         <is>
           <t>Footnote on p18: 'This service date refers to capacity available following completion of inter-network testing.'</t>
@@ -34153,7 +34154,7 @@
           <t>Project EnergyConnect has been split into two stages. Stage 1 connecting Robertstown (via Bundey) to Buronga was completed in late 2024</t>
         </is>
       </c>
-      <c r="R318" s="4" t="inlineStr"/>
+      <c r="R318" s="4" t="n"/>
       <c r="S318" s="4" t="inlineStr"/>
     </row>
     <row r="319">
@@ -34315,7 +34316,7 @@
           <t>integration into the National Electricity Market (NEM) by the end of 2026.</t>
         </is>
       </c>
-      <c r="R320" s="4" t="inlineStr"/>
+      <c r="R320" s="4" t="n"/>
       <c r="S320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
@@ -34392,7 +34393,7 @@
           <t>Construction and initial energisation is complete for EnergyConnect</t>
         </is>
       </c>
-      <c r="R321" s="4" t="inlineStr"/>
+      <c r="R321" s="4" t="n"/>
       <c r="S321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
@@ -34467,7 +34468,7 @@
           <t>At the start of this year, we confirmed that the forecast cost to deliver PEC had increased to $3.6 billion.</t>
         </is>
       </c>
-      <c r="R322" s="4" t="inlineStr"/>
+      <c r="R322" s="4" t="n"/>
       <c r="S322" s="4" t="inlineStr">
         <is>
           <t>See PEC-AO-2026-TG-REOPENER-COST-TABLE3 for the itemised figure with its stated price basis; see PRICE_BASIS_UNKNOWN.</t>
@@ -34633,7 +34634,7 @@
           <t>Transgrid and its delivery partner Elecnor Australia have completed construction of the 700km NSW section of the essential interconnector, with more than 1,500 towers and over 10,000km of high-voltage conductor.</t>
         </is>
       </c>
-      <c r="R324" s="4" t="inlineStr"/>
+      <c r="R324" s="4" t="n"/>
       <c r="S324" s="4" t="inlineStr">
         <is>
           <t>The same figure ('700km of transmission lines from the South Australian border to Red Cliffs in Victoria and Wagga Wagga') recurs in the release's Fast Facts block, derivative line 184.</t>
@@ -34714,7 +34715,7 @@
           <t>Transgrid and its delivery partner Elecnor Australia have completed construction of the 700km NSW section of the essential interconnector, with more than 1,500 towers and over 10,000km of high-voltage conductor.</t>
         </is>
       </c>
-      <c r="R325" s="4" t="inlineStr"/>
+      <c r="R325" s="4" t="n"/>
       <c r="S325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
@@ -34791,7 +34792,7 @@
           <t>Stage 2 of EnergyConnect, the 540km line between Buronga and Wagga Wagga, is being energised following detailed commissioning checks.</t>
         </is>
       </c>
-      <c r="R326" s="4" t="inlineStr"/>
+      <c r="R326" s="4" t="n"/>
       <c r="S326" s="4" t="inlineStr">
         <is>
           <t>Sentence continues: 'Later this year, the Australian Energy Market Operator will begin its inter-network testing on stage 2.'</t>
@@ -34870,7 +34871,7 @@
           <t>Stage 2 of EnergyConnect, the 540km line between Buronga and Wagga Wagga, is being energised following detailed commissioning checks.</t>
         </is>
       </c>
-      <c r="R327" s="4" t="inlineStr"/>
+      <c r="R327" s="4" t="n"/>
       <c r="S327" s="4" t="inlineStr"/>
     </row>
     <row r="328">
@@ -34947,7 +34948,7 @@
           <t>The first stage of the project, a 160km line from the South Australian border to Buronga and into Victoria, became operational last year.</t>
         </is>
       </c>
-      <c r="R328" s="4" t="inlineStr"/>
+      <c r="R328" s="4" t="n"/>
       <c r="S328" s="4" t="inlineStr"/>
     </row>
     <row r="329">
@@ -35101,7 +35102,7 @@
           <t>Approximate total length of 900km</t>
         </is>
       </c>
-      <c r="R330" s="4" t="inlineStr"/>
+      <c r="R330" s="4" t="n"/>
       <c r="S330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
@@ -35176,7 +35177,7 @@
           <t>the 700km NSW section of this nation-critical infrastructure.</t>
         </is>
       </c>
-      <c r="R331" s="4" t="inlineStr"/>
+      <c r="R331" s="4" t="n"/>
       <c r="S331" s="4" t="inlineStr">
         <is>
           <t>Preceding text: 'Transgrid and its construction partner Elecnor Australia are getting on with the job of delivering'.</t>
@@ -35256,7 +35257,7 @@
 800MW transfer capacity.</t>
         </is>
       </c>
-      <c r="R332" s="4" t="inlineStr"/>
+      <c r="R332" s="4" t="n"/>
       <c r="S332" s="4" t="inlineStr">
         <is>
           <t>Preceding text: 'Project EnergyConnect involves the construction of a new 330 kilovolt (kV) above ground transmission line, with approximately'.</t>
@@ -35347,7 +35348,7 @@
           <t>$2,621 million, consisting of $261 million (power flow control option) and $2,360 million (500 kV transmission option)</t>
         </is>
       </c>
-      <c r="R333" s="4" t="inlineStr"/>
+      <c r="R333" s="4" t="n"/>
       <c r="S333" s="4" t="inlineStr">
         <is>
           <t>Table cell reads 261 with footnotes 85 and 86; footnote 85 gives the price basis and the split.</t>
@@ -35438,7 +35439,7 @@
           <t>$2,621 million, consisting of $261 million (power flow control option) and $2,360 million (500 kV transmission option)</t>
         </is>
       </c>
-      <c r="R334" s="4" t="inlineStr"/>
+      <c r="R334" s="4" t="n"/>
       <c r="S334" s="4" t="inlineStr">
         <is>
           <t>Table cell on p.44 reads 2,360 with footnote 85; footnote 85 on p.43 states the basis.</t>
@@ -35529,7 +35530,7 @@
           <t>$2,621 million, consisting of $261 million (power flow control option) and $2,360 million (500 kV transmission option)</t>
         </is>
       </c>
-      <c r="R335" s="4" t="inlineStr"/>
+      <c r="R335" s="4" t="n"/>
       <c r="S335" s="4" t="inlineStr">
         <is>
           <t>AEMO states the composition itself; the pack does not sum the components.</t>
@@ -35612,10 +35613,10 @@
           <t>Transgrid’s Sydney Ring South PADR has identified the preferred option (PADR Option 6) with a capital cost estimate of $3,519 million (nominal).</t>
         </is>
       </c>
-      <c r="R336" s="4" t="inlineStr"/>
+      <c r="R336" s="4" t="n"/>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>The PADR itself is unavailable (SRS-TG-PADR-DIRECT, SRS-TG-PADR-INDEX). AEMO's quoted figure is $3,519m, not the $3,510m used in the chart notes.</t>
+          <t>The immutable chart contains $3.5bn, consistent with rounding the PADR Option 6 total of $3,519m nominal to one decimal billion. The source gives Stage 1 $1,135m and Stage 2 $2,384m, P50 Class 5 (+100%/-50%). AEMO's $2,621m modelled $2025 amount is a different price basis. No transcription error is established (PADR p38; AEMO 2026 p43).</t>
         </is>
       </c>
     </row>
@@ -35695,7 +35696,7 @@
           <t>first options (PADR Option 3, 4, 5, 6) have capital cost estimates between $3,353 million (nominal) and $4,915 million (nominal).</t>
         </is>
       </c>
-      <c r="R337" s="4" t="inlineStr"/>
+      <c r="R337" s="4" t="n"/>
       <c r="S337" s="4" t="inlineStr"/>
     </row>
     <row r="338">
@@ -35774,7 +35775,7 @@
           <t>first options (PADR Option 3, 4, 5, 6) have capital cost estimates between $3,353 million (nominal) and $4,915 million (nominal).</t>
         </is>
       </c>
-      <c r="R338" s="4" t="inlineStr"/>
+      <c r="R338" s="4" t="n"/>
       <c r="S338" s="4" t="inlineStr"/>
     </row>
     <row r="339">
@@ -35861,7 +35862,7 @@
           <t>^ Transgrid’s preparatory activity addendum cost estimate of $225 million ($2023-24) has been converted to ($2022-23).</t>
         </is>
       </c>
-      <c r="R339" s="4" t="inlineStr"/>
+      <c r="R339" s="4" t="n"/>
       <c r="S339" s="4" t="inlineStr">
         <is>
           <t>Table cell on p.27 reads 221^; footnote ^ on p.28 states the conversion and price basis.</t>
@@ -35940,7 +35941,7 @@
           <t>SNW1: 3,600 MW</t>
         </is>
       </c>
-      <c r="R340" s="4" t="inlineStr"/>
+      <c r="R340" s="4" t="n"/>
       <c r="S340" s="4" t="inlineStr">
         <is>
           <t>The same table states Forward: 3,600 MW and SNW1: 3,600 MW; the power flow control option is stated at 0 MW forward.</t>
@@ -36019,7 +36020,7 @@
           <t>REZ: N11 + N12: 2,000 MW</t>
         </is>
       </c>
-      <c r="R341" s="4" t="inlineStr"/>
+      <c r="R341" s="4" t="n"/>
       <c r="S341" s="4" t="inlineStr"/>
     </row>
     <row r="342">
@@ -36094,7 +36095,7 @@
           <t>Forward: 0 MW</t>
         </is>
       </c>
-      <c r="R342" s="4" t="inlineStr"/>
+      <c r="R342" s="4" t="n"/>
       <c r="S342" s="4" t="inlineStr"/>
     </row>
     <row r="343">
@@ -36169,7 +36170,7 @@
           <t>flow path is 2,540 MW at peak demand and summer typical, and 2,720 MW at winter reference periods.</t>
         </is>
       </c>
-      <c r="R343" s="4" t="inlineStr"/>
+      <c r="R343" s="4" t="n"/>
       <c r="S343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
@@ -36244,7 +36245,7 @@
           <t>flow path is 2,540 MW at peak demand and summer typical, and 2,720 MW at winter reference periods.</t>
         </is>
       </c>
-      <c r="R344" s="4" t="inlineStr"/>
+      <c r="R344" s="4" t="n"/>
       <c r="S344" s="4" t="inlineStr"/>
     </row>
     <row r="345">
@@ -36319,7 +36320,7 @@
           <t>Rebuild 7 km of existing single-circuit 330 kV between South Creek and Sydney West</t>
         </is>
       </c>
-      <c r="R345" s="4" t="inlineStr"/>
+      <c r="R345" s="4" t="n"/>
       <c r="S345" s="4" t="inlineStr"/>
     </row>
     <row r="346">
@@ -36394,7 +36395,7 @@
           <t>Re-conductor approx. 7 km of existing double-circuit 330 kV lines 32 and 38 with high</t>
         </is>
       </c>
-      <c r="R346" s="4" t="inlineStr"/>
+      <c r="R346" s="4" t="n"/>
       <c r="S346" s="4" t="inlineStr">
         <is>
           <t>Source says 'approx. 7 km'.</t>
@@ -36631,7 +36632,7 @@
           <t>Double-circuit 330 kV transmission line built to a 500 kV design between Bannaby</t>
         </is>
       </c>
-      <c r="R349" s="4" t="inlineStr"/>
+      <c r="R349" s="4" t="n"/>
       <c r="S349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
@@ -36706,7 +36707,7 @@
           <t>Double-circuit 330 kV transmission line built to a 500 kV design between Bannaby</t>
         </is>
       </c>
-      <c r="R350" s="4" t="inlineStr"/>
+      <c r="R350" s="4" t="n"/>
       <c r="S350" s="4" t="inlineStr">
         <is>
           <t>South Creek is separately upgraded to a 330/500 kV substation and 500 kV lines are re-terminated at Bannaby and South Creek.</t>
@@ -36868,7 +36869,7 @@
           <t>Establish a new substation in the locality of South Creek with 2 x</t>
         </is>
       </c>
-      <c r="R352" s="4" t="inlineStr"/>
+      <c r="R352" s="4" t="n"/>
       <c r="S352" s="4" t="inlineStr"/>
     </row>
     <row r="353">
@@ -36943,7 +36944,7 @@
           <t>4x 120 MVAr line shunt reactors on the 500kv lines between Bannaby and South Creek</t>
         </is>
       </c>
-      <c r="R353" s="4" t="inlineStr"/>
+      <c r="R353" s="4" t="n"/>
       <c r="S353" s="4" t="inlineStr">
         <is>
           <t>Source states 4x 120 MVAr.</t>
@@ -37109,7 +37110,7 @@
           <t>July 2033</t>
         </is>
       </c>
-      <c r="R355" s="4" t="inlineStr"/>
+      <c r="R355" s="4" t="n"/>
       <c r="S355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
@@ -37186,7 +37187,7 @@
           <t>July 2030 (power flow control)</t>
         </is>
       </c>
-      <c r="R356" s="4" t="inlineStr"/>
+      <c r="R356" s="4" t="n"/>
       <c r="S356" s="4" t="inlineStr"/>
     </row>
     <row r="357">
@@ -37344,7 +37345,7 @@
           <t>could extend to around 100 km</t>
         </is>
       </c>
-      <c r="R358" s="4" t="inlineStr"/>
+      <c r="R358" s="4" t="n"/>
       <c r="S358" s="4" t="inlineStr">
         <is>
           <t>PADR pages 6 and 41 separately describe the same line as extending 'more than 100 km'; no corridor or route has been selected.</t>
@@ -37433,7 +37434,7 @@
           <t>The Class 5 estimates are of an expected accuracy of +100 per cent/-50 per cent.</t>
         </is>
       </c>
-      <c r="R359" s="4" t="inlineStr"/>
+      <c r="R359" s="4" t="n"/>
       <c r="S359" s="4" t="inlineStr"/>
     </row>
     <row r="360">
@@ -37520,7 +37521,7 @@
           <t>The estimated capital cost of Stage 1 is approximately $1,135 million (nominal), with Stage 2 adding a further $2,384</t>
         </is>
       </c>
-      <c r="R360" s="4" t="inlineStr"/>
+      <c r="R360" s="4" t="n"/>
       <c r="S360" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33) of the PADR. Same sentence gives Stage 2 and the option total; see SRS-AO-2026-PADR-OPT6-STAGE2-COST and SRS-AO-2026-PADR-OPT6-TOTAL-COST.</t>
@@ -37611,7 +37612,7 @@
           <t>Stage 2 adding a further $2,384 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent).</t>
         </is>
       </c>
-      <c r="R361" s="4" t="inlineStr"/>
+      <c r="R361" s="4" t="n"/>
       <c r="S361" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33) of the PADR.</t>
@@ -37848,7 +37849,7 @@
       </c>
       <c r="N364" s="4" t="inlineStr">
         <is>
-          <t>Matches the ODP timing for Stage 1 works</t>
+          <t>PADR earliest-service modelling in 2030/31 differs from the June 2026 ISP ODP, which delivers both stages in 2033-34 (AEMO 2026 Appendix A5 PDF p44, footnote 87). Keep the modelling and ODP milestone definitions separate.</t>
         </is>
       </c>
       <c r="O364" s="4" t="inlineStr">
@@ -37866,7 +37867,7 @@
           <t>The earliest in-service timing modelled for Option 6 is 2030/31 for the South Creek substation and power flow control scope (series reactors), and 2033/34 for the 500 kV transmission line, which considers early works commencing in 2026/27.</t>
         </is>
       </c>
-      <c r="R364" s="4" t="inlineStr"/>
+      <c r="R364" s="4" t="n"/>
       <c r="S364" s="4" t="inlineStr"/>
     </row>
     <row r="365">
@@ -37943,7 +37944,7 @@
           <t>The earliest in-service timing modelled for Option 6 is 2030/31 for the South Creek substation and power flow control scope (series reactors), and 2033/34 for the 500 kV transmission line, which considers early works commencing in 2026/27.</t>
         </is>
       </c>
-      <c r="R365" s="4" t="inlineStr"/>
+      <c r="R365" s="4" t="n"/>
       <c r="S365" s="4" t="inlineStr"/>
     </row>
     <row r="366">
@@ -38030,7 +38031,7 @@
           <t>The estimated capital cost of this option is approximately $644 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent).</t>
         </is>
       </c>
-      <c r="R366" s="4" t="inlineStr"/>
+      <c r="R366" s="4" t="n"/>
       <c r="S366" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38121,7 +38122,7 @@
           <t>The estimated capital cost of this option is approximately $240 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent).</t>
         </is>
       </c>
-      <c r="R367" s="4" t="inlineStr"/>
+      <c r="R367" s="4" t="n"/>
       <c r="S367" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38212,7 +38213,7 @@
           <t>The estimated capital cost of Stage 1 is approximately $2,646 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent).</t>
         </is>
       </c>
-      <c r="R368" s="4" t="inlineStr"/>
+      <c r="R368" s="4" t="n"/>
       <c r="S368" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38303,7 +38304,7 @@
           <t>The estimated capital cost of Stage 2 is a further $1,162 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent), bringing the total estimated capital cost of the option to $3,808 million (nominal).</t>
         </is>
       </c>
-      <c r="R369" s="4" t="inlineStr"/>
+      <c r="R369" s="4" t="n"/>
       <c r="S369" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38394,7 +38395,7 @@
           <t>bringing the total estimated capital cost of the option to $3,808 million (nominal).</t>
         </is>
       </c>
-      <c r="R370" s="4" t="inlineStr"/>
+      <c r="R370" s="4" t="n"/>
       <c r="S370" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38485,7 +38486,7 @@
           <t>The estimated capital cost of Stage 1 is approximately $942 million (nominal), with Stage 2 adding a further $2,411 million</t>
         </is>
       </c>
-      <c r="R371" s="4" t="inlineStr"/>
+      <c r="R371" s="4" t="n"/>
       <c r="S371" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38576,7 +38577,7 @@
           <t>with Stage 2 adding a further $2,411 million (nominal) based on a P50 Class 5 estimate</t>
         </is>
       </c>
-      <c r="R372" s="4" t="inlineStr"/>
+      <c r="R372" s="4" t="n"/>
       <c r="S372" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38667,7 +38668,7 @@
           <t>The total estimated capital cost of the option is $3,353 million (nominal).</t>
         </is>
       </c>
-      <c r="R373" s="4" t="inlineStr"/>
+      <c r="R373" s="4" t="n"/>
       <c r="S373" s="4" t="inlineStr">
         <is>
           <t>Matches AEMO's secondhand range low end (SRS-AO-2026-PADR-RANK1-LOW). Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38758,7 +38759,7 @@
           <t>The estimated capital cost of Stage 1 is approximately $251 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent).</t>
         </is>
       </c>
-      <c r="R374" s="4" t="inlineStr"/>
+      <c r="R374" s="4" t="n"/>
       <c r="S374" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38849,7 +38850,7 @@
           <t>The estimated capital cost of Stage 2 is a further $4,664 million (nominal) based on a P50 Class 5 estimate ( +100 per cent/-50 per cent), bringing the total estimated capital cost of the option to $4,915 million (nominal).</t>
         </is>
       </c>
-      <c r="R375" s="4" t="inlineStr"/>
+      <c r="R375" s="4" t="n"/>
       <c r="S375" s="4" t="inlineStr">
         <is>
           <t>Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -38940,7 +38941,7 @@
           <t>bringing the total estimated capital cost of the option to $4,915 million (nominal).</t>
         </is>
       </c>
-      <c r="R376" s="4" t="inlineStr"/>
+      <c r="R376" s="4" t="n"/>
       <c r="S376" s="4" t="inlineStr">
         <is>
           <t>Matches AEMO's secondhand range high end (SRS-AO-2026-PADR-RANK1-HIGH). Also tabulated in Table E.1 (p.8) and Table 3.1 (p.33).</t>
@@ -39019,7 +39020,7 @@
           <t>Transgrid has assessed six options to upgrade infrastructure, including upgrades to the existing network and new substations and transmission lines that could bring more energy into Western Sydney.</t>
         </is>
       </c>
-      <c r="R377" s="4" t="inlineStr"/>
+      <c r="R377" s="4" t="n"/>
       <c r="S377" s="4" t="inlineStr">
         <is>
           <t>Web capture; unpaged, cited as page 'web'.</t>
@@ -39098,7 +39099,7 @@
           <t>Transgrid is investigating options for a second high-capacity transmission pathway, such as a 500 kV transmission line, into Western Sydney.</t>
         </is>
       </c>
-      <c r="R378" s="4" t="inlineStr"/>
+      <c r="R378" s="4" t="n"/>
       <c r="S378" s="4" t="inlineStr">
         <is>
           <t>Same page states elsewhere that no corridor, route or preferred technology has been decided (SRS-AO-2026-PROJECTPAGE-NO-ROUTE).</t>
@@ -39175,7 +39176,7 @@
           <t>13-week consultation period was open for submissions between 29 May and 28 August 2026.</t>
         </is>
       </c>
-      <c r="R379" s="4" t="inlineStr"/>
+      <c r="R379" s="4" t="n"/>
       <c r="S379" s="4" t="inlineStr">
         <is>
           <t>Page marks the PADR stage as 'Completed' with this consultation window.</t>
@@ -39256,7 +39257,7 @@
           <t>We anticipate the PACR, which outlines the final preferred option, will be published in mid-2027 at the earliest.</t>
         </is>
       </c>
-      <c r="R380" s="4" t="inlineStr"/>
+      <c r="R380" s="4" t="n"/>
       <c r="S380" s="4" t="inlineStr">
         <is>
           <t>Do not conflate with SRS-AO-2026-COMPLETION-ODP; this is the PACR publication date, not a completion date.</t>
@@ -39329,7 +39330,7 @@
           <t>At this stage of the planning process, no corridor, route or preferred technology has been decided, and the final engineering solution remains open. No final decision on a preferred option has been made.</t>
         </is>
       </c>
-      <c r="R381" s="4" t="inlineStr"/>
+      <c r="R381" s="4" t="n"/>
       <c r="S381" s="4" t="inlineStr"/>
     </row>
     <row r="382">
@@ -39507,7 +39508,7 @@
           <t>This has been modelled separately at an additional cost of $116</t>
         </is>
       </c>
-      <c r="R383" s="4" t="inlineStr"/>
+      <c r="R383" s="4" t="n"/>
       <c r="S383" s="4" t="inlineStr">
         <is>
           <t>Price basis is not stated for the increment; the $7,600m it sits above is $2025.</t>
@@ -39598,7 +39599,7 @@
           <t>3,499 *</t>
         </is>
       </c>
-      <c r="R384" s="4" t="inlineStr"/>
+      <c r="R384" s="4" t="n"/>
       <c r="S384" s="4" t="inlineStr">
         <is>
           <t>Source states the cost is inclusive of the $315m WRL project.</t>
@@ -39685,7 +39686,7 @@
           <t>AEMO has applied a cost of $3,614 million for VNI West. This is determined by subtracting the cost of WRL from the quoted project cost in 2020-21 dollars and converting to real 2023 dollars.</t>
         </is>
       </c>
-      <c r="R385" s="4" t="inlineStr"/>
+      <c r="R385" s="4" t="n"/>
       <c r="S385" s="4" t="inlineStr"/>
     </row>
     <row r="386">
@@ -39764,7 +39765,7 @@
           <t>The Minns Labor Government will invest $225 million in the 2026 NSW Budget to bring more low-cost renewable energy into the grid</t>
         </is>
       </c>
-      <c r="R386" s="4" t="inlineStr"/>
+      <c r="R386" s="4" t="n"/>
       <c r="S386" s="4" t="inlineStr">
         <is>
           <t>Publication date is not asserted from the page. AEMO 2026 footnote 100 cites the same announcement.</t>
@@ -39847,7 +39848,7 @@
           <t>N5: 600 (+1,800105)</t>
         </is>
       </c>
-      <c r="R387" s="4" t="inlineStr"/>
+      <c r="R387" s="4" t="n"/>
       <c r="S387" s="4" t="inlineStr">
         <is>
           <t>Superscript 105 is the footnote marker retained by the text derivative.</t>
@@ -40017,7 +40018,7 @@
           <t>Forward: 1,890</t>
         </is>
       </c>
-      <c r="R389" s="4" t="inlineStr"/>
+      <c r="R389" s="4" t="n"/>
       <c r="S389" s="4" t="inlineStr"/>
     </row>
     <row r="390">
@@ -40096,7 +40097,7 @@
           <t>Reverse: 1,670</t>
         </is>
       </c>
-      <c r="R390" s="4" t="inlineStr"/>
+      <c r="R390" s="4" t="n"/>
       <c r="S390" s="4" t="inlineStr"/>
     </row>
     <row r="391">
@@ -40175,7 +40176,7 @@
           <t>N5: 900 MW</t>
         </is>
       </c>
-      <c r="R391" s="4" t="inlineStr"/>
+      <c r="R391" s="4" t="n"/>
       <c r="S391" s="4" t="inlineStr"/>
     </row>
     <row r="392">
@@ -40254,7 +40255,7 @@
           <t>Additional REZ hosting capacity South West NSW: +1,000 MW</t>
         </is>
       </c>
-      <c r="R392" s="4" t="inlineStr"/>
+      <c r="R392" s="4" t="n"/>
       <c r="S392" s="4" t="inlineStr"/>
     </row>
     <row r="393">
@@ -40333,7 +40334,7 @@
           <t>Increase in VIC-NSW transfer (at time of peak demand) A +1,930MW North</t>
         </is>
       </c>
-      <c r="R393" s="4" t="inlineStr"/>
+      <c r="R393" s="4" t="n"/>
       <c r="S393" s="4" t="inlineStr"/>
     </row>
     <row r="394">
@@ -40412,7 +40413,7 @@
           <t>+1,800 MW South</t>
         </is>
       </c>
-      <c r="R394" s="4" t="inlineStr"/>
+      <c r="R394" s="4" t="n"/>
       <c r="S394" s="4" t="inlineStr">
         <is>
           <t>The identical figure appears for the Shepparton route option on p33-34.</t>
@@ -40582,7 +40583,7 @@
           <t>Establish Dinawan 500 kV switchyard with two 500/330 kV 1,500 MVA</t>
         </is>
       </c>
-      <c r="R396" s="4" t="inlineStr"/>
+      <c r="R396" s="4" t="n"/>
       <c r="S396" s="4" t="inlineStr"/>
     </row>
     <row r="397">
@@ -40748,7 +40749,7 @@
           <t>VNI West is a proposed 500 kV interconnector from near Bulgana in Victoria to Dinawan in south-west New South Wales.</t>
         </is>
       </c>
-      <c r="R398" s="4" t="inlineStr"/>
+      <c r="R398" s="4" t="n"/>
       <c r="S398" s="4" t="inlineStr"/>
     </row>
     <row r="399">
@@ -40829,7 +40830,7 @@
           <t>component is now August 2029.</t>
         </is>
       </c>
-      <c r="R399" s="4" t="inlineStr"/>
+      <c r="R399" s="4" t="n"/>
       <c r="S399" s="4" t="inlineStr">
         <is>
           <t>AEMO had assumed an earliest in-service date of June 2030 per Transgrid advice for the 2025 Electricity Network Options Report.</t>
@@ -40999,7 +41000,7 @@
           <t>release date identified in the PACR is December 2029.</t>
         </is>
       </c>
-      <c r="R401" s="4" t="inlineStr"/>
+      <c r="R401" s="4" t="n"/>
       <c r="S401" s="4" t="inlineStr"/>
     </row>
     <row r="402">
@@ -41082,7 +41083,7 @@
           <t>for $1,096.3 million ($Real 2022–23) in capital expenditure (capex).1 This application relates to the New South Wales portion of the project.</t>
         </is>
       </c>
-      <c r="R402" s="4" t="inlineStr"/>
+      <c r="R402" s="4" t="n"/>
       <c r="S402" s="4" t="inlineStr">
         <is>
           <t>AER also states this $1,096.3 million represents 55% of the total expected costs for the NSW portion of costs (p.11); the implied NSW total is not computed here. AER separately reports the whole VNI West cost at $3,963.6 million with an approximately 50/50 NSW/Victoria split (see VNN-AO-2024-AER-VNIWEST-TOTAL).</t>
@@ -41169,7 +41170,7 @@
           <t>Total capex ($2022–23) to be commissioned for VNI West stage 1 in years 2022–23 to 2025–26 $1,096.3 million $948.8 million</t>
         </is>
       </c>
-      <c r="R403" s="4" t="inlineStr"/>
+      <c r="R403" s="4" t="n"/>
       <c r="S403" s="4" t="inlineStr">
         <is>
           <t>AER: 'Our decision is to not accept Transgrid's proposed capex of $1,096.3 million and instead substitute an alternative estimate of $948.8 million to ensure consumers pay no more than necessary for progressing stage 1 of the project.' (p.7).</t>
@@ -41256,7 +41257,7 @@
           <t>The total costs for VNI West are estimated at $3,963.6 million ($Real 2022–23),2 with the costs split about 50/50 between the Victorian component and the NSW component</t>
         </is>
       </c>
-      <c r="R404" s="4" t="inlineStr"/>
+      <c r="R404" s="4" t="n"/>
       <c r="S404" s="4" t="inlineStr"/>
     </row>
     <row r="405">
@@ -41339,7 +41340,7 @@
           <t>N5 – South West NSW: +900 MW +4,140 MW 3,499</t>
         </is>
       </c>
-      <c r="R405" s="4" t="inlineStr"/>
+      <c r="R405" s="4" t="n"/>
       <c r="S405" s="4" t="inlineStr">
         <is>
           <t>Table 1 header: 'Capital cost* $m 2020-21'. The identical 3,499 figure also appears for the Option 5A westerly sensitivity row on the same page.</t>
@@ -41422,7 +41423,7 @@
           <t>the total line length of the New South Wales portion has been assumed to be 184 km, of which 85% is assumed to be on private land.</t>
         </is>
       </c>
-      <c r="R406" s="4" t="inlineStr"/>
+      <c r="R406" s="4" t="n"/>
       <c r="S406" s="4" t="inlineStr">
         <is>
           <t>Appears in PACR Appendix A5, Cost estimating methodology, Strategic payments subsection.</t>
@@ -41507,7 +41508,7 @@
           <t>The Environmental Impact Statement (EIS) for the NSW section of the VNI West project was placed on public exhibition in August 2025.</t>
         </is>
       </c>
-      <c r="R407" s="4" t="inlineStr"/>
+      <c r="R407" s="4" t="n"/>
       <c r="S407" s="4" t="inlineStr">
         <is>
           <t>Page also states an Amendment Report and Submissions Report were subsequently prepared and lodged with NSW DPHI.</t>
@@ -41592,7 +41593,7 @@
           <t>We currently anticipate a decision on project approval in late 2026.</t>
         </is>
       </c>
-      <c r="R408" s="4" t="inlineStr"/>
+      <c r="R408" s="4" t="n"/>
       <c r="S408" s="4" t="inlineStr">
         <is>
           <t>Full sentence: 'NSW DPHI is reviewing the EIS, Amendment Report and Submissions Report for VNI West before making a recommendation towards a final approval decision by the State and Commonwealth governments.'</t>
@@ -41774,7 +41775,7 @@
 Class 4 (± 30%)</t>
         </is>
       </c>
-      <c r="R410" s="4" t="inlineStr"/>
+      <c r="R410" s="4" t="n"/>
       <c r="S410" s="4" t="inlineStr">
         <is>
           <t>Page numbers are the '--- PDF page n ---' markers of the text derivative.</t>
@@ -41866,7 +41867,7 @@
 $315m WRL project)</t>
         </is>
       </c>
-      <c r="R411" s="4" t="inlineStr"/>
+      <c r="R411" s="4" t="n"/>
       <c r="S411" s="4" t="inlineStr">
         <is>
           <t>Basis for the SHARED_ATTRIBUTION warning.</t>
@@ -41957,7 +41958,7 @@
           <t>For ISP modelling, AEMO has applied a cost of $3,614 million for VNI West. This is determined by subtracting the cost of WRL from the quoted project cost in 2020-21 dollars</t>
         </is>
       </c>
-      <c r="R412" s="4" t="inlineStr"/>
+      <c r="R412" s="4" t="n"/>
       <c r="S412" s="4" t="inlineStr">
         <is>
           <t>Do not present $3,499m and $3,614m as two points in a cost series.</t>
@@ -42139,7 +42140,7 @@
           <t>Transgrid has advised $565 million of this amount relates to approved early works and other incurred costs.</t>
         </is>
       </c>
-      <c r="R414" s="4" t="inlineStr"/>
+      <c r="R414" s="4" t="n"/>
       <c r="S414" s="4" t="inlineStr">
         <is>
           <t>Price basis not restated in the footnote; see PRICE_BASIS_UNKNOWN.</t>
@@ -42227,7 +42228,7 @@
 million Class 5b (±50%), above the $7,600 million cost of VNI West, which includes two transformers only.</t>
         </is>
       </c>
-      <c r="R415" s="4" t="inlineStr"/>
+      <c r="R415" s="4" t="n"/>
       <c r="S415" s="4" t="inlineStr">
         <is>
           <t>Footnote 103. Price basis not stated.</t>
@@ -42310,7 +42311,7 @@
           <t>North: 1,935 MW</t>
         </is>
       </c>
-      <c r="R416" s="4" t="inlineStr"/>
+      <c r="R416" s="4" t="n"/>
       <c r="S416" s="4" t="inlineStr"/>
     </row>
     <row r="417">
@@ -42389,7 +42390,7 @@
           <t>South: 1,669 MW</t>
         </is>
       </c>
-      <c r="R417" s="4" t="inlineStr"/>
+      <c r="R417" s="4" t="n"/>
       <c r="S417" s="4" t="inlineStr"/>
     </row>
     <row r="418">
@@ -42468,7 +42469,7 @@
           <t>V2: 1,580 MW</t>
         </is>
       </c>
-      <c r="R418" s="4" t="inlineStr"/>
+      <c r="R418" s="4" t="n"/>
       <c r="S418" s="4" t="inlineStr"/>
     </row>
     <row r="419">
@@ -42547,7 +42548,7 @@
           <t>V3 (WRL and VNI timing): 200 MW**</t>
         </is>
       </c>
-      <c r="R419" s="4" t="inlineStr"/>
+      <c r="R419" s="4" t="n"/>
       <c r="S419" s="4" t="inlineStr">
         <is>
           <t>Footnote ** states the 200 MW is in addition to the 1,460 MW from the anticipated WRL (uprated) project.</t>
@@ -42630,7 +42631,7 @@
           <t>N5: 900 MW</t>
         </is>
       </c>
-      <c r="R420" s="4" t="inlineStr"/>
+      <c r="R420" s="4" t="n"/>
       <c r="S420" s="4" t="inlineStr"/>
     </row>
     <row r="421">
@@ -42792,7 +42793,7 @@
           <t>Reverse: 1,670</t>
         </is>
       </c>
-      <c r="R422" s="4" t="inlineStr"/>
+      <c r="R422" s="4" t="n"/>
       <c r="S422" s="4" t="inlineStr"/>
     </row>
     <row r="423">
@@ -42871,7 +42872,7 @@
           <t>V1: 1,580</t>
         </is>
       </c>
-      <c r="R423" s="4" t="inlineStr"/>
+      <c r="R423" s="4" t="n"/>
       <c r="S423" s="4" t="inlineStr">
         <is>
           <t>REZ labels changed between the 2024 and 2026 ISPs; do not treat V2 (2024) and V1 (2026) as the same series without checking the REZ definitions.</t>
@@ -42954,7 +42955,7 @@
           <t>WV2: 200</t>
         </is>
       </c>
-      <c r="R424" s="4" t="inlineStr"/>
+      <c r="R424" s="4" t="n"/>
       <c r="S424" s="4" t="inlineStr"/>
     </row>
     <row r="425">
@@ -43033,7 +43034,7 @@
           <t>N5: 600 (+1,800105)</t>
         </is>
       </c>
-      <c r="R425" s="4" t="inlineStr"/>
+      <c r="R425" s="4" t="n"/>
       <c r="S425" s="4" t="inlineStr"/>
     </row>
     <row r="426">
@@ -43112,7 +43113,7 @@
           <t>expand the REZ transfer capacity from Dinawan by 1,800 MW</t>
         </is>
       </c>
-      <c r="R426" s="4" t="inlineStr"/>
+      <c r="R426" s="4" t="n"/>
       <c r="S426" s="4" t="inlineStr">
         <is>
           <t>Footnotes 103 and 105; based on advice from Transgrid and EnergyCo.</t>
@@ -43439,7 +43440,7 @@
 transformers.</t>
         </is>
       </c>
-      <c r="R430" s="4" t="inlineStr"/>
+      <c r="R430" s="4" t="n"/>
       <c r="S430" s="4" t="inlineStr"/>
     </row>
     <row r="431">
@@ -43514,7 +43515,7 @@
           <t>Establish Dinawan 500 kV switchyard with three103 500/330 kV 1,500 MVA transformers.</t>
         </is>
       </c>
-      <c r="R431" s="4" t="inlineStr"/>
+      <c r="R431" s="4" t="n"/>
       <c r="S431" s="4" t="inlineStr"/>
     </row>
     <row r="432">
@@ -43589,7 +43590,7 @@
           <t>Up to +/- 400 MVAr dynamic reactive compensation at the new 220 kV Tragowel</t>
         </is>
       </c>
-      <c r="R432" s="4" t="inlineStr"/>
+      <c r="R432" s="4" t="n"/>
       <c r="S432" s="4" t="inlineStr"/>
     </row>
     <row r="433">
@@ -43664,7 +43665,7 @@
           <t>VNI West is a proposed 500 kV interconnector from near Bulgana in Victoria to Dinawan in south-west New South Wales.</t>
         </is>
       </c>
-      <c r="R433" s="4" t="inlineStr"/>
+      <c r="R433" s="4" t="n"/>
       <c r="S433" s="4" t="inlineStr"/>
     </row>
     <row r="434">
@@ -43831,7 +43832,7 @@
 August 2029107</t>
         </is>
       </c>
-      <c r="R435" s="4" t="inlineStr"/>
+      <c r="R435" s="4" t="n"/>
       <c r="S435" s="4" t="inlineStr"/>
     </row>
     <row r="436">
@@ -43913,7 +43914,7 @@
 release date identified in the PACR is December 2029.</t>
         </is>
       </c>
-      <c r="R436" s="4" t="inlineStr"/>
+      <c r="R436" s="4" t="n"/>
       <c r="S436" s="4" t="inlineStr">
         <is>
           <t>The PACR is now archived (VNV-TRANSGRID-2023-PACR) but its text does not use the phrase 'capacity release date'; the PACR instead states a headline commissioning date of 1 July 2031 in the Step Change scenario (p84), matching VNV-AO-2023-DELIVERY-JULY2031. This December 2029 figure remains sourced only from the 2024 ISP's characterisation of the PACR.</t>
@@ -43993,7 +43994,7 @@
 Kerang to Dinawan crossing the Murray river north of Kerang to Bulgana Terminal Station (BGTS)</t>
         </is>
       </c>
-      <c r="R437" s="4" t="inlineStr"/>
+      <c r="R437" s="4" t="n"/>
       <c r="S437" s="4" t="inlineStr">
         <is>
           <t>This is the NEVA order the earlier version of this pack recorded as unavailable.</t>
@@ -44073,7 +44074,7 @@
 Kerang to Dinawan crossing the Murray river north of Kerang to Bulgana Terminal Station (BGTS)</t>
         </is>
       </c>
-      <c r="R438" s="4" t="inlineStr"/>
+      <c r="R438" s="4" t="n"/>
       <c r="S438" s="4" t="inlineStr"/>
     </row>
     <row r="439">
@@ -44148,7 +44149,7 @@
           <t>a new 500 kV double-circuit overhead line</t>
         </is>
       </c>
-      <c r="R439" s="4" t="inlineStr"/>
+      <c r="R439" s="4" t="n"/>
       <c r="S439" s="4" t="inlineStr"/>
     </row>
     <row r="440">
@@ -44224,7 +44225,7 @@
 and up to +/- 400 MV Ar dynamic reactive compensation on the 220 kV network.</t>
         </is>
       </c>
-      <c r="R440" s="4" t="inlineStr"/>
+      <c r="R440" s="4" t="n"/>
       <c r="S440" s="4" t="inlineStr">
         <is>
           <t>Source text renders 'MVA'/'MVAr' with an internal space ('MV A', 'MV Ar'); reproduced verbatim.</t>
@@ -44303,7 +44304,7 @@
           <t>and up to +/- 400 MV Ar dynamic reactive compensation on the 220 kV network</t>
         </is>
       </c>
-      <c r="R441" s="4" t="inlineStr"/>
+      <c r="R441" s="4" t="n"/>
       <c r="S441" s="4" t="inlineStr">
         <is>
           <t>Source text renders 'MVAr' with an internal space ('MV Ar'); reproduced verbatim.</t>
@@ -44388,7 +44389,7 @@
           <t>with a schedule delivery date of July 2031</t>
         </is>
       </c>
-      <c r="R442" s="4" t="inlineStr"/>
+      <c r="R442" s="4" t="n"/>
       <c r="S442" s="4" t="inlineStr">
         <is>
           <t>Not an independent estimate; the Minister is quoting AEMO's 2022 ISP page 67.</t>
@@ -44467,7 +44468,7 @@
           <t>a preferred easement of 70m wide along most of the route has been identified</t>
         </is>
       </c>
-      <c r="R443" s="4" t="inlineStr"/>
+      <c r="R443" s="4" t="n"/>
       <c r="S443" s="4" t="inlineStr">
         <is>
           <t>Web capture has no page markers; pinpoint recorded as 'web'.</t>
@@ -44559,7 +44560,7 @@
 comprised of $1,755 million in Victoria and $1,744 million in New South Wales.</t>
         </is>
       </c>
-      <c r="R444" s="4" t="inlineStr"/>
+      <c r="R444" s="4" t="n"/>
       <c r="S444" s="4" t="inlineStr">
         <is>
           <t>Estimate accuracy of ±30% ('Class 4' under the AACE classification) is stated separately on p49; FY2020-21 dollars basis stated in footnote 77 on p47. The Victoria/NSW split figures ($1,755m / $1,744m) also appear in Table 6 on p48 ('Total (by state) 1,651 1,755 1,744 1,755').</t>
@@ -44731,7 +44732,7 @@
 +1,935 MW</t>
         </is>
       </c>
-      <c r="R446" s="4" t="inlineStr"/>
+      <c r="R446" s="4" t="n"/>
       <c r="S446" s="4" t="inlineStr">
         <is>
           <t>Table 1, Summary of the credible options assessed (p10).</t>
@@ -44814,7 +44815,7 @@
           <t>+1,669 MW V2 – Murray River: +1,580 MW</t>
         </is>
       </c>
-      <c r="R447" s="4" t="inlineStr"/>
+      <c r="R447" s="4" t="n"/>
       <c r="S447" s="4" t="inlineStr">
         <is>
           <t>Table 1, Summary of the credible options assessed (p10).</t>
@@ -44906,7 +44907,7 @@
 option of approximately $3.256 billion: $1.605 billion in Victoria and $1.651 billion in New South Wales.</t>
         </is>
       </c>
-      <c r="R448" s="4" t="inlineStr"/>
+      <c r="R448" s="4" t="n"/>
       <c r="S448" s="4" t="inlineStr">
         <is>
           <t>Accuracy of ±30% ('class 4') for these PADR estimates is stated on p71. Table 4 (p53) shows the same Victoria/NSW split: 'Total (by state) 1,651 1,605 1,957 1,918' and 'Total (all states) 3,256 3,874'.</t>
@@ -44998,7 +44999,7 @@
 Total (all states) 3,256 3,874</t>
         </is>
       </c>
-      <c r="R449" s="4" t="inlineStr"/>
+      <c r="R449" s="4" t="n"/>
       <c r="S449" s="4" t="inlineStr">
         <is>
           <t>Table 4, Summary of the credible options assessed in this PADR.</t>
@@ -45082,7 +45083,7 @@
 option of approximately $3.256 billion: $1.605 billion in Victoria and $1.651 billion in New South Wales.</t>
         </is>
       </c>
-      <c r="R450" s="4" t="inlineStr"/>
+      <c r="R450" s="4" t="n"/>
       <c r="S450" s="4" t="inlineStr">
         <is>
           <t>Unlike PACR Table 6, PADR Table 4 does not itemise an approximate line length split by state for this option.</t>
@@ -45166,7 +45167,7 @@
 Victoria to New South Wales and 1,800 MW from New South Wales to Victoria 148.</t>
         </is>
       </c>
-      <c r="R451" s="4" t="inlineStr"/>
+      <c r="R451" s="4" t="n"/>
       <c r="S451" s="4" t="inlineStr"/>
     </row>
     <row r="452">
@@ -45246,7 +45247,7 @@
 Victoria to New South Wales and 1,800 MW from New South Wales to Victoria 148.</t>
         </is>
       </c>
-      <c r="R452" s="4" t="inlineStr"/>
+      <c r="R452" s="4" t="n"/>
       <c r="S452" s="4" t="inlineStr"/>
     </row>
     <row r="453">
@@ -45326,7 +45327,7 @@
 Project EnergyConnect to a 500 kV specification instead of 330 kV.</t>
         </is>
       </c>
-      <c r="R453" s="4" t="inlineStr"/>
+      <c r="R453" s="4" t="n"/>
       <c r="S453" s="4" t="inlineStr">
         <is>
           <t>The $181.5 million Federal underwriting funds this enhancement as part of VNI West early works (Appendix A3, Cost estimating methodology).</t>
@@ -45405,7 +45406,7 @@
           <t>The updated scope results in a higher capacity and harnesses 1,460 MW of renewable capacity rather than the original</t>
         </is>
       </c>
-      <c r="R454" s="4" t="inlineStr"/>
+      <c r="R454" s="4" t="n"/>
       <c r="S454" s="4" t="inlineStr">
         <is>
           <t>The 600 MW figure completes on the next derivative line as 'design of 600 MW.'; the 2019 PACR itself is unavailable.</t>
@@ -45484,7 +45485,7 @@
           <t>The updated scope results in a higher capacity and harnesses 1,460 MW of renewable capacity rather than the original design of 600 MW.</t>
         </is>
       </c>
-      <c r="R455" s="4" t="inlineStr"/>
+      <c r="R455" s="4" t="n"/>
       <c r="S455" s="4" t="inlineStr"/>
     </row>
     <row r="456">
@@ -45559,7 +45560,7 @@
           <t>The updated scope results in a higher capacity and harnesses 1,460 MW of renewable capacity rather than the original</t>
         </is>
       </c>
-      <c r="R456" s="4" t="inlineStr"/>
+      <c r="R456" s="4" t="n"/>
       <c r="S456" s="4" t="inlineStr"/>
     </row>
     <row r="457">
@@ -45634,7 +45635,7 @@
           <t>The updated scope results in a higher capacity and harnesses 1,460 MW of renewable capacity rather than the original design of 600 MW.</t>
         </is>
       </c>
-      <c r="R457" s="4" t="inlineStr"/>
+      <c r="R457" s="4" t="n"/>
       <c r="S457" s="4" t="inlineStr"/>
     </row>
     <row r="458">
@@ -45709,7 +45710,7 @@
           <t>695 MW</t>
         </is>
       </c>
-      <c r="R458" s="4" t="inlineStr"/>
+      <c r="R458" s="4" t="n"/>
       <c r="S458" s="4" t="inlineStr">
         <is>
           <t>Delivery scope table cell; adjacent derivative lines give the MEL-WNV directional boundary.</t>
@@ -45788,7 +45789,7 @@
           <t>V2:310 MW</t>
         </is>
       </c>
-      <c r="R459" s="4" t="inlineStr"/>
+      <c r="R459" s="4" t="n"/>
       <c r="S459" s="4" t="inlineStr"/>
     </row>
     <row r="460">
@@ -46025,7 +46026,7 @@
           <t>The proposed 190-kilometre 500 kV transmission line will connect new renewable energy generation projects and transmit electricity from near Bulgana in western Victoria to Sydenham in Melbourne’s north-west.</t>
         </is>
       </c>
-      <c r="R462" s="4" t="inlineStr"/>
+      <c r="R462" s="4" t="n"/>
       <c r="S462" s="4" t="inlineStr">
         <is>
           <t>Web capture; unpaged, cited as page 'web'.</t>
@@ -46098,7 +46099,7 @@
           <t>AusNet is pleased to announce that it has appointed a joint venture between ACCIONA and Genus to undertake the construction works for the Western Renewables Link (WRL), marking a significant milestone for the project.</t>
         </is>
       </c>
-      <c r="R463" s="4" t="inlineStr"/>
+      <c r="R463" s="4" t="n"/>
       <c r="S463" s="4" t="inlineStr">
         <is>
           <t>Released 12 December 2025. The release states construction can 'move ahead if the project receives the necessary planning approvals'; the WRL EES hearing outcome remains unarchived (see WRL-AO-2026-EES-HEARING).</t>
@@ -46284,7 +46285,7 @@
           <t>Included cost  315  315</t>
         </is>
       </c>
-      <c r="R465" s="4" t="inlineStr"/>
+      <c r="R465" s="4" t="n"/>
       <c r="S465" s="4" t="inlineStr">
         <is>
           <t>PACR Table 6 states this WRL incremental cost is 'included in the totals above but separately itemised here as well for transparency', identical across both Option 5 and Option 5A. The PACR separately explains (p.48-49) that these are 'the direct costs of modifying the WRL project so that all costs associated with modifying WRL to connect VNI West at Bulgana are captured'; costs are estimated to an accuracy of ±30%, 'Class 4' under AACE classification.</t>
@@ -46375,7 +46376,7 @@
           <t>3,499 *</t>
         </is>
       </c>
-      <c r="R466" s="4" t="inlineStr"/>
+      <c r="R466" s="4" t="n"/>
       <c r="S466" s="4" t="inlineStr">
         <is>
           <t>Recorded for boundary transparency only.</t>
@@ -46458,7 +46459,7 @@
           <t>For ISP modelling, AEMO has applied a cost of $3,614 million for VNI West. This is determined by subtracting the cost of WRL from the quoted project cost in 2020-21 dollars</t>
         </is>
       </c>
-      <c r="R467" s="4" t="inlineStr"/>
+      <c r="R467" s="4" t="n"/>
       <c r="S467" s="4" t="inlineStr">
         <is>
           <t>Do not back-solve a WRL cost from this figure.</t>
@@ -46778,7 +46779,7 @@
           <t>A new 500 kV switchyard with two new 1,000 MVA 500/220 kV transformers at</t>
         </is>
       </c>
-      <c r="R471" s="4" t="inlineStr"/>
+      <c r="R471" s="4" t="n"/>
       <c r="S471" s="4" t="inlineStr"/>
     </row>
     <row r="472">
@@ -46853,7 +46854,7 @@
           <t>Western Renewables Link (WRL) is a planned 500 kV double-circuit overhead electricity transmission line from Bulgana in western Victoria to</t>
         </is>
       </c>
-      <c r="R472" s="4" t="inlineStr"/>
+      <c r="R472" s="4" t="n"/>
       <c r="S472" s="4" t="inlineStr"/>
     </row>
     <row r="473">
@@ -46928,7 +46929,7 @@
           <t>relocation of the North Ballarat terminal station to Bulgana and upgrade of the transmission line from north of Ballarat to Bulgana from 220 kV</t>
         </is>
       </c>
-      <c r="R473" s="4" t="inlineStr"/>
+      <c r="R473" s="4" t="n"/>
       <c r="S473" s="4" t="inlineStr"/>
     </row>
     <row r="474">
@@ -46962,7 +46963,11 @@
           <t>AEMO 2026 expected completion</t>
         </is>
       </c>
-      <c r="G474" s="4" t="n"/>
+      <c r="G474" s="4" t="inlineStr">
+        <is>
+          <t>November 2029</t>
+        </is>
+      </c>
       <c r="H474" s="4" t="inlineStr">
         <is>
           <t>date</t>
@@ -47082,7 +47087,7 @@
           <t>This project is classified as an anticipated project and is expected to be completed in mid-2027.</t>
         </is>
       </c>
-      <c r="R475" s="4" t="inlineStr"/>
+      <c r="R475" s="4" t="n"/>
       <c r="S475" s="4" t="inlineStr">
         <is>
           <t>Stated value: mid-2027; scope table states 'project July 2027*' with a full-capacity-after-testing qualifier.</t>
@@ -47159,7 +47164,7 @@
           <t>The WRL EES public hearing concluded on 3 March 2026.</t>
         </is>
       </c>
-      <c r="R476" s="4" t="inlineStr"/>
+      <c r="R476" s="4" t="n"/>
       <c r="S476" s="4" t="inlineStr">
         <is>
           <t>Stated value: 3 March 2026.</t>
@@ -47238,7 +47243,7 @@
           <t>Construction of a new 500 kV double circuit transmission line from SYTS to BGTS with switched estimated 70 MV Ar shunt line reactors at the end of each circuit.</t>
         </is>
       </c>
-      <c r="R477" s="4" t="inlineStr"/>
+      <c r="R477" s="4" t="n"/>
       <c r="S477" s="4" t="inlineStr">
         <is>
           <t>SYTS = Sydenham Terminal Station; BGTS = Bulgana Terminal Station, per the Order's own defined terms.</t>
@@ -47317,7 +47322,7 @@
           <t>Construction of a new 500 kV double circuit transmission line from SYTS to BGTS with switched estimated 70 MV Ar shunt line reactors at the end of each circuit.</t>
         </is>
       </c>
-      <c r="R478" s="4" t="inlineStr"/>
+      <c r="R478" s="4" t="n"/>
       <c r="S478" s="4" t="inlineStr"/>
     </row>
     <row r="479">
@@ -47392,7 +47397,7 @@
           <t>including two 500/220 kV 1000 MV A transformers</t>
         </is>
       </c>
-      <c r="R479" s="4" t="inlineStr"/>
+      <c r="R479" s="4" t="n"/>
       <c r="S479" s="4" t="inlineStr">
         <is>
           <t>This is the legal instrument underlying the AEMO 2024/2026 delivery scope statements of the same transformers.</t>
@@ -47471,7 +47476,7 @@
           <t>the WRL segment from Mount Prospect to Bulgana should be uprated from 220 kilovolts to 500 kilovolts (the WRL Uprate)</t>
         </is>
       </c>
-      <c r="R480" s="4" t="inlineStr"/>
+      <c r="R480" s="4" t="n"/>
       <c r="S480" s="4" t="inlineStr">
         <is>
           <t>Para 32 of the reasons states the WRL terminal station previously proposed for Mount Prospect (north of Ballarat) would be constructed instead at Bulgana.</t>
@@ -47544,7 +47549,7 @@
           <t>Option 5A requires some changes to the WRL, including relocation of the Mount Prospect terminal station site to Bulgana and uprating the WRL from 220 kilovolts to 500 kilovolts from Mount Prospect to Bulgana.</t>
         </is>
       </c>
-      <c r="R481" s="4" t="inlineStr"/>
+      <c r="R481" s="4" t="n"/>
       <c r="S481" s="4" t="inlineStr">
         <is>
           <t>Para 32 clarifies Mount Prospect is 'north of Ballarat'.</t>
@@ -47621,7 +47626,7 @@
           <t>uprated from 220 kilovolts to 500 kilovolts (the WRL Uprate), which would enable additional generation capacity in Western Victoria by as early as 2027</t>
         </is>
       </c>
-      <c r="R482" s="4" t="inlineStr"/>
+      <c r="R482" s="4" t="n"/>
       <c r="S482" s="4" t="inlineStr">
         <is>
           <t>Recorded for CONTRADICTION context; do not treat as equivalent to WRL-AO-2024-COMPLETION-MID2027.</t>
@@ -47698,7 +47703,7 @@
           <t>WRL PACR means the Western Victoria Renewable Integration Project Assessment Conclusion Report published by AEMO on 19 July 2019.</t>
         </is>
       </c>
-      <c r="R483" s="4" t="inlineStr"/>
+      <c r="R483" s="4" t="n"/>
       <c r="S483" s="4" t="inlineStr"/>
     </row>
   </sheetData>
@@ -47746,6 +47751,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -51990,6 +51996,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -57169,10 +57176,11 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every capture cited by a pack, hash-verified against its manifest row. Shared AEMO captures appear once.</t>
-        </is>
-      </c>
-    </row>
+          <t>Archived source register; hashes retained from the verified upstream register. Referenced upstream manifest files are not asserted to be included. Research cutoff 2026-09-04; audit correction 2026-09-07 is not new research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -62658,6 +62666,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -63088,7 +63097,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>All three figures are retained unresolved (two sources at 150 km, one at 166 km). Do not silently prefer either value for the H2P/feeder length; the chart's feeder_lines_km finding is recorded as contradicted rather than supported.</t>
+          <t>The chart's 150 km has positive support: CWO-18 p11 states a corridor of around 150 km and CWO-26 derivative line18 states 150 km of 330 kV generator-connection lines. CWO-23 p10 instead describes approximately 166 km of H2P lines, with conditional separable portions (pp12,19). Different vintages, corridor versus line measurement and conditional scope remain unreconciled. Retain an unresolved source discrepancy, not a same-boundary numerical disproof; five portions were excluded in 2025.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -63194,12 +63203,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>The chart's date cell reads 2029. No archived source states 2029: AEMO gives December 2028 for the committed project, the AER gives staged infrastructure completion between April 2028 and April 2030 with generation from December 2028 to September 2030, and the Expansion whose cost is in the same row is timed March 2033.</t>
+          <t>2029 is not the AEMO 2026 committed-project timing of December 2028 (CWO-22 p23), but falls within the AER infrastructure-completion window April 2028-April 2030 (CWO-18 p12). Expansion timing is March 2033 (CWO-22 p57). The chart milestone is unspecified; a timing conflict applies only if comparing the same committed-project milestone.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>The author must choose which milestone the date column represents and whether one date can stand for a row that aggregates three projects.</t>
+          <t>Define the milestone before comparing dates; 2029 is within the AER staged window.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -64514,7 +64523,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>The chart row states $5.5 billion and 1.4 GW. No archived source states either value for any Project Marinus boundary; sources state 1,500 MW and, for the chart's own two-stage boundary, a reported total of $7,570 million in $2023.</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex. Separately, the chart's 1.4 GW contradicts the source-defined two-link nameplate of 1.5 GW (AEMO 2026 pp26,58-59).</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -64736,12 +64745,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Tasmania REZ Expansion (T2 Option 1) and the NWTD works share scope and benefits with Project Marinus but are separate actionable projects with their own cost boundaries.</t>
+          <t>NWTD is a component of Project Marinus. Tasmania REZ Expansion is a separate actionable project receiving the Burnie-Hampshire Hills scope under Option 2A.</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Do not allocate Tasmania REZ Expansion or NWTD amounts to the Marinus chart row, and do not treat the row as covering all Tasmanian works enabled by the interconnector.</t>
+          <t>Do not double count NWTD within Project Marinus or re-add transferred T2 Option 1 scope to Option 2A. A Link-only cost is unresolved.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -64773,7 +64782,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>The chart's 345 km trunk length is the sum of two separately stated approximate HVDC cable lengths (255 km subsea, 90 km underground), and Millions/trunk KM is a workbook formula over that sum and the contradicted cost cell.</t>
+          <t>The chart's 345 km trunk length is the sum of two separately stated approximate HVDC cable lengths (255 km subsea, 90 km underground), and Millions/trunk KM is a workbook formula over that sum and the unresolved Link-only cost cell.</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -64810,12 +64819,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Three definitions are the author's to settle: whether any inclusive cost view (Project Marinus plus NWTD) may be published; whether an HVDC cable route counts as trunk kilometres when the chart defines trunk as distance rated at 500 kV; and how alt routes and hubs are counted for a subsea interconnector.</t>
+          <t>Project Marinus includes Marinus Link and NWTD (2025 RIT-T pp6,18). The $5,035m Stage 1 and $2,535m Stage 2 figures, in June 2023 prices, are Project Marinus study-period costs, not Link-only construction outturn; the valuation period is shorter than project life and depends on cable 2 timing. AEMO 2026 p59 reports $7,570m in the feedback-loop context. Stage 2 Option 2A differs from Option 2: the source removes $184m Burnie-Hampshire Hills scope transferred to T2 Option 1, giving $2,351m in $2023 and $2,485m in $2025. No like-for-like Link-only replacement for the chart's $5.5bn is established; do not derive one by subtraction. Funding is not capex.</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Until the author decides, the cost cell stays at the source-defined boundary, the trunk cell stays marked as derived, and alt_routes and hubs stay marked as judgments.</t>
+          <t>The Link-only cost replacement remains unresolved; the trunk cell stays derived and alt_routes and hubs remain author judgments.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
@@ -66044,12 +66053,12 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Two archived cost figures exist for this row on different bases: the AEMO-modelled $2,621m ($2025, both options combined) and Transgrid's own PADR Option 6 total of $3,519m (nominal, staged $1,135m then $2,384m). The chart's $3.510bn matches neither basis and is a transcription of $3,519m.</t>
+          <t>The immutable chart contains $3.5bn, consistent with rounding the PADR Option 6 total of $3,519m nominal to one decimal billion. The source gives Stage 1 $1,135m and Stage 2 $2,384m, P50 Class 5 (+100%/-50%). AEMO's $2,621m modelled $2025 amount is a different price basis. No transcription error is established (PADR p38; AEMO 2026 p43).</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>The author must choose which basis the chart publishes ($2025 modelled or nominal PADR) and correct the transcription; the pack neither converts between price bases nor treats the difference as growth.</t>
+          <t>The immutable chart contains $3.5bn, consistent with rounding the PADR Option 6 total of $3,519m nominal to one decimal billion. The source gives Stage 1 $1,135m and Stage 2 $2,384m, P50 Class 5 (+100%/-50%). AEMO's $2,621m modelled $2025 amount is a different price basis. No transcription error is established (PADR p38; AEMO 2026 p43).</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -66076,17 +66085,17 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>CONTRADICTION</t>
+          <t>NON_COMPARABLE_SERIES</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>The chart notes cite $3.510 billion for PADR Option 6. Transgrid's own PADR, now archived, states Option 6's total capital cost as $3,519 million (nominal), confirming the archived AEMO quotation of the same figure; the chart value matches neither this total nor AEMO's separately archived $2,621 million ($2025) modelled total for the same two options combined.</t>
+          <t>The immutable chart contains $3.5bn, consistent with rounding the PADR Option 6 total of $3,519m nominal to one decimal billion. The source gives Stage 1 $1,135m and Stage 2 $2,384m, P50 Class 5 (+100%/-50%). AEMO's $2,621m modelled $2025 amount is a different price basis. No transcription error is established (PADR p38; AEMO 2026 p43).</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>The $3.510bn is a transcription of $3,519m (last two digits transposed), not a distinct sourced figure; it also does not match the AEMO-modelled total on a different price basis. Both must be resolved before publication.</t>
+          <t>Retain rounding, nominal/modelled price bases and estimate uncertainty; no numerical cost contradiction is established.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -66225,12 +66234,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>The millions-per-trunk-km cell (30.70) is 3,510 divided by 114. The 114 km is now archived (2023 Southern Ring document), but 3,510 does not match any archived cost figure -- the archived PADR Option 6 total is $3,519 million, not $3,510 million.</t>
+          <t>30.70175438596491 = 3,500 AUD million / 114 km, using the original chart inputs. The $3.5bn rounds the $3,519m nominal Option 6 estimate; the 114 km is the older 2023 preparatory route, whereas the 2026 PADR describes approximately 100 km on a revised scope. This mixed-vintage ratio is not a reconciled source-defined construction cost per km (2023 preparatory p8; PADR pp38,43).</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>The ratio's cost input remains an unverified transcription and cannot be validated against any archived source; recomputing with the archived $3,519 million would give a different ratio.</t>
+          <t>30.70175438596491 = 3,500 AUD million / 114 km, using the original chart inputs. The $3.5bn rounds the $3,519m nominal Option 6 estimate; the 114 km is the older 2023 preparatory route, whereas the 2026 PADR describes approximately 100 km on a revised scope. This mixed-vintage ratio is not a reconciled source-defined construction cost per km (2023 preparatory p8; PADR pp38,43).</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
@@ -66476,12 +66485,12 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>The chart's 3.7 cost is half of a whole-interconnector amount: the VNI West (NSW) and VNI West (VIC) rows carry the identical 3.7, and no archived source states a NSW-only cost. The only current whole-VNI figure, $7,600m ($2025, Class 4, two transformers), halves to 3.8, so the halved input cannot be identified in the archive.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>The cell must not be published as a NSW project cost. Either restate it as an explicitly labelled half of the $7,600m whole-project amount or leave it unsourced.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -67068,7 +67077,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>The chart's $3.7bn cost cell is not a sourced value: it is half of AEMO's 2026 reported $7,600m ($2025) whole-project figure, with the same 3.7 placed in both the VNI West (VIC) and VNI West (NSW) rows.</t>
+          <t>The identical $3.7bn NSW and Victoria chart entries have no evidenced current state allocation. $3.7bn is not half of the 2026 $7.6bn whole-VNI total (half is $3.8bn). The author's exact derivation is unresolved. Historical PACR Option 5A allocations ($1,755m Victoria / $1,744m NSW, FY2020-21, p48) do not allocate the 2026 total; NSW $948.8m approved early works is not a NSW whole-project estimate.</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
